--- a/Assets/AddressableResource/Data/Excels/CardData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\Resources\Data\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5331ED99-1494-4266-86A7-2009F2979FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4830343F-71D3-4C97-AABA-C358A334B429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42450" yWindow="3750" windowWidth="31935" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="1155" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -55,11 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="66">
-  <si>
-    <t>number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="65">
   <si>
     <t>Normal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -485,7 +481,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -493,6 +489,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -543,540 +549,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1410,7 +882,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:XFC114"/>
+  <dimension ref="A1:R114"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="2" width="18.25" style="7" customWidth="1"/>
@@ -1422,32 +894,30 @@
     <col min="12" max="14" width="14" style="4" customWidth="1"/>
     <col min="15" max="15" width="17.625" style="4"/>
     <col min="16" max="16" width="17.625" style="9"/>
-    <col min="19" max="16382" width="17.625" style="4"/>
-    <col min="16383" max="16383" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16384" max="16384" width="8.875" style="4" customWidth="1"/>
+    <col min="19" max="16384" width="17.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16 16383:16383">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K1" s="4">
         <f>VLOOKUP(J1,N:O,2,FALSE)</f>
@@ -1462,24 +932,21 @@
         <v>6</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="XFC1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16 16383:16383">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="5">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -1494,10 +961,10 @@
         <v>59</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" s="4">
         <v>0</v>
@@ -1507,15 +974,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:16 16383:16383">
+    <row r="3" spans="1:16">
       <c r="A3" s="5">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1530,10 +997,10 @@
         <v>26</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O3" s="4">
         <v>1</v>
@@ -1543,15 +1010,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16 16383:16383">
+    <row r="4" spans="1:16">
       <c r="A4" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1565,10 +1032,10 @@
         <v>13</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O4" s="4">
         <v>2</v>
@@ -1578,15 +1045,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:16 16383:16383">
+    <row r="5" spans="1:16">
       <c r="A5" s="5">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1600,10 +1067,10 @@
         <v>5</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O5" s="10">
         <v>3</v>
@@ -1613,15 +1080,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:16 16383:16383">
+    <row r="6" spans="1:16">
       <c r="A6" s="5">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1635,10 +1102,10 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O6" s="4">
         <v>4</v>
@@ -1648,15 +1115,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:16 16383:16383">
+    <row r="7" spans="1:16">
       <c r="A7" s="5">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1670,10 +1137,10 @@
         <v>4</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O7" s="4">
         <v>5</v>
@@ -1683,15 +1150,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16 16383:16383">
+    <row r="8" spans="1:16">
       <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1700,7 +1167,7 @@
         <v>700</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O8" s="4">
         <v>6</v>
@@ -1710,15 +1177,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:16 16383:16383">
+    <row r="9" spans="1:16">
       <c r="A9" s="7">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1727,7 +1194,7 @@
         <v>800</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O9" s="4">
         <v>7</v>
@@ -1737,15 +1204,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:16 16383:16383">
+    <row r="10" spans="1:16">
       <c r="A10" s="7">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1754,7 +1221,7 @@
         <v>900</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O10" s="4">
         <v>8</v>
@@ -1764,15 +1231,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:16 16383:16383">
+    <row r="11" spans="1:16">
       <c r="A11" s="7">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1781,7 +1248,7 @@
         <v>1000</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O11" s="4">
         <v>9</v>
@@ -1791,15 +1258,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16 16383:16383">
+    <row r="12" spans="1:16">
       <c r="A12" s="7">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1808,7 +1275,7 @@
         <v>1100</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O12" s="4">
         <v>10</v>
@@ -1818,15 +1285,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:16 16383:16383">
+    <row r="13" spans="1:16">
       <c r="A13" s="7">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1835,7 +1302,7 @@
         <v>1200</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O13" s="4">
         <v>11</v>
@@ -1845,15 +1312,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:16 16383:16383">
+    <row r="14" spans="1:16">
       <c r="A14" s="7">
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1862,7 +1329,7 @@
         <v>1300</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O14" s="4">
         <v>12</v>
@@ -1872,15 +1339,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:16 16383:16383">
+    <row r="15" spans="1:16">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1889,7 +1356,7 @@
         <v>1400</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O15" s="4">
         <v>13</v>
@@ -1899,15 +1366,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16 16383:16383">
+    <row r="16" spans="1:16">
       <c r="A16" s="7">
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1916,7 +1383,7 @@
         <v>1500</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O16" s="4">
         <v>14</v>
@@ -1931,10 +1398,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1943,7 +1410,7 @@
         <v>1600</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O17" s="4">
         <v>15</v>
@@ -1958,10 +1425,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1970,7 +1437,7 @@
         <v>1700</v>
       </c>
       <c r="N18" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O18" s="20">
         <v>16</v>
@@ -1985,10 +1452,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -1997,7 +1464,7 @@
         <v>1800</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O19" s="4">
         <v>17</v>
@@ -2009,13 +1476,13 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
@@ -2024,7 +1491,7 @@
         <v>1900</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" s="4">
         <v>18</v>
@@ -2039,10 +1506,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
@@ -2051,7 +1518,7 @@
         <v>2000</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O21" s="10">
         <v>19</v>
@@ -2063,13 +1530,13 @@
     </row>
     <row r="22" spans="1:16">
       <c r="A22" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -2078,7 +1545,7 @@
         <v>2100</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O22" s="4">
         <v>20</v>
@@ -2093,10 +1560,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
@@ -2105,7 +1572,7 @@
         <v>2200</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O23" s="10">
         <v>21</v>
@@ -2117,13 +1584,13 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
@@ -2132,7 +1599,7 @@
         <v>2300</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O24" s="4">
         <v>22</v>
@@ -2147,10 +1614,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4">
         <v>1</v>
@@ -2159,7 +1626,7 @@
         <v>2400</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O25" s="11">
         <v>23</v>
@@ -2174,10 +1641,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
@@ -2186,7 +1653,7 @@
         <v>2500</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O26" s="4">
         <v>24</v>
@@ -2198,13 +1665,13 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="4">
         <v>1</v>
@@ -2213,7 +1680,7 @@
         <v>2600</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O27" s="4">
         <v>25</v>
@@ -2228,10 +1695,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
@@ -2240,7 +1707,7 @@
         <v>2700</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O28" s="10">
         <v>26</v>
@@ -2255,10 +1722,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
@@ -2267,7 +1734,7 @@
         <v>2800</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O29" s="4">
         <v>27</v>
@@ -2282,10 +1749,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
@@ -2294,7 +1761,7 @@
         <v>2900</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O30" s="4">
         <v>28</v>
@@ -2309,10 +1776,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
@@ -2321,7 +1788,7 @@
         <v>3000</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O31" s="4">
         <v>29</v>
@@ -2333,13 +1800,13 @@
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="4">
         <v>1</v>
@@ -2348,7 +1815,7 @@
         <v>3100</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O32" s="4">
         <v>30</v>
@@ -2363,10 +1830,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="4">
         <v>1</v>
@@ -2375,7 +1842,7 @@
         <v>3200</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O33" s="11">
         <v>31</v>
@@ -2390,10 +1857,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
@@ -2402,7 +1869,7 @@
         <v>3300</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O34" s="4">
         <v>32</v>
@@ -2417,10 +1884,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="4">
         <v>1</v>
@@ -2429,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O35" s="4">
         <v>33</v>
@@ -2444,10 +1911,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36" s="4">
         <v>2</v>
@@ -2461,10 +1928,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" s="4">
         <v>3</v>
@@ -2478,10 +1945,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -2496,10 +1963,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" s="4">
         <v>5</v>
@@ -2514,10 +1981,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="4">
         <v>6</v>
@@ -2532,10 +1999,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="4">
         <v>7</v>
@@ -2549,10 +2016,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" s="4">
         <v>8</v>
@@ -2566,10 +2033,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D43" s="4">
         <v>9</v>
@@ -2584,10 +2051,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" s="4">
         <v>10</v>
@@ -2602,10 +2069,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" s="4">
         <v>11</v>
@@ -2620,10 +2087,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" s="4">
         <v>12</v>
@@ -2637,10 +2104,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D47" s="4">
         <v>13</v>
@@ -2651,13 +2118,13 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D48" s="4">
         <v>1</v>
@@ -2672,10 +2139,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="4">
         <v>1</v>
@@ -2689,10 +2156,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="4">
         <v>2</v>
@@ -2706,10 +2173,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="4">
         <v>3</v>
@@ -2723,10 +2190,10 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="4">
         <v>1</v>
@@ -2740,10 +2207,10 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" s="4">
         <v>1</v>
@@ -2758,10 +2225,10 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D54" s="4">
         <v>1</v>
@@ -2775,10 +2242,10 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D55" s="4">
         <v>1</v>
@@ -2792,10 +2259,10 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D56" s="4">
         <v>2</v>
@@ -2809,10 +2276,10 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D57" s="4">
         <v>1</v>
@@ -2826,10 +2293,10 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D58" s="4">
         <v>2</v>
@@ -2843,10 +2310,10 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" s="4">
         <v>1</v>
@@ -2860,10 +2327,10 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" s="4">
         <v>1</v>
@@ -2877,10 +2344,10 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="4">
         <v>2</v>
@@ -2894,10 +2361,10 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D62" s="4">
         <v>2</v>
@@ -2911,10 +2378,10 @@
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63" s="4">
         <v>1</v>
@@ -2928,10 +2395,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D64" s="4">
         <v>2</v>
@@ -2945,10 +2412,10 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="4">
         <v>1</v>
@@ -2962,10 +2429,10 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D66" s="4">
         <v>2</v>
@@ -2977,13 +2444,13 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" s="16">
         <v>3</v>
@@ -2993,7 +2460,7 @@
       </c>
       <c r="F67" s="18"/>
       <c r="G67" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3001,10 +2468,10 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="4">
         <v>5</v>
@@ -3018,10 +2485,10 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" s="4">
         <v>3</v>
@@ -3035,10 +2502,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70" s="4">
         <v>2</v>
@@ -3052,10 +2519,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" s="4">
         <v>2</v>
@@ -3069,10 +2536,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" s="4">
         <v>2</v>
@@ -3086,10 +2553,10 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" s="4">
         <v>3</v>
@@ -3103,10 +2570,10 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="4">
         <v>2</v>
@@ -3120,10 +2587,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" s="4">
         <v>2</v>
@@ -3137,10 +2604,10 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" s="4">
         <v>3</v>
@@ -3154,10 +2621,10 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" s="4">
         <v>2</v>
@@ -3171,10 +2638,10 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" s="4">
         <v>2</v>
@@ -3188,10 +2655,10 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" s="4">
         <v>4</v>
@@ -3205,10 +2672,10 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="4">
         <v>2</v>
@@ -3222,10 +2689,10 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" s="4">
         <v>2</v>
@@ -3239,10 +2706,10 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" s="4">
         <v>4</v>
@@ -3256,10 +2723,10 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" s="4">
         <v>2</v>
@@ -3270,13 +2737,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" s="4">
         <v>2</v>
@@ -3290,10 +2757,10 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" s="4">
         <v>2</v>
@@ -3307,10 +2774,10 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" s="4">
         <v>3</v>
@@ -3324,10 +2791,10 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" s="4">
         <v>2</v>
@@ -3341,10 +2808,10 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" s="4">
         <v>4</v>
@@ -3358,10 +2825,10 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" s="4">
         <v>4</v>
@@ -3375,10 +2842,10 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" s="4">
         <v>4</v>
@@ -3392,10 +2859,10 @@
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" s="4">
         <v>2</v>
@@ -3409,10 +2876,10 @@
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D92" s="4">
         <v>0</v>
@@ -3423,13 +2890,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D93" s="4">
         <v>0</v>
@@ -3443,10 +2910,10 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D94" s="4">
         <v>0</v>
@@ -3460,10 +2927,10 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D95" s="4">
         <v>0</v>
@@ -3477,10 +2944,10 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D96" s="4">
         <v>0</v>
@@ -3494,10 +2961,10 @@
         <v>95</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D97" s="4">
         <v>0</v>
@@ -3511,10 +2978,10 @@
         <v>96</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D98" s="4">
         <v>0</v>
@@ -3528,10 +2995,10 @@
         <v>97</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D99" s="4">
         <v>0</v>
@@ -3545,10 +3012,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D100" s="4">
         <v>0</v>
@@ -3562,10 +3029,10 @@
         <v>99</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D101" s="4">
         <v>0</v>
@@ -3579,10 +3046,10 @@
         <v>100</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D102" s="4">
         <v>0</v>
@@ -3596,10 +3063,10 @@
         <v>101</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D103" s="4">
         <v>0</v>
@@ -3613,10 +3080,10 @@
         <v>102</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D104" s="4">
         <v>0</v>
@@ -3630,10 +3097,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D105" s="4">
         <v>0</v>
@@ -3647,10 +3114,10 @@
         <v>104</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D106" s="4">
         <v>0</v>
@@ -3664,10 +3131,10 @@
         <v>105</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D107" s="4">
         <v>0</v>
@@ -3681,10 +3148,10 @@
         <v>106</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D108" s="4">
         <v>0</v>
@@ -3698,10 +3165,10 @@
         <v>107</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D109" s="4">
         <v>0</v>
@@ -3715,10 +3182,10 @@
         <v>108</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D110" s="4">
         <v>0</v>
@@ -3732,10 +3199,10 @@
         <v>109</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D111" s="4">
         <v>0</v>
@@ -3749,10 +3216,10 @@
         <v>110</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D112" s="4">
         <v>0</v>
@@ -3766,10 +3233,10 @@
         <v>111</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D113" s="4">
         <v>0</v>
@@ -3792,20 +3259,20 @@
     <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>$N$5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
-      <formula>$J$1</formula>
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>$N$21</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>$N$23</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>$N$25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>$N$21</formula>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>$N$28</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>$N$23</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>$N$28</formula>
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="equal">
+      <formula>$J$1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">

--- a/Assets/AddressableResource/Data/Excels/CardData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E76F827-6BEC-41D4-95F2-63C270A26A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881C999A-048D-416A-BA01-8B075E8F0526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="54">
   <si>
     <t>Normal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,14 +196,27 @@
     <t>Silver</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>3주년</t>
+    <t>2주년</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2주년</t>
+    <t>3주년(멍개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈퍼레어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블랙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적당히 넣을것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -760,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B2, $M:$M, $N:$N), "00") &amp; TEXT(E2, "00"))</f>
+        <f t="shared" ref="D2:D33" si="0">VALUE(TEXT(_xlfn.XLOOKUP(B2, $M:$M, $N:$N), "00") &amp; TEXT(E2, "00"))</f>
         <v>100</v>
       </c>
       <c r="E2" s="10">
@@ -770,8 +783,8 @@
       <c r="F2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" s="2">
-        <f>COUNTIF(C:C,L2)</f>
-        <v>49</v>
+        <f t="shared" ref="K2:K7" si="1">COUNTIF(C:C,L2)</f>
+        <v>75</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>31</v>
@@ -783,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <f>COUNTIF(B:B,M2)</f>
+        <f t="shared" ref="O2:O28" si="2">COUNTIF(B:B,M2)</f>
         <v>2</v>
       </c>
     </row>
@@ -799,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B3, $M:$M, $N:$N), "00") &amp; TEXT(E3, "00"))</f>
+        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="E3" s="10">
@@ -809,7 +822,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
       <c r="K3" s="2">
-        <f>COUNTIF(C:C,L3)</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -822,13 +835,13 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <f>COUNTIF(B:B,M3)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <f t="shared" ref="A4:A67" si="3">A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -838,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B4, $M:$M, $N:$N), "00") &amp; TEXT(E4, "00"))</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
       <c r="E4" s="10">
@@ -847,7 +860,7 @@
       </c>
       <c r="F4" s="1"/>
       <c r="K4" s="2">
-        <f>COUNTIF(C:C,L4)</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="L4" s="2" t="s">
@@ -860,13 +873,13 @@
         <v>2</v>
       </c>
       <c r="O4" s="5">
-        <f>COUNTIF(B:B,M4)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -876,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B5, $M:$M, $N:$N), "00") &amp; TEXT(E5, "00"))</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
       <c r="E5" s="10">
@@ -885,7 +898,7 @@
       </c>
       <c r="F5" s="1"/>
       <c r="K5" s="2">
-        <f>COUNTIF(C:C,L5)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="L5" s="1" t="s">
@@ -898,13 +911,13 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <f>COUNTIF(B:B,M5)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -914,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B6, $M:$M, $N:$N), "00") &amp; TEXT(E6, "00"))</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="E6" s="10">
@@ -923,8 +936,8 @@
       </c>
       <c r="F6" s="1"/>
       <c r="K6" s="2">
-        <f>COUNTIF(C:C,L6)</f>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>35</v>
@@ -936,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="O6" s="5">
-        <f>COUNTIF(B:B,M6)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -952,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B7, $M:$M, $N:$N), "00") &amp; TEXT(E7, "00"))</f>
+        <f t="shared" si="0"/>
         <v>600</v>
       </c>
       <c r="E7" s="10">
@@ -961,7 +974,7 @@
       </c>
       <c r="F7" s="1"/>
       <c r="K7" s="2">
-        <f>COUNTIF(C:C,L7)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
@@ -974,13 +987,13 @@
         <v>5</v>
       </c>
       <c r="O7" s="5">
-        <f>COUNTIF(B:B,M7)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -990,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B8, $M:$M, $N:$N), "00") &amp; TEXT(E8, "00"))</f>
+        <f t="shared" si="0"/>
         <v>700</v>
       </c>
       <c r="E8" s="10">
@@ -1004,13 +1017,13 @@
         <v>6</v>
       </c>
       <c r="O8" s="5">
-        <f>COUNTIF(B:B,M8)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1020,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B9, $M:$M, $N:$N), "00") &amp; TEXT(E9, "00"))</f>
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="E9" s="10">
@@ -1034,13 +1047,13 @@
         <v>7</v>
       </c>
       <c r="O9" s="5">
-        <f>COUNTIF(B:B,M9)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1050,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B10, $M:$M, $N:$N), "00") &amp; TEXT(E10, "00"))</f>
+        <f t="shared" si="0"/>
         <v>900</v>
       </c>
       <c r="E10" s="10">
@@ -1064,13 +1077,13 @@
         <v>8</v>
       </c>
       <c r="O10" s="5">
-        <f>COUNTIF(B:B,M10)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1080,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B11, $M:$M, $N:$N), "00") &amp; TEXT(E11, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="E11" s="10">
@@ -1094,13 +1107,13 @@
         <v>9</v>
       </c>
       <c r="O11" s="5">
-        <f>COUNTIF(B:B,M11)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1110,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B12, $M:$M, $N:$N), "00") &amp; TEXT(E12, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="E12" s="10">
@@ -1124,13 +1137,13 @@
         <v>10</v>
       </c>
       <c r="O12" s="5">
-        <f>COUNTIF(B:B,M12)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1140,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B13, $M:$M, $N:$N), "00") &amp; TEXT(E13, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="E13" s="10">
@@ -1154,13 +1167,13 @@
         <v>11</v>
       </c>
       <c r="O13" s="5">
-        <f>COUNTIF(B:B,M13)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1170,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B14, $M:$M, $N:$N), "00") &amp; TEXT(E14, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1300</v>
       </c>
       <c r="E14" s="10">
@@ -1184,13 +1197,13 @@
         <v>12</v>
       </c>
       <c r="O14" s="5">
-        <f>COUNTIF(B:B,M14)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1200,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B15, $M:$M, $N:$N), "00") &amp; TEXT(E15, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1400</v>
       </c>
       <c r="E15" s="10">
@@ -1214,13 +1227,13 @@
         <v>13</v>
       </c>
       <c r="O15" s="5">
-        <f>COUNTIF(B:B,M15)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1230,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B16, $M:$M, $N:$N), "00") &amp; TEXT(E16, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="E16" s="10">
@@ -1244,13 +1257,13 @@
         <v>14</v>
       </c>
       <c r="O16" s="8">
-        <f>COUNTIF(B:B,M16)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1260,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B17, $M:$M, $N:$N), "00") &amp; TEXT(E17, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="E17" s="10">
@@ -1274,13 +1287,13 @@
         <v>15</v>
       </c>
       <c r="O17" s="5">
-        <f>COUNTIF(B:B,M17)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1290,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B18, $M:$M, $N:$N), "00") &amp; TEXT(E18, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1700</v>
       </c>
       <c r="E18" s="10">
@@ -1304,13 +1317,13 @@
         <v>16</v>
       </c>
       <c r="O18" s="5">
-        <f>COUNTIF(B:B,M18)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1320,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B19, $M:$M, $N:$N), "00") &amp; TEXT(E19, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1800</v>
       </c>
       <c r="E19" s="10">
@@ -1334,13 +1347,13 @@
         <v>17</v>
       </c>
       <c r="O19" s="5">
-        <f>COUNTIF(B:B,M19)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1350,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B20, $M:$M, $N:$N), "00") &amp; TEXT(E20, "00"))</f>
+        <f t="shared" si="0"/>
         <v>1900</v>
       </c>
       <c r="E20" s="10">
@@ -1364,13 +1377,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="5">
-        <f>COUNTIF(B:B,M20)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1380,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B21, $M:$M, $N:$N), "00") &amp; TEXT(E21, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
       <c r="E21" s="10">
@@ -1394,13 +1407,13 @@
         <v>19</v>
       </c>
       <c r="O21" s="5">
-        <f>COUNTIF(B:B,M21)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1410,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B22, $M:$M, $N:$N), "00") &amp; TEXT(E22, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2100</v>
       </c>
       <c r="E22" s="10">
@@ -1424,13 +1437,13 @@
         <v>20</v>
       </c>
       <c r="O22" s="5">
-        <f>COUNTIF(B:B,M22)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1440,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B23, $M:$M, $N:$N), "00") &amp; TEXT(E23, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2200</v>
       </c>
       <c r="E23" s="10">
@@ -1454,13 +1467,13 @@
         <v>21</v>
       </c>
       <c r="O23" s="5">
-        <f>COUNTIF(B:B,M23)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1470,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B24, $M:$M, $N:$N), "00") &amp; TEXT(E24, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2300</v>
       </c>
       <c r="E24" s="10">
@@ -1484,13 +1497,13 @@
         <v>22</v>
       </c>
       <c r="O24" s="5">
-        <f>COUNTIF(B:B,M24)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1500,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B25, $M:$M, $N:$N), "00") &amp; TEXT(E25, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="E25" s="10">
@@ -1514,13 +1527,13 @@
         <v>23</v>
       </c>
       <c r="O25" s="5">
-        <f>COUNTIF(B:B,M25)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1530,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B26, $M:$M, $N:$N), "00") &amp; TEXT(E26, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2500</v>
       </c>
       <c r="E26" s="10">
@@ -1544,13 +1557,13 @@
         <v>24</v>
       </c>
       <c r="O26" s="5">
-        <f>COUNTIF(B:B,M26)</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1560,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B27, $M:$M, $N:$N), "00") &amp; TEXT(E27, "00"))</f>
+        <f t="shared" si="0"/>
         <v>2600</v>
       </c>
       <c r="E27" s="10">
@@ -1574,13 +1587,13 @@
         <v>25</v>
       </c>
       <c r="O27" s="5">
-        <f>COUNTIF(B:B,M27)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1590,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B28, $M:$M, $N:$N), "00") &amp; TEXT(E28, "00"))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E28" s="10">
@@ -1604,13 +1617,13 @@
         <v>26</v>
       </c>
       <c r="O28" s="5">
-        <f>COUNTIF(B:B,M28)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1620,7 +1633,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B29, $M:$M, $N:$N), "00") &amp; TEXT(E29, "00"))</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="E29" s="10">
@@ -1630,7 +1643,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1640,7 +1653,7 @@
         <v>32</v>
       </c>
       <c r="D30" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B30, $M:$M, $N:$N), "00") &amp; TEXT(E30, "00"))</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="E30" s="10">
@@ -1650,7 +1663,7 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1660,7 +1673,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B31, $M:$M, $N:$N), "00") &amp; TEXT(E31, "00"))</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="E31" s="10">
@@ -1670,7 +1683,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1680,7 +1693,7 @@
         <v>2</v>
       </c>
       <c r="D32" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B32, $M:$M, $N:$N), "00") &amp; TEXT(E32, "00"))</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="E32" s="10">
@@ -1690,7 +1703,7 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1700,7 +1713,7 @@
         <v>33</v>
       </c>
       <c r="D33" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B33, $M:$M, $N:$N), "00") &amp; TEXT(E33, "00"))</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="E33" s="10">
@@ -1710,7 +1723,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1720,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B34, $M:$M, $N:$N), "00") &amp; TEXT(E34, "00"))</f>
+        <f t="shared" ref="D34:D65" si="4">VALUE(TEXT(_xlfn.XLOOKUP(B34, $M:$M, $N:$N), "00") &amp; TEXT(E34, "00"))</f>
         <v>106</v>
       </c>
       <c r="E34" s="10">
@@ -1730,7 +1743,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1740,7 +1753,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B35, $M:$M, $N:$N), "00") &amp; TEXT(E35, "00"))</f>
+        <f t="shared" si="4"/>
         <v>107</v>
       </c>
       <c r="E35" s="10">
@@ -1750,7 +1763,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1760,7 +1773,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B36, $M:$M, $N:$N), "00") &amp; TEXT(E36, "00"))</f>
+        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="E36" s="10">
@@ -1770,7 +1783,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -1780,7 +1793,7 @@
         <v>35</v>
       </c>
       <c r="D37" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B37, $M:$M, $N:$N), "00") &amp; TEXT(E37, "00"))</f>
+        <f t="shared" si="4"/>
         <v>109</v>
       </c>
       <c r="E37" s="10">
@@ -1790,7 +1803,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1800,7 +1813,7 @@
         <v>35</v>
       </c>
       <c r="D38" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B38, $M:$M, $N:$N), "00") &amp; TEXT(E38, "00"))</f>
+        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="E38" s="10">
@@ -1811,7 +1824,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -1821,7 +1834,7 @@
         <v>36</v>
       </c>
       <c r="D39" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B39, $M:$M, $N:$N), "00") &amp; TEXT(E39, "00"))</f>
+        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="E39" s="10">
@@ -1832,7 +1845,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -1842,7 +1855,7 @@
         <v>36</v>
       </c>
       <c r="D40" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B40, $M:$M, $N:$N), "00") &amp; TEXT(E40, "00"))</f>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="E40" s="10">
@@ -1853,7 +1866,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -1863,7 +1876,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B41, $M:$M, $N:$N), "00") &amp; TEXT(E41, "00"))</f>
+        <f t="shared" si="4"/>
         <v>301</v>
       </c>
       <c r="E41" s="10">
@@ -1873,7 +1886,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -1883,7 +1896,7 @@
         <v>2</v>
       </c>
       <c r="D42" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B42, $M:$M, $N:$N), "00") &amp; TEXT(E42, "00"))</f>
+        <f t="shared" si="4"/>
         <v>302</v>
       </c>
       <c r="E42" s="10">
@@ -1893,7 +1906,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -1903,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B43, $M:$M, $N:$N), "00") &amp; TEXT(E43, "00"))</f>
+        <f t="shared" si="4"/>
         <v>303</v>
       </c>
       <c r="E43" s="10">
@@ -1913,7 +1926,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -1923,7 +1936,7 @@
         <v>2</v>
       </c>
       <c r="D44" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B44, $M:$M, $N:$N), "00") &amp; TEXT(E44, "00"))</f>
+        <f t="shared" si="4"/>
         <v>401</v>
       </c>
       <c r="E44" s="10">
@@ -1933,7 +1946,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -1943,7 +1956,7 @@
         <v>2</v>
       </c>
       <c r="D45" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B45, $M:$M, $N:$N), "00") &amp; TEXT(E45, "00"))</f>
+        <f t="shared" si="4"/>
         <v>801</v>
       </c>
       <c r="E45" s="10">
@@ -1953,7 +1966,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -1963,7 +1976,7 @@
         <v>36</v>
       </c>
       <c r="D46" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B46, $M:$M, $N:$N), "00") &amp; TEXT(E46, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1001</v>
       </c>
       <c r="E46" s="10">
@@ -1973,7 +1986,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1983,7 +1996,7 @@
         <v>34</v>
       </c>
       <c r="D47" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B47, $M:$M, $N:$N), "00") &amp; TEXT(E47, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1301</v>
       </c>
       <c r="E47" s="10">
@@ -1993,7 +2006,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2003,7 +2016,7 @@
         <v>35</v>
       </c>
       <c r="D48" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B48, $M:$M, $N:$N), "00") &amp; TEXT(E48, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1302</v>
       </c>
       <c r="E48" s="10">
@@ -2014,7 +2027,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2024,7 +2037,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B49, $M:$M, $N:$N), "00") &amp; TEXT(E49, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1601</v>
       </c>
       <c r="E49" s="10">
@@ -2034,7 +2047,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2044,7 +2057,7 @@
         <v>36</v>
       </c>
       <c r="D50" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B50, $M:$M, $N:$N), "00") &amp; TEXT(E50, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1602</v>
       </c>
       <c r="E50" s="10">
@@ -2054,7 +2067,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2064,7 +2077,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B51, $M:$M, $N:$N), "00") &amp; TEXT(E51, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1901</v>
       </c>
       <c r="E51" s="10">
@@ -2074,7 +2087,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2084,7 +2097,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B52, $M:$M, $N:$N), "00") &amp; TEXT(E52, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2201</v>
       </c>
       <c r="E52" s="10">
@@ -2094,7 +2107,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2104,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B53, $M:$M, $N:$N), "00") &amp; TEXT(E53, "00"))</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E53" s="10">
@@ -2115,7 +2128,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2125,7 +2138,7 @@
         <v>34</v>
       </c>
       <c r="D54" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B54, $M:$M, $N:$N), "00") &amp; TEXT(E54, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2202</v>
       </c>
       <c r="E54" s="10">
@@ -2135,7 +2148,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2145,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="D55" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B55, $M:$M, $N:$N), "00") &amp; TEXT(E55, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2301</v>
       </c>
       <c r="E55" s="10">
@@ -2155,7 +2168,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2165,7 +2178,7 @@
         <v>34</v>
       </c>
       <c r="D56" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B56, $M:$M, $N:$N), "00") &amp; TEXT(E56, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2302</v>
       </c>
       <c r="E56" s="10">
@@ -2175,7 +2188,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2185,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B57, $M:$M, $N:$N), "00") &amp; TEXT(E57, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2401</v>
       </c>
       <c r="E57" s="10">
@@ -2195,7 +2208,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -2205,7 +2218,7 @@
         <v>35</v>
       </c>
       <c r="D58" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B58, $M:$M, $N:$N), "00") &amp; TEXT(E58, "00"))</f>
+        <f t="shared" si="4"/>
         <v>2402</v>
       </c>
       <c r="E58" s="10">
@@ -2215,7 +2228,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2225,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B59, $M:$M, $N:$N), "00") &amp; TEXT(E59, "00"))</f>
+        <f t="shared" si="4"/>
         <v>304</v>
       </c>
       <c r="E59" s="10">
@@ -2235,7 +2248,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -2245,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B60, $M:$M, $N:$N), "00") &amp; TEXT(E60, "00"))</f>
+        <f t="shared" si="4"/>
         <v>402</v>
       </c>
       <c r="E60" s="10">
@@ -2255,7 +2268,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -2265,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B61, $M:$M, $N:$N), "00") &amp; TEXT(E61, "00"))</f>
+        <f t="shared" si="4"/>
         <v>501</v>
       </c>
       <c r="E61" s="10">
@@ -2275,7 +2288,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -2285,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B62, $M:$M, $N:$N), "00") &amp; TEXT(E62, "00"))</f>
+        <f t="shared" si="4"/>
         <v>601</v>
       </c>
       <c r="E62" s="10">
@@ -2295,7 +2308,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -2305,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B63, $M:$M, $N:$N), "00") &amp; TEXT(E63, "00"))</f>
+        <f t="shared" si="4"/>
         <v>701</v>
       </c>
       <c r="E63" s="10">
@@ -2315,7 +2328,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2325,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B64, $M:$M, $N:$N), "00") &amp; TEXT(E64, "00"))</f>
+        <f t="shared" si="4"/>
         <v>802</v>
       </c>
       <c r="E64" s="10">
@@ -2335,7 +2348,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -2345,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B65, $M:$M, $N:$N), "00") &amp; TEXT(E65, "00"))</f>
+        <f t="shared" si="4"/>
         <v>901</v>
       </c>
       <c r="E65" s="10">
@@ -2355,7 +2368,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -2365,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B66, $M:$M, $N:$N), "00") &amp; TEXT(E66, "00"))</f>
+        <f t="shared" ref="D66:D97" si="5">VALUE(TEXT(_xlfn.XLOOKUP(B66, $M:$M, $N:$N), "00") &amp; TEXT(E66, "00"))</f>
         <v>1002</v>
       </c>
       <c r="E66" s="10">
@@ -2375,7 +2388,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -2385,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B67, $M:$M, $N:$N), "00") &amp; TEXT(E67, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1101</v>
       </c>
       <c r="E67" s="10">
@@ -2395,7 +2408,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1">
-        <f t="shared" ref="A68:A132" si="1">A67+1</f>
+        <f t="shared" ref="A68:A132" si="6">A67+1</f>
         <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -2405,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B68, $M:$M, $N:$N), "00") &amp; TEXT(E68, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1201</v>
       </c>
       <c r="E68" s="10">
@@ -2415,7 +2428,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -2425,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B69, $M:$M, $N:$N), "00") &amp; TEXT(E69, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1303</v>
       </c>
       <c r="E69" s="10">
@@ -2435,7 +2448,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -2445,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B70, $M:$M, $N:$N), "00") &amp; TEXT(E70, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1401</v>
       </c>
       <c r="E70" s="10">
@@ -2455,7 +2468,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -2465,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B71, $M:$M, $N:$N), "00") &amp; TEXT(E71, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1501</v>
       </c>
       <c r="E71" s="10">
@@ -2475,7 +2488,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -2485,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B72, $M:$M, $N:$N), "00") &amp; TEXT(E72, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1603</v>
       </c>
       <c r="E72" s="10">
@@ -2495,7 +2508,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -2505,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B73, $M:$M, $N:$N), "00") &amp; TEXT(E73, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1701</v>
       </c>
       <c r="E73" s="10">
@@ -2515,7 +2528,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -2525,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B74, $M:$M, $N:$N), "00") &amp; TEXT(E74, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1801</v>
       </c>
       <c r="E74" s="10">
@@ -2535,7 +2548,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -2545,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B75, $M:$M, $N:$N), "00") &amp; TEXT(E75, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1902</v>
       </c>
       <c r="E75" s="10">
@@ -2555,7 +2568,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -2565,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B76, $M:$M, $N:$N), "00") &amp; TEXT(E76, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2101</v>
       </c>
       <c r="E76" s="10">
@@ -2575,7 +2588,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -2585,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B77, $M:$M, $N:$N), "00") &amp; TEXT(E77, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2203</v>
       </c>
       <c r="E77" s="10">
@@ -2595,7 +2608,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -2605,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B78, $M:$M, $N:$N), "00") &amp; TEXT(E78, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2303</v>
       </c>
       <c r="E78" s="10">
@@ -2615,7 +2628,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -2625,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B79, $M:$M, $N:$N), "00") &amp; TEXT(E79, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2403</v>
       </c>
       <c r="E79" s="10">
@@ -2635,7 +2648,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -2645,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B80, $M:$M, $N:$N), "00") &amp; TEXT(E80, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2601</v>
       </c>
       <c r="E80" s="10">
@@ -2655,7 +2668,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -2665,7 +2678,7 @@
         <v>32</v>
       </c>
       <c r="D81" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B81, $M:$M, $N:$N), "00") &amp; TEXT(E81, "00"))</f>
+        <f t="shared" si="5"/>
         <v>201</v>
       </c>
       <c r="E81" s="10">
@@ -2675,7 +2688,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -2685,7 +2698,7 @@
         <v>32</v>
       </c>
       <c r="D82" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B82, $M:$M, $N:$N), "00") &amp; TEXT(E82, "00"))</f>
+        <f t="shared" si="5"/>
         <v>502</v>
       </c>
       <c r="E82" s="10">
@@ -2695,7 +2708,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -2705,7 +2718,7 @@
         <v>32</v>
       </c>
       <c r="D83" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B83, $M:$M, $N:$N), "00") &amp; TEXT(E83, "00"))</f>
+        <f t="shared" si="5"/>
         <v>803</v>
       </c>
       <c r="E83" s="10">
@@ -2715,7 +2728,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -2725,7 +2738,7 @@
         <v>32</v>
       </c>
       <c r="D84" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B84, $M:$M, $N:$N), "00") &amp; TEXT(E84, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1003</v>
       </c>
       <c r="E84" s="10">
@@ -2735,7 +2748,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -2745,7 +2758,7 @@
         <v>32</v>
       </c>
       <c r="D85" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B85, $M:$M, $N:$N), "00") &amp; TEXT(E85, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1202</v>
       </c>
       <c r="E85" s="10">
@@ -2755,7 +2768,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -2765,7 +2778,7 @@
         <v>32</v>
       </c>
       <c r="D86" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B86, $M:$M, $N:$N), "00") &amp; TEXT(E86, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1304</v>
       </c>
       <c r="E86" s="10">
@@ -2775,7 +2788,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>85</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -2785,7 +2798,7 @@
         <v>32</v>
       </c>
       <c r="D87" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B87, $M:$M, $N:$N), "00") &amp; TEXT(E87, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1402</v>
       </c>
       <c r="E87" s="10">
@@ -2795,7 +2808,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>86</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -2805,7 +2818,7 @@
         <v>32</v>
       </c>
       <c r="D88" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B88, $M:$M, $N:$N), "00") &amp; TEXT(E88, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1502</v>
       </c>
       <c r="E88" s="10">
@@ -2815,7 +2828,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -2825,7 +2838,7 @@
         <v>32</v>
       </c>
       <c r="D89" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B89, $M:$M, $N:$N), "00") &amp; TEXT(E89, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1503</v>
       </c>
       <c r="E89" s="10">
@@ -2835,7 +2848,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>88</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -2845,7 +2858,7 @@
         <v>32</v>
       </c>
       <c r="D90" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B90, $M:$M, $N:$N), "00") &amp; TEXT(E90, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1504</v>
       </c>
       <c r="E90" s="10">
@@ -2855,7 +2868,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>89</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -2865,7 +2878,7 @@
         <v>32</v>
       </c>
       <c r="D91" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B91, $M:$M, $N:$N), "00") &amp; TEXT(E91, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1604</v>
       </c>
       <c r="E91" s="10">
@@ -2875,7 +2888,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -2885,7 +2898,7 @@
         <v>32</v>
       </c>
       <c r="D92" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B92, $M:$M, $N:$N), "00") &amp; TEXT(E92, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2102</v>
       </c>
       <c r="E92" s="10">
@@ -2895,7 +2908,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>91</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -2905,7 +2918,7 @@
         <v>32</v>
       </c>
       <c r="D93" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B93, $M:$M, $N:$N), "00") &amp; TEXT(E93, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2204</v>
       </c>
       <c r="E93" s="10">
@@ -2915,7 +2928,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>92</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -2925,7 +2938,7 @@
         <v>32</v>
       </c>
       <c r="D94" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B94, $M:$M, $N:$N), "00") &amp; TEXT(E94, "00"))</f>
+        <f t="shared" si="5"/>
         <v>2404</v>
       </c>
       <c r="E94" s="10">
@@ -2935,7 +2948,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>93</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -2945,7 +2958,7 @@
         <v>33</v>
       </c>
       <c r="D95" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B95, $M:$M, $N:$N), "00") &amp; TEXT(E95, "00"))</f>
+        <f t="shared" si="5"/>
         <v>305</v>
       </c>
       <c r="E95" s="10">
@@ -2955,7 +2968,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>94</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -2965,7 +2978,7 @@
         <v>33</v>
       </c>
       <c r="D96" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B96, $M:$M, $N:$N), "00") &amp; TEXT(E96, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1505</v>
       </c>
       <c r="E96" s="10">
@@ -2975,7 +2988,7 @@
     </row>
     <row r="97" spans="1:17">
       <c r="A97" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -2985,7 +2998,7 @@
         <v>33</v>
       </c>
       <c r="D97" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B97, $M:$M, $N:$N), "00") &amp; TEXT(E97, "00"))</f>
+        <f t="shared" si="5"/>
         <v>1702</v>
       </c>
       <c r="E97" s="10">
@@ -2995,7 +3008,7 @@
     </row>
     <row r="98" spans="1:17">
       <c r="A98" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -3005,7 +3018,7 @@
         <v>33</v>
       </c>
       <c r="D98" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B98, $M:$M, $N:$N), "00") &amp; TEXT(E98, "00"))</f>
+        <f t="shared" ref="D98:D129" si="7">VALUE(TEXT(_xlfn.XLOOKUP(B98, $M:$M, $N:$N), "00") &amp; TEXT(E98, "00"))</f>
         <v>2103</v>
       </c>
       <c r="E98" s="10">
@@ -3015,7 +3028,7 @@
     </row>
     <row r="99" spans="1:17">
       <c r="A99" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -3025,7 +3038,7 @@
         <v>33</v>
       </c>
       <c r="D99" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B99, $M:$M, $N:$N), "00") &amp; TEXT(E99, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2205</v>
       </c>
       <c r="E99" s="10">
@@ -3035,7 +3048,7 @@
     </row>
     <row r="100" spans="1:17">
       <c r="A100" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -3045,7 +3058,7 @@
         <v>33</v>
       </c>
       <c r="D100" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B100, $M:$M, $N:$N), "00") &amp; TEXT(E100, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2304</v>
       </c>
       <c r="E100" s="10">
@@ -3055,7 +3068,7 @@
     </row>
     <row r="101" spans="1:17">
       <c r="A101" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>99</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -3065,7 +3078,7 @@
         <v>33</v>
       </c>
       <c r="D101" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B101, $M:$M, $N:$N), "00") &amp; TEXT(E101, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2501</v>
       </c>
       <c r="E101" s="10">
@@ -3075,17 +3088,17 @@
     </row>
     <row r="102" spans="1:17" s="17" customFormat="1">
       <c r="A102" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D102" s="17">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B102, $M:$M, $N:$N), "00") &amp; TEXT(E102, "00"))</f>
+        <f t="shared" si="7"/>
         <v>804</v>
       </c>
       <c r="E102" s="18">
@@ -3101,17 +3114,17 @@
     </row>
     <row r="103" spans="1:17">
       <c r="A103" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D103" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B103, $M:$M, $N:$N), "00") &amp; TEXT(E103, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1802</v>
       </c>
       <c r="E103" s="10">
@@ -3121,17 +3134,17 @@
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D104" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B104, $M:$M, $N:$N), "00") &amp; TEXT(E104, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1102</v>
       </c>
       <c r="E104" s="10">
@@ -3141,17 +3154,17 @@
     </row>
     <row r="105" spans="1:17">
       <c r="A105" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D105" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B105, $M:$M, $N:$N), "00") &amp; TEXT(E105, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2206</v>
       </c>
       <c r="E105" s="10">
@@ -3161,17 +3174,17 @@
     </row>
     <row r="106" spans="1:17">
       <c r="A106" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D106" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B106, $M:$M, $N:$N), "00") &amp; TEXT(E106, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1203</v>
       </c>
       <c r="E106" s="10">
@@ -3181,17 +3194,17 @@
     </row>
     <row r="107" spans="1:17">
       <c r="A107" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D107" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B107, $M:$M, $N:$N), "00") &amp; TEXT(E107, "00"))</f>
+        <f t="shared" si="7"/>
         <v>113</v>
       </c>
       <c r="E107" s="10">
@@ -3201,17 +3214,17 @@
     </row>
     <row r="108" spans="1:17">
       <c r="A108" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>106</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D108" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B108, $M:$M, $N:$N), "00") &amp; TEXT(E108, "00"))</f>
+        <f t="shared" si="7"/>
         <v>702</v>
       </c>
       <c r="E108" s="10">
@@ -3221,17 +3234,17 @@
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D109" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B109, $M:$M, $N:$N), "00") &amp; TEXT(E109, "00"))</f>
+        <f t="shared" si="7"/>
         <v>503</v>
       </c>
       <c r="E109" s="10">
@@ -3241,17 +3254,17 @@
     </row>
     <row r="110" spans="1:17">
       <c r="A110" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>108</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D110" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B110, $M:$M, $N:$N), "00") &amp; TEXT(E110, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2602</v>
       </c>
       <c r="E110" s="10">
@@ -3261,17 +3274,17 @@
     </row>
     <row r="111" spans="1:17">
       <c r="A111" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>109</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D111" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B111, $M:$M, $N:$N), "00") &amp; TEXT(E111, "00"))</f>
+        <f t="shared" si="7"/>
         <v>306</v>
       </c>
       <c r="E111" s="10">
@@ -3281,17 +3294,17 @@
     </row>
     <row r="112" spans="1:17">
       <c r="A112" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D112" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B112, $M:$M, $N:$N), "00") &amp; TEXT(E112, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2405</v>
       </c>
       <c r="E112" s="10">
@@ -3301,17 +3314,17 @@
     </row>
     <row r="113" spans="1:17">
       <c r="A113" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D113" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B113, $M:$M, $N:$N), "00") &amp; TEXT(E113, "00"))</f>
+        <f t="shared" si="7"/>
         <v>902</v>
       </c>
       <c r="E113" s="10">
@@ -3321,17 +3334,17 @@
     </row>
     <row r="114" spans="1:17">
       <c r="A114" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D114" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B114, $M:$M, $N:$N), "00") &amp; TEXT(E114, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1605</v>
       </c>
       <c r="E114" s="10">
@@ -3341,17 +3354,17 @@
     </row>
     <row r="115" spans="1:17">
       <c r="A115" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D115" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B115, $M:$M, $N:$N), "00") &amp; TEXT(E115, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2502</v>
       </c>
       <c r="E115" s="10">
@@ -3361,17 +3374,17 @@
     </row>
     <row r="116" spans="1:17">
       <c r="A116" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>114</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D116" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B116, $M:$M, $N:$N), "00") &amp; TEXT(E116, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2104</v>
       </c>
       <c r="E116" s="10">
@@ -3381,17 +3394,17 @@
     </row>
     <row r="117" spans="1:17">
       <c r="A117" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>115</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D117" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B117, $M:$M, $N:$N), "00") &amp; TEXT(E117, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2305</v>
       </c>
       <c r="E117" s="10">
@@ -3401,17 +3414,17 @@
     </row>
     <row r="118" spans="1:17">
       <c r="A118" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D118" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B118, $M:$M, $N:$N), "00") &amp; TEXT(E118, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1004</v>
       </c>
       <c r="E118" s="10">
@@ -3421,17 +3434,17 @@
     </row>
     <row r="119" spans="1:17">
       <c r="A119" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>117</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D119" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B119, $M:$M, $N:$N), "00") &amp; TEXT(E119, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1703</v>
       </c>
       <c r="E119" s="10">
@@ -3441,17 +3454,17 @@
     </row>
     <row r="120" spans="1:17">
       <c r="A120" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>118</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D120" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B120, $M:$M, $N:$N), "00") &amp; TEXT(E120, "00"))</f>
+        <f t="shared" si="7"/>
         <v>202</v>
       </c>
       <c r="E120" s="10">
@@ -3461,17 +3474,17 @@
     </row>
     <row r="121" spans="1:17">
       <c r="A121" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>119</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D121" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B121, $M:$M, $N:$N), "00") &amp; TEXT(E121, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1506</v>
       </c>
       <c r="E121" s="10">
@@ -3481,17 +3494,17 @@
     </row>
     <row r="122" spans="1:17">
       <c r="A122" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>120</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D122" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B122, $M:$M, $N:$N), "00") &amp; TEXT(E122, "00"))</f>
+        <f t="shared" si="7"/>
         <v>2001</v>
       </c>
       <c r="E122" s="10">
@@ -3501,17 +3514,17 @@
     </row>
     <row r="123" spans="1:17">
       <c r="A123" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>121</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D123" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B123, $M:$M, $N:$N), "00") &amp; TEXT(E123, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1403</v>
       </c>
       <c r="E123" s="10">
@@ -3521,17 +3534,17 @@
     </row>
     <row r="124" spans="1:17">
       <c r="A124" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>122</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D124" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B124, $M:$M, $N:$N), "00") &amp; TEXT(E124, "00"))</f>
+        <f t="shared" si="7"/>
         <v>403</v>
       </c>
       <c r="E124" s="10">
@@ -3541,17 +3554,17 @@
     </row>
     <row r="125" spans="1:17">
       <c r="A125" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>123</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D125" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B125, $M:$M, $N:$N), "00") &amp; TEXT(E125, "00"))</f>
+        <f t="shared" si="7"/>
         <v>602</v>
       </c>
       <c r="E125" s="10">
@@ -3561,17 +3574,17 @@
     </row>
     <row r="126" spans="1:17">
       <c r="A126" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>124</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D126" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B126, $M:$M, $N:$N), "00") &amp; TEXT(E126, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1305</v>
       </c>
       <c r="E126" s="10">
@@ -3581,17 +3594,17 @@
     </row>
     <row r="127" spans="1:17">
       <c r="A127" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D127" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B127, $M:$M, $N:$N), "00") &amp; TEXT(E127, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1903</v>
       </c>
       <c r="E127" s="10">
@@ -3601,17 +3614,17 @@
     </row>
     <row r="128" spans="1:17" s="12" customFormat="1">
       <c r="A128" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>126</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D128" s="12">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B128, $M:$M, $N:$N), "00") &amp; TEXT(E128, "00"))</f>
+        <f t="shared" si="7"/>
         <v>805</v>
       </c>
       <c r="E128" s="13">
@@ -3619,7 +3632,7 @@
         <v>5</v>
       </c>
       <c r="G128" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O128" s="14"/>
       <c r="P128" s="15"/>
@@ -3627,17 +3640,17 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>127</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D129" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B129, $M:$M, $N:$N), "00") &amp; TEXT(E129, "00"))</f>
+        <f t="shared" si="7"/>
         <v>1803</v>
       </c>
       <c r="E129" s="10">
@@ -3647,17 +3660,17 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>128</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D130" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B130, $M:$M, $N:$N), "00") &amp; TEXT(E130, "00"))</f>
+        <f t="shared" ref="D130:D161" si="8">VALUE(TEXT(_xlfn.XLOOKUP(B130, $M:$M, $N:$N), "00") &amp; TEXT(E130, "00"))</f>
         <v>1103</v>
       </c>
       <c r="E130" s="10">
@@ -3667,17 +3680,17 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>129</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D131" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B131, $M:$M, $N:$N), "00") &amp; TEXT(E131, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2207</v>
       </c>
       <c r="E131" s="10">
@@ -3687,17 +3700,17 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>130</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D132" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B132, $M:$M, $N:$N), "00") &amp; TEXT(E132, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1204</v>
       </c>
       <c r="E132" s="10">
@@ -3707,17 +3720,17 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1">
-        <f t="shared" ref="A133:A153" si="2">A132+1</f>
+        <f t="shared" ref="A133:A153" si="9">A132+1</f>
         <v>131</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D133" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B133, $M:$M, $N:$N), "00") &amp; TEXT(E133, "00"))</f>
+        <f t="shared" si="8"/>
         <v>114</v>
       </c>
       <c r="E133" s="10">
@@ -3727,17 +3740,17 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>132</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D134" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B134, $M:$M, $N:$N), "00") &amp; TEXT(E134, "00"))</f>
+        <f t="shared" si="8"/>
         <v>703</v>
       </c>
       <c r="E134" s="10">
@@ -3747,17 +3760,17 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>133</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D135" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B135, $M:$M, $N:$N), "00") &amp; TEXT(E135, "00"))</f>
+        <f t="shared" si="8"/>
         <v>504</v>
       </c>
       <c r="E135" s="10">
@@ -3767,17 +3780,17 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>134</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D136" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B136, $M:$M, $N:$N), "00") &amp; TEXT(E136, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2603</v>
       </c>
       <c r="E136" s="10">
@@ -3787,17 +3800,17 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>135</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D137" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B137, $M:$M, $N:$N), "00") &amp; TEXT(E137, "00"))</f>
+        <f t="shared" si="8"/>
         <v>307</v>
       </c>
       <c r="E137" s="10">
@@ -3807,17 +3820,17 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>136</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D138" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B138, $M:$M, $N:$N), "00") &amp; TEXT(E138, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2406</v>
       </c>
       <c r="E138" s="10">
@@ -3827,17 +3840,17 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>137</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D139" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B139, $M:$M, $N:$N), "00") &amp; TEXT(E139, "00"))</f>
+        <f t="shared" si="8"/>
         <v>903</v>
       </c>
       <c r="E139" s="10">
@@ -3847,17 +3860,17 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>138</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D140" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B140, $M:$M, $N:$N), "00") &amp; TEXT(E140, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1606</v>
       </c>
       <c r="E140" s="10">
@@ -3867,17 +3880,17 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>139</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D141" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B141, $M:$M, $N:$N), "00") &amp; TEXT(E141, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2503</v>
       </c>
       <c r="E141" s="10">
@@ -3887,17 +3900,17 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>140</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D142" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B142, $M:$M, $N:$N), "00") &amp; TEXT(E142, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2105</v>
       </c>
       <c r="E142" s="10">
@@ -3907,17 +3920,17 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>141</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D143" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B143, $M:$M, $N:$N), "00") &amp; TEXT(E143, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2306</v>
       </c>
       <c r="E143" s="10">
@@ -3927,17 +3940,17 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>142</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D144" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B144, $M:$M, $N:$N), "00") &amp; TEXT(E144, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1005</v>
       </c>
       <c r="E144" s="10">
@@ -3945,19 +3958,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:7">
       <c r="A145" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>143</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D145" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B145, $M:$M, $N:$N), "00") &amp; TEXT(E145, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1704</v>
       </c>
       <c r="E145" s="10">
@@ -3965,19 +3978,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:7">
       <c r="A146" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>144</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D146" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B146, $M:$M, $N:$N), "00") &amp; TEXT(E146, "00"))</f>
+        <f t="shared" si="8"/>
         <v>203</v>
       </c>
       <c r="E146" s="10">
@@ -3985,19 +3998,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:7">
       <c r="A147" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>145</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D147" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B147, $M:$M, $N:$N), "00") &amp; TEXT(E147, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1507</v>
       </c>
       <c r="E147" s="10">
@@ -4005,19 +4018,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:7">
       <c r="A148" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>146</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D148" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B148, $M:$M, $N:$N), "00") &amp; TEXT(E148, "00"))</f>
+        <f t="shared" si="8"/>
         <v>2002</v>
       </c>
       <c r="E148" s="10">
@@ -4025,19 +4038,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:7">
       <c r="A149" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D149" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B149, $M:$M, $N:$N), "00") &amp; TEXT(E149, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1404</v>
       </c>
       <c r="E149" s="10">
@@ -4045,19 +4058,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:7">
       <c r="A150" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>148</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D150" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B150, $M:$M, $N:$N), "00") &amp; TEXT(E150, "00"))</f>
+        <f t="shared" si="8"/>
         <v>404</v>
       </c>
       <c r="E150" s="10">
@@ -4065,19 +4078,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:7">
       <c r="A151" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>149</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D151" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B151, $M:$M, $N:$N), "00") &amp; TEXT(E151, "00"))</f>
+        <f t="shared" si="8"/>
         <v>603</v>
       </c>
       <c r="E151" s="10">
@@ -4085,19 +4098,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:7">
       <c r="A152" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>150</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D152" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B152, $M:$M, $N:$N), "00") &amp; TEXT(E152, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1306</v>
       </c>
       <c r="E152" s="10">
@@ -4105,19 +4118,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:7">
       <c r="A153" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>151</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D153" s="2">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B153, $M:$M, $N:$N), "00") &amp; TEXT(E153, "00"))</f>
+        <f t="shared" si="8"/>
         <v>1904</v>
       </c>
       <c r="E153" s="10">
@@ -4125,69 +4138,81 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:7">
       <c r="A155" s="1">
         <f>A153+1</f>
         <v>152</v>
       </c>
       <c r="D155" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B155, $M:$M, $N:$N), "00") &amp; TEXT(E155, "00"))</f>
+        <f t="shared" ref="D155:D218" si="10">VALUE(TEXT(_xlfn.XLOOKUP(B155, $M:$M, $N:$N), "00") &amp; TEXT(E155, "00"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E155" s="10">
         <f>COUNTIF($B$2:B155, B155) - 1</f>
         <v>-1</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="G155" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" s="1">
-        <f t="shared" ref="A133:A196" si="3">A155+1</f>
+        <f t="shared" ref="A156:A196" si="11">A155+1</f>
         <v>153</v>
       </c>
       <c r="D156" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B156, $M:$M, $N:$N), "00") &amp; TEXT(E156, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E156" s="10">
         <f>COUNTIF($B$2:B156, B156) - 1</f>
         <v>-1</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="G156" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
       <c r="A157" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>154</v>
       </c>
       <c r="D157" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B157, $M:$M, $N:$N), "00") &amp; TEXT(E157, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E157" s="10">
         <f>COUNTIF($B$2:B157, B157) - 1</f>
         <v>-1</v>
       </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="G157" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>155</v>
       </c>
       <c r="D158" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B158, $M:$M, $N:$N), "00") &amp; TEXT(E158, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E158" s="10">
         <f>COUNTIF($B$2:B158, B158) - 1</f>
         <v>-1</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="G158" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>156</v>
       </c>
       <c r="D159" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B159, $M:$M, $N:$N), "00") &amp; TEXT(E159, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E159" s="10">
@@ -4195,13 +4220,13 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:7">
       <c r="A160" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>157</v>
       </c>
       <c r="D160" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B160, $M:$M, $N:$N), "00") &amp; TEXT(E160, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E160" s="10">
@@ -4211,11 +4236,11 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>158</v>
       </c>
       <c r="D161" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B161, $M:$M, $N:$N), "00") &amp; TEXT(E161, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E161" s="10">
@@ -4225,11 +4250,11 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>159</v>
       </c>
       <c r="D162" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B162, $M:$M, $N:$N), "00") &amp; TEXT(E162, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E162" s="10">
@@ -4239,11 +4264,11 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>160</v>
       </c>
       <c r="D163" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B163, $M:$M, $N:$N), "00") &amp; TEXT(E163, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E163" s="10">
@@ -4253,11 +4278,11 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>161</v>
       </c>
       <c r="D164" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B164, $M:$M, $N:$N), "00") &amp; TEXT(E164, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E164" s="10">
@@ -4267,11 +4292,11 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>162</v>
       </c>
       <c r="D165" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B165, $M:$M, $N:$N), "00") &amp; TEXT(E165, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E165" s="10">
@@ -4281,11 +4306,11 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>163</v>
       </c>
       <c r="D166" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B166, $M:$M, $N:$N), "00") &amp; TEXT(E166, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E166" s="10">
@@ -4295,11 +4320,11 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>164</v>
       </c>
       <c r="D167" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B167, $M:$M, $N:$N), "00") &amp; TEXT(E167, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E167" s="10">
@@ -4309,11 +4334,11 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>165</v>
       </c>
       <c r="D168" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B168, $M:$M, $N:$N), "00") &amp; TEXT(E168, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E168" s="10">
@@ -4323,11 +4348,11 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>166</v>
       </c>
       <c r="D169" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B169, $M:$M, $N:$N), "00") &amp; TEXT(E169, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E169" s="10">
@@ -4337,11 +4362,11 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>167</v>
       </c>
       <c r="D170" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B170, $M:$M, $N:$N), "00") &amp; TEXT(E170, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E170" s="10">
@@ -4351,11 +4376,11 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="D171" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B171, $M:$M, $N:$N), "00") &amp; TEXT(E171, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E171" s="10">
@@ -4365,11 +4390,11 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>169</v>
       </c>
       <c r="D172" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B172, $M:$M, $N:$N), "00") &amp; TEXT(E172, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E172" s="10">
@@ -4379,11 +4404,11 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
       <c r="D173" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B173, $M:$M, $N:$N), "00") &amp; TEXT(E173, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E173" s="10">
@@ -4393,11 +4418,11 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>171</v>
       </c>
       <c r="D174" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B174, $M:$M, $N:$N), "00") &amp; TEXT(E174, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E174" s="10">
@@ -4407,11 +4432,11 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>172</v>
       </c>
       <c r="D175" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B175, $M:$M, $N:$N), "00") &amp; TEXT(E175, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E175" s="10">
@@ -4421,11 +4446,11 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>173</v>
       </c>
       <c r="D176" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B176, $M:$M, $N:$N), "00") &amp; TEXT(E176, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E176" s="10">
@@ -4435,11 +4460,11 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>174</v>
       </c>
       <c r="D177" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B177, $M:$M, $N:$N), "00") &amp; TEXT(E177, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E177" s="10">
@@ -4449,11 +4474,11 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>175</v>
       </c>
       <c r="D178" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B178, $M:$M, $N:$N), "00") &amp; TEXT(E178, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E178" s="10">
@@ -4463,11 +4488,11 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>176</v>
       </c>
       <c r="D179" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B179, $M:$M, $N:$N), "00") &amp; TEXT(E179, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E179" s="10">
@@ -4477,11 +4502,11 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>177</v>
       </c>
       <c r="D180" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B180, $M:$M, $N:$N), "00") &amp; TEXT(E180, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E180" s="10">
@@ -4491,11 +4516,11 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>178</v>
       </c>
       <c r="D181" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B181, $M:$M, $N:$N), "00") &amp; TEXT(E181, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E181" s="10">
@@ -4505,11 +4530,11 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>179</v>
       </c>
       <c r="D182" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B182, $M:$M, $N:$N), "00") &amp; TEXT(E182, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E182" s="10">
@@ -4519,11 +4544,11 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>180</v>
       </c>
       <c r="D183" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B183, $M:$M, $N:$N), "00") &amp; TEXT(E183, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E183" s="10">
@@ -4533,11 +4558,11 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>181</v>
       </c>
       <c r="D184" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B184, $M:$M, $N:$N), "00") &amp; TEXT(E184, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E184" s="10">
@@ -4547,11 +4572,11 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>182</v>
       </c>
       <c r="D185" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B185, $M:$M, $N:$N), "00") &amp; TEXT(E185, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E185" s="10">
@@ -4561,11 +4586,11 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>183</v>
       </c>
       <c r="D186" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B186, $M:$M, $N:$N), "00") &amp; TEXT(E186, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E186" s="10">
@@ -4575,11 +4600,11 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>184</v>
       </c>
       <c r="D187" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B187, $M:$M, $N:$N), "00") &amp; TEXT(E187, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E187" s="10">
@@ -4589,11 +4614,11 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>185</v>
       </c>
       <c r="D188" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B188, $M:$M, $N:$N), "00") &amp; TEXT(E188, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E188" s="10">
@@ -4603,11 +4628,11 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>186</v>
       </c>
       <c r="D189" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B189, $M:$M, $N:$N), "00") &amp; TEXT(E189, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E189" s="10">
@@ -4617,11 +4642,11 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>187</v>
       </c>
       <c r="D190" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B190, $M:$M, $N:$N), "00") &amp; TEXT(E190, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E190" s="10">
@@ -4631,11 +4656,11 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>188</v>
       </c>
       <c r="D191" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B191, $M:$M, $N:$N), "00") &amp; TEXT(E191, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E191" s="10">
@@ -4645,11 +4670,11 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>189</v>
       </c>
       <c r="D192" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B192, $M:$M, $N:$N), "00") &amp; TEXT(E192, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E192" s="10">
@@ -4659,11 +4684,11 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>190</v>
       </c>
       <c r="D193" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B193, $M:$M, $N:$N), "00") &amp; TEXT(E193, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E193" s="10">
@@ -4673,11 +4698,11 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>191</v>
       </c>
       <c r="D194" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B194, $M:$M, $N:$N), "00") &amp; TEXT(E194, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E194" s="10">
@@ -4687,11 +4712,11 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>192</v>
       </c>
       <c r="D195" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B195, $M:$M, $N:$N), "00") &amp; TEXT(E195, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E195" s="10">
@@ -4701,11 +4726,11 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>193</v>
       </c>
       <c r="D196" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B196, $M:$M, $N:$N), "00") &amp; TEXT(E196, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E196" s="10">
@@ -4715,11 +4740,11 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="1">
-        <f t="shared" ref="A197:A260" si="4">A196+1</f>
+        <f t="shared" ref="A197:A260" si="12">A196+1</f>
         <v>194</v>
       </c>
       <c r="D197" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B197, $M:$M, $N:$N), "00") &amp; TEXT(E197, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E197" s="10">
@@ -4729,11 +4754,11 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>195</v>
       </c>
       <c r="D198" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B198, $M:$M, $N:$N), "00") &amp; TEXT(E198, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E198" s="10">
@@ -4743,11 +4768,11 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>196</v>
       </c>
       <c r="D199" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B199, $M:$M, $N:$N), "00") &amp; TEXT(E199, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E199" s="10">
@@ -4757,11 +4782,11 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>197</v>
       </c>
       <c r="D200" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B200, $M:$M, $N:$N), "00") &amp; TEXT(E200, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E200" s="10">
@@ -4771,11 +4796,11 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>198</v>
       </c>
       <c r="D201" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B201, $M:$M, $N:$N), "00") &amp; TEXT(E201, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E201" s="10">
@@ -4785,11 +4810,11 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>199</v>
       </c>
       <c r="D202" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B202, $M:$M, $N:$N), "00") &amp; TEXT(E202, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E202" s="10">
@@ -4799,11 +4824,11 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
       <c r="D203" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B203, $M:$M, $N:$N), "00") &amp; TEXT(E203, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E203" s="10">
@@ -4813,11 +4838,11 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>201</v>
       </c>
       <c r="D204" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B204, $M:$M, $N:$N), "00") &amp; TEXT(E204, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E204" s="10">
@@ -4827,11 +4852,11 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>202</v>
       </c>
       <c r="D205" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B205, $M:$M, $N:$N), "00") &amp; TEXT(E205, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E205" s="10">
@@ -4841,11 +4866,11 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>203</v>
       </c>
       <c r="D206" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B206, $M:$M, $N:$N), "00") &amp; TEXT(E206, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E206" s="10">
@@ -4855,11 +4880,11 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>204</v>
       </c>
       <c r="D207" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B207, $M:$M, $N:$N), "00") &amp; TEXT(E207, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E207" s="10">
@@ -4869,11 +4894,11 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>205</v>
       </c>
       <c r="D208" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B208, $M:$M, $N:$N), "00") &amp; TEXT(E208, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E208" s="10">
@@ -4883,11 +4908,11 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>206</v>
       </c>
       <c r="D209" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B209, $M:$M, $N:$N), "00") &amp; TEXT(E209, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E209" s="10">
@@ -4897,11 +4922,11 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>207</v>
       </c>
       <c r="D210" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B210, $M:$M, $N:$N), "00") &amp; TEXT(E210, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E210" s="10">
@@ -4911,11 +4936,11 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>208</v>
       </c>
       <c r="D211" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B211, $M:$M, $N:$N), "00") &amp; TEXT(E211, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E211" s="10">
@@ -4925,11 +4950,11 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>209</v>
       </c>
       <c r="D212" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B212, $M:$M, $N:$N), "00") &amp; TEXT(E212, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E212" s="10">
@@ -4939,11 +4964,11 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>210</v>
       </c>
       <c r="D213" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B213, $M:$M, $N:$N), "00") &amp; TEXT(E213, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E213" s="10">
@@ -4953,11 +4978,11 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>211</v>
       </c>
       <c r="D214" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B214, $M:$M, $N:$N), "00") &amp; TEXT(E214, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E214" s="10">
@@ -4967,11 +4992,11 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>212</v>
       </c>
       <c r="D215" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B215, $M:$M, $N:$N), "00") &amp; TEXT(E215, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E215" s="10">
@@ -4981,11 +5006,11 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>213</v>
       </c>
       <c r="D216" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B216, $M:$M, $N:$N), "00") &amp; TEXT(E216, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E216" s="10">
@@ -4995,11 +5020,11 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>214</v>
       </c>
       <c r="D217" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B217, $M:$M, $N:$N), "00") &amp; TEXT(E217, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E217" s="10">
@@ -5009,11 +5034,11 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>215</v>
       </c>
       <c r="D218" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B218, $M:$M, $N:$N), "00") &amp; TEXT(E218, "00"))</f>
+        <f t="shared" si="10"/>
         <v>#VALUE!</v>
       </c>
       <c r="E218" s="10">
@@ -5023,11 +5048,11 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>216</v>
       </c>
       <c r="D219" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B219, $M:$M, $N:$N), "00") &amp; TEXT(E219, "00"))</f>
+        <f t="shared" ref="D219:D282" si="13">VALUE(TEXT(_xlfn.XLOOKUP(B219, $M:$M, $N:$N), "00") &amp; TEXT(E219, "00"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E219" s="10">
@@ -5037,11 +5062,11 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>217</v>
       </c>
       <c r="D220" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B220, $M:$M, $N:$N), "00") &amp; TEXT(E220, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E220" s="10">
@@ -5051,11 +5076,11 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>218</v>
       </c>
       <c r="D221" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B221, $M:$M, $N:$N), "00") &amp; TEXT(E221, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E221" s="10">
@@ -5065,11 +5090,11 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>219</v>
       </c>
       <c r="D222" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B222, $M:$M, $N:$N), "00") &amp; TEXT(E222, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E222" s="10">
@@ -5079,11 +5104,11 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>220</v>
       </c>
       <c r="D223" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B223, $M:$M, $N:$N), "00") &amp; TEXT(E223, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E223" s="10">
@@ -5093,11 +5118,11 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>221</v>
       </c>
       <c r="D224" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B224, $M:$M, $N:$N), "00") &amp; TEXT(E224, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E224" s="10">
@@ -5107,11 +5132,11 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>222</v>
       </c>
       <c r="D225" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B225, $M:$M, $N:$N), "00") &amp; TEXT(E225, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E225" s="10">
@@ -5121,11 +5146,11 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>223</v>
       </c>
       <c r="D226" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B226, $M:$M, $N:$N), "00") &amp; TEXT(E226, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E226" s="10">
@@ -5135,11 +5160,11 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>224</v>
       </c>
       <c r="D227" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B227, $M:$M, $N:$N), "00") &amp; TEXT(E227, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E227" s="10">
@@ -5149,11 +5174,11 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>225</v>
       </c>
       <c r="D228" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B228, $M:$M, $N:$N), "00") &amp; TEXT(E228, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E228" s="10">
@@ -5163,11 +5188,11 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>226</v>
       </c>
       <c r="D229" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B229, $M:$M, $N:$N), "00") &amp; TEXT(E229, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E229" s="10">
@@ -5177,11 +5202,11 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>227</v>
       </c>
       <c r="D230" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B230, $M:$M, $N:$N), "00") &amp; TEXT(E230, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E230" s="10">
@@ -5191,11 +5216,11 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>228</v>
       </c>
       <c r="D231" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B231, $M:$M, $N:$N), "00") &amp; TEXT(E231, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E231" s="10">
@@ -5205,11 +5230,11 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>229</v>
       </c>
       <c r="D232" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B232, $M:$M, $N:$N), "00") &amp; TEXT(E232, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E232" s="10">
@@ -5219,11 +5244,11 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>230</v>
       </c>
       <c r="D233" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B233, $M:$M, $N:$N), "00") &amp; TEXT(E233, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E233" s="10">
@@ -5233,11 +5258,11 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>231</v>
       </c>
       <c r="D234" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B234, $M:$M, $N:$N), "00") &amp; TEXT(E234, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E234" s="10">
@@ -5247,11 +5272,11 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>232</v>
       </c>
       <c r="D235" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B235, $M:$M, $N:$N), "00") &amp; TEXT(E235, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E235" s="10">
@@ -5261,11 +5286,11 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>233</v>
       </c>
       <c r="D236" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B236, $M:$M, $N:$N), "00") &amp; TEXT(E236, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E236" s="10">
@@ -5275,11 +5300,11 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>234</v>
       </c>
       <c r="D237" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B237, $M:$M, $N:$N), "00") &amp; TEXT(E237, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E237" s="10">
@@ -5289,11 +5314,11 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>235</v>
       </c>
       <c r="D238" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B238, $M:$M, $N:$N), "00") &amp; TEXT(E238, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E238" s="10">
@@ -5303,11 +5328,11 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>236</v>
       </c>
       <c r="D239" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B239, $M:$M, $N:$N), "00") &amp; TEXT(E239, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E239" s="10">
@@ -5317,11 +5342,11 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>237</v>
       </c>
       <c r="D240" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B240, $M:$M, $N:$N), "00") &amp; TEXT(E240, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E240" s="10">
@@ -5331,11 +5356,11 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>238</v>
       </c>
       <c r="D241" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B241, $M:$M, $N:$N), "00") &amp; TEXT(E241, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E241" s="10">
@@ -5345,11 +5370,11 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>239</v>
       </c>
       <c r="D242" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B242, $M:$M, $N:$N), "00") &amp; TEXT(E242, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E242" s="10">
@@ -5359,11 +5384,11 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>240</v>
       </c>
       <c r="D243" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B243, $M:$M, $N:$N), "00") &amp; TEXT(E243, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E243" s="10">
@@ -5373,11 +5398,11 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>241</v>
       </c>
       <c r="D244" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B244, $M:$M, $N:$N), "00") &amp; TEXT(E244, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E244" s="10">
@@ -5387,11 +5412,11 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>242</v>
       </c>
       <c r="D245" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B245, $M:$M, $N:$N), "00") &amp; TEXT(E245, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E245" s="10">
@@ -5401,11 +5426,11 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>243</v>
       </c>
       <c r="D246" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B246, $M:$M, $N:$N), "00") &amp; TEXT(E246, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E246" s="10">
@@ -5415,11 +5440,11 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>244</v>
       </c>
       <c r="D247" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B247, $M:$M, $N:$N), "00") &amp; TEXT(E247, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E247" s="10">
@@ -5429,11 +5454,11 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>245</v>
       </c>
       <c r="D248" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B248, $M:$M, $N:$N), "00") &amp; TEXT(E248, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E248" s="10">
@@ -5443,11 +5468,11 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>246</v>
       </c>
       <c r="D249" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B249, $M:$M, $N:$N), "00") &amp; TEXT(E249, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E249" s="10">
@@ -5457,11 +5482,11 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>247</v>
       </c>
       <c r="D250" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B250, $M:$M, $N:$N), "00") &amp; TEXT(E250, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E250" s="10">
@@ -5471,11 +5496,11 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>248</v>
       </c>
       <c r="D251" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B251, $M:$M, $N:$N), "00") &amp; TEXT(E251, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E251" s="10">
@@ -5485,11 +5510,11 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>249</v>
       </c>
       <c r="D252" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B252, $M:$M, $N:$N), "00") &amp; TEXT(E252, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E252" s="10">
@@ -5499,11 +5524,11 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>250</v>
       </c>
       <c r="D253" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B253, $M:$M, $N:$N), "00") &amp; TEXT(E253, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E253" s="10">
@@ -5513,11 +5538,11 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>251</v>
       </c>
       <c r="D254" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B254, $M:$M, $N:$N), "00") &amp; TEXT(E254, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E254" s="10">
@@ -5527,11 +5552,11 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>252</v>
       </c>
       <c r="D255" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B255, $M:$M, $N:$N), "00") &amp; TEXT(E255, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E255" s="10">
@@ -5541,11 +5566,11 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>253</v>
       </c>
       <c r="D256" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B256, $M:$M, $N:$N), "00") &amp; TEXT(E256, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E256" s="10">
@@ -5555,11 +5580,11 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>254</v>
       </c>
       <c r="D257" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B257, $M:$M, $N:$N), "00") &amp; TEXT(E257, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E257" s="10">
@@ -5569,11 +5594,11 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>255</v>
       </c>
       <c r="D258" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B258, $M:$M, $N:$N), "00") &amp; TEXT(E258, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E258" s="10">
@@ -5583,11 +5608,11 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>256</v>
       </c>
       <c r="D259" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B259, $M:$M, $N:$N), "00") &amp; TEXT(E259, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E259" s="10">
@@ -5597,11 +5622,11 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="12"/>
         <v>257</v>
       </c>
       <c r="D260" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B260, $M:$M, $N:$N), "00") &amp; TEXT(E260, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E260" s="10">
@@ -5611,11 +5636,11 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="1">
-        <f t="shared" ref="A261:A324" si="5">A260+1</f>
+        <f t="shared" ref="A261:A324" si="14">A260+1</f>
         <v>258</v>
       </c>
       <c r="D261" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B261, $M:$M, $N:$N), "00") &amp; TEXT(E261, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E261" s="10">
@@ -5625,11 +5650,11 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>259</v>
       </c>
       <c r="D262" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B262, $M:$M, $N:$N), "00") &amp; TEXT(E262, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E262" s="10">
@@ -5639,11 +5664,11 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>260</v>
       </c>
       <c r="D263" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B263, $M:$M, $N:$N), "00") &amp; TEXT(E263, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E263" s="10">
@@ -5653,11 +5678,11 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>261</v>
       </c>
       <c r="D264" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B264, $M:$M, $N:$N), "00") &amp; TEXT(E264, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E264" s="10">
@@ -5667,11 +5692,11 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>262</v>
       </c>
       <c r="D265" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B265, $M:$M, $N:$N), "00") &amp; TEXT(E265, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E265" s="10">
@@ -5681,11 +5706,11 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>263</v>
       </c>
       <c r="D266" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B266, $M:$M, $N:$N), "00") &amp; TEXT(E266, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E266" s="10">
@@ -5695,11 +5720,11 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>264</v>
       </c>
       <c r="D267" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B267, $M:$M, $N:$N), "00") &amp; TEXT(E267, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E267" s="10">
@@ -5709,11 +5734,11 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>265</v>
       </c>
       <c r="D268" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B268, $M:$M, $N:$N), "00") &amp; TEXT(E268, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E268" s="10">
@@ -5723,11 +5748,11 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>266</v>
       </c>
       <c r="D269" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B269, $M:$M, $N:$N), "00") &amp; TEXT(E269, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E269" s="10">
@@ -5737,11 +5762,11 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>267</v>
       </c>
       <c r="D270" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B270, $M:$M, $N:$N), "00") &amp; TEXT(E270, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E270" s="10">
@@ -5751,11 +5776,11 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>268</v>
       </c>
       <c r="D271" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B271, $M:$M, $N:$N), "00") &amp; TEXT(E271, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E271" s="10">
@@ -5765,11 +5790,11 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>269</v>
       </c>
       <c r="D272" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B272, $M:$M, $N:$N), "00") &amp; TEXT(E272, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E272" s="10">
@@ -5779,11 +5804,11 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>270</v>
       </c>
       <c r="D273" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B273, $M:$M, $N:$N), "00") &amp; TEXT(E273, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E273" s="10">
@@ -5793,11 +5818,11 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>271</v>
       </c>
       <c r="D274" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B274, $M:$M, $N:$N), "00") &amp; TEXT(E274, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E274" s="10">
@@ -5807,11 +5832,11 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>272</v>
       </c>
       <c r="D275" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B275, $M:$M, $N:$N), "00") &amp; TEXT(E275, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E275" s="10">
@@ -5821,11 +5846,11 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>273</v>
       </c>
       <c r="D276" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B276, $M:$M, $N:$N), "00") &amp; TEXT(E276, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E276" s="10">
@@ -5835,11 +5860,11 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>274</v>
       </c>
       <c r="D277" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B277, $M:$M, $N:$N), "00") &amp; TEXT(E277, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E277" s="10">
@@ -5849,11 +5874,11 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>275</v>
       </c>
       <c r="D278" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B278, $M:$M, $N:$N), "00") &amp; TEXT(E278, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E278" s="10">
@@ -5863,11 +5888,11 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>276</v>
       </c>
       <c r="D279" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B279, $M:$M, $N:$N), "00") &amp; TEXT(E279, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E279" s="10">
@@ -5877,11 +5902,11 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>277</v>
       </c>
       <c r="D280" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B280, $M:$M, $N:$N), "00") &amp; TEXT(E280, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E280" s="10">
@@ -5891,11 +5916,11 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>278</v>
       </c>
       <c r="D281" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B281, $M:$M, $N:$N), "00") &amp; TEXT(E281, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E281" s="10">
@@ -5905,11 +5930,11 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>279</v>
       </c>
       <c r="D282" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B282, $M:$M, $N:$N), "00") &amp; TEXT(E282, "00"))</f>
+        <f t="shared" si="13"/>
         <v>#VALUE!</v>
       </c>
       <c r="E282" s="10">
@@ -5919,11 +5944,11 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>280</v>
       </c>
       <c r="D283" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B283, $M:$M, $N:$N), "00") &amp; TEXT(E283, "00"))</f>
+        <f t="shared" ref="D283:D346" si="15">VALUE(TEXT(_xlfn.XLOOKUP(B283, $M:$M, $N:$N), "00") &amp; TEXT(E283, "00"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E283" s="10">
@@ -5933,11 +5958,11 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>281</v>
       </c>
       <c r="D284" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B284, $M:$M, $N:$N), "00") &amp; TEXT(E284, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E284" s="10">
@@ -5947,11 +5972,11 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>282</v>
       </c>
       <c r="D285" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B285, $M:$M, $N:$N), "00") &amp; TEXT(E285, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E285" s="10">
@@ -5961,11 +5986,11 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>283</v>
       </c>
       <c r="D286" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B286, $M:$M, $N:$N), "00") &amp; TEXT(E286, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E286" s="10">
@@ -5975,11 +6000,11 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>284</v>
       </c>
       <c r="D287" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B287, $M:$M, $N:$N), "00") &amp; TEXT(E287, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E287" s="10">
@@ -5989,11 +6014,11 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>285</v>
       </c>
       <c r="D288" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B288, $M:$M, $N:$N), "00") &amp; TEXT(E288, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E288" s="10">
@@ -6003,11 +6028,11 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>286</v>
       </c>
       <c r="D289" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B289, $M:$M, $N:$N), "00") &amp; TEXT(E289, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E289" s="10">
@@ -6017,11 +6042,11 @@
     </row>
     <row r="290" spans="1:5">
       <c r="A290" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>287</v>
       </c>
       <c r="D290" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B290, $M:$M, $N:$N), "00") &amp; TEXT(E290, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E290" s="10">
@@ -6031,11 +6056,11 @@
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>288</v>
       </c>
       <c r="D291" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B291, $M:$M, $N:$N), "00") &amp; TEXT(E291, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E291" s="10">
@@ -6045,11 +6070,11 @@
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>289</v>
       </c>
       <c r="D292" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B292, $M:$M, $N:$N), "00") &amp; TEXT(E292, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E292" s="10">
@@ -6059,11 +6084,11 @@
     </row>
     <row r="293" spans="1:5">
       <c r="A293" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>290</v>
       </c>
       <c r="D293" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B293, $M:$M, $N:$N), "00") &amp; TEXT(E293, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E293" s="10">
@@ -6073,11 +6098,11 @@
     </row>
     <row r="294" spans="1:5">
       <c r="A294" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>291</v>
       </c>
       <c r="D294" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B294, $M:$M, $N:$N), "00") &amp; TEXT(E294, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E294" s="10">
@@ -6087,11 +6112,11 @@
     </row>
     <row r="295" spans="1:5">
       <c r="A295" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>292</v>
       </c>
       <c r="D295" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B295, $M:$M, $N:$N), "00") &amp; TEXT(E295, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E295" s="10">
@@ -6101,11 +6126,11 @@
     </row>
     <row r="296" spans="1:5">
       <c r="A296" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>293</v>
       </c>
       <c r="D296" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B296, $M:$M, $N:$N), "00") &amp; TEXT(E296, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E296" s="10">
@@ -6115,11 +6140,11 @@
     </row>
     <row r="297" spans="1:5">
       <c r="A297" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>294</v>
       </c>
       <c r="D297" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B297, $M:$M, $N:$N), "00") &amp; TEXT(E297, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E297" s="10">
@@ -6129,11 +6154,11 @@
     </row>
     <row r="298" spans="1:5">
       <c r="A298" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>295</v>
       </c>
       <c r="D298" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B298, $M:$M, $N:$N), "00") &amp; TEXT(E298, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E298" s="10">
@@ -6143,11 +6168,11 @@
     </row>
     <row r="299" spans="1:5">
       <c r="A299" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>296</v>
       </c>
       <c r="D299" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B299, $M:$M, $N:$N), "00") &amp; TEXT(E299, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E299" s="10">
@@ -6157,11 +6182,11 @@
     </row>
     <row r="300" spans="1:5">
       <c r="A300" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>297</v>
       </c>
       <c r="D300" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B300, $M:$M, $N:$N), "00") &amp; TEXT(E300, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E300" s="10">
@@ -6171,11 +6196,11 @@
     </row>
     <row r="301" spans="1:5">
       <c r="A301" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>298</v>
       </c>
       <c r="D301" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B301, $M:$M, $N:$N), "00") &amp; TEXT(E301, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E301" s="10">
@@ -6185,11 +6210,11 @@
     </row>
     <row r="302" spans="1:5">
       <c r="A302" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>299</v>
       </c>
       <c r="D302" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B302, $M:$M, $N:$N), "00") &amp; TEXT(E302, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E302" s="10">
@@ -6199,11 +6224,11 @@
     </row>
     <row r="303" spans="1:5">
       <c r="A303" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>300</v>
       </c>
       <c r="D303" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B303, $M:$M, $N:$N), "00") &amp; TEXT(E303, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E303" s="10">
@@ -6213,11 +6238,11 @@
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>301</v>
       </c>
       <c r="D304" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B304, $M:$M, $N:$N), "00") &amp; TEXT(E304, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E304" s="10">
@@ -6227,11 +6252,11 @@
     </row>
     <row r="305" spans="1:5">
       <c r="A305" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>302</v>
       </c>
       <c r="D305" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B305, $M:$M, $N:$N), "00") &amp; TEXT(E305, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E305" s="10">
@@ -6241,11 +6266,11 @@
     </row>
     <row r="306" spans="1:5">
       <c r="A306" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>303</v>
       </c>
       <c r="D306" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B306, $M:$M, $N:$N), "00") &amp; TEXT(E306, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E306" s="10">
@@ -6255,11 +6280,11 @@
     </row>
     <row r="307" spans="1:5">
       <c r="A307" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>304</v>
       </c>
       <c r="D307" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B307, $M:$M, $N:$N), "00") &amp; TEXT(E307, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E307" s="10">
@@ -6269,11 +6294,11 @@
     </row>
     <row r="308" spans="1:5">
       <c r="A308" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>305</v>
       </c>
       <c r="D308" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B308, $M:$M, $N:$N), "00") &amp; TEXT(E308, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E308" s="10">
@@ -6283,11 +6308,11 @@
     </row>
     <row r="309" spans="1:5">
       <c r="A309" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>306</v>
       </c>
       <c r="D309" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B309, $M:$M, $N:$N), "00") &amp; TEXT(E309, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E309" s="10">
@@ -6297,11 +6322,11 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>307</v>
       </c>
       <c r="D310" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B310, $M:$M, $N:$N), "00") &amp; TEXT(E310, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E310" s="10">
@@ -6311,11 +6336,11 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>308</v>
       </c>
       <c r="D311" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B311, $M:$M, $N:$N), "00") &amp; TEXT(E311, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E311" s="10">
@@ -6325,11 +6350,11 @@
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>309</v>
       </c>
       <c r="D312" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B312, $M:$M, $N:$N), "00") &amp; TEXT(E312, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E312" s="10">
@@ -6339,11 +6364,11 @@
     </row>
     <row r="313" spans="1:5">
       <c r="A313" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>310</v>
       </c>
       <c r="D313" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B313, $M:$M, $N:$N), "00") &amp; TEXT(E313, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E313" s="10">
@@ -6353,11 +6378,11 @@
     </row>
     <row r="314" spans="1:5">
       <c r="A314" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>311</v>
       </c>
       <c r="D314" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B314, $M:$M, $N:$N), "00") &amp; TEXT(E314, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E314" s="10">
@@ -6367,11 +6392,11 @@
     </row>
     <row r="315" spans="1:5">
       <c r="A315" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>312</v>
       </c>
       <c r="D315" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B315, $M:$M, $N:$N), "00") &amp; TEXT(E315, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E315" s="10">
@@ -6381,11 +6406,11 @@
     </row>
     <row r="316" spans="1:5">
       <c r="A316" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>313</v>
       </c>
       <c r="D316" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B316, $M:$M, $N:$N), "00") &amp; TEXT(E316, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E316" s="10">
@@ -6395,11 +6420,11 @@
     </row>
     <row r="317" spans="1:5">
       <c r="A317" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>314</v>
       </c>
       <c r="D317" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B317, $M:$M, $N:$N), "00") &amp; TEXT(E317, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E317" s="10">
@@ -6409,11 +6434,11 @@
     </row>
     <row r="318" spans="1:5">
       <c r="A318" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>315</v>
       </c>
       <c r="D318" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B318, $M:$M, $N:$N), "00") &amp; TEXT(E318, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E318" s="10">
@@ -6423,11 +6448,11 @@
     </row>
     <row r="319" spans="1:5">
       <c r="A319" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>316</v>
       </c>
       <c r="D319" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B319, $M:$M, $N:$N), "00") &amp; TEXT(E319, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E319" s="10">
@@ -6437,11 +6462,11 @@
     </row>
     <row r="320" spans="1:5">
       <c r="A320" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>317</v>
       </c>
       <c r="D320" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B320, $M:$M, $N:$N), "00") &amp; TEXT(E320, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E320" s="10">
@@ -6451,11 +6476,11 @@
     </row>
     <row r="321" spans="1:5">
       <c r="A321" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>318</v>
       </c>
       <c r="D321" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B321, $M:$M, $N:$N), "00") &amp; TEXT(E321, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E321" s="10">
@@ -6465,11 +6490,11 @@
     </row>
     <row r="322" spans="1:5">
       <c r="A322" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>319</v>
       </c>
       <c r="D322" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B322, $M:$M, $N:$N), "00") &amp; TEXT(E322, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E322" s="10">
@@ -6479,11 +6504,11 @@
     </row>
     <row r="323" spans="1:5">
       <c r="A323" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>320</v>
       </c>
       <c r="D323" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B323, $M:$M, $N:$N), "00") &amp; TEXT(E323, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E323" s="10">
@@ -6493,11 +6518,11 @@
     </row>
     <row r="324" spans="1:5">
       <c r="A324" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>321</v>
       </c>
       <c r="D324" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B324, $M:$M, $N:$N), "00") &amp; TEXT(E324, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E324" s="10">
@@ -6507,11 +6532,11 @@
     </row>
     <row r="325" spans="1:5">
       <c r="A325" s="1">
-        <f t="shared" ref="A325:A388" si="6">A324+1</f>
+        <f t="shared" ref="A325:A388" si="16">A324+1</f>
         <v>322</v>
       </c>
       <c r="D325" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B325, $M:$M, $N:$N), "00") &amp; TEXT(E325, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E325" s="10">
@@ -6521,11 +6546,11 @@
     </row>
     <row r="326" spans="1:5">
       <c r="A326" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>323</v>
       </c>
       <c r="D326" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B326, $M:$M, $N:$N), "00") &amp; TEXT(E326, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E326" s="10">
@@ -6535,11 +6560,11 @@
     </row>
     <row r="327" spans="1:5">
       <c r="A327" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>324</v>
       </c>
       <c r="D327" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B327, $M:$M, $N:$N), "00") &amp; TEXT(E327, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E327" s="10">
@@ -6549,11 +6574,11 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>325</v>
       </c>
       <c r="D328" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B328, $M:$M, $N:$N), "00") &amp; TEXT(E328, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E328" s="10">
@@ -6563,11 +6588,11 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>326</v>
       </c>
       <c r="D329" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B329, $M:$M, $N:$N), "00") &amp; TEXT(E329, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E329" s="10">
@@ -6577,11 +6602,11 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>327</v>
       </c>
       <c r="D330" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B330, $M:$M, $N:$N), "00") &amp; TEXT(E330, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E330" s="10">
@@ -6591,11 +6616,11 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>328</v>
       </c>
       <c r="D331" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B331, $M:$M, $N:$N), "00") &amp; TEXT(E331, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E331" s="10">
@@ -6605,11 +6630,11 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>329</v>
       </c>
       <c r="D332" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B332, $M:$M, $N:$N), "00") &amp; TEXT(E332, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E332" s="10">
@@ -6619,11 +6644,11 @@
     </row>
     <row r="333" spans="1:5">
       <c r="A333" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>330</v>
       </c>
       <c r="D333" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B333, $M:$M, $N:$N), "00") &amp; TEXT(E333, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E333" s="10">
@@ -6633,11 +6658,11 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>331</v>
       </c>
       <c r="D334" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B334, $M:$M, $N:$N), "00") &amp; TEXT(E334, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E334" s="10">
@@ -6647,11 +6672,11 @@
     </row>
     <row r="335" spans="1:5">
       <c r="A335" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>332</v>
       </c>
       <c r="D335" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B335, $M:$M, $N:$N), "00") &amp; TEXT(E335, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E335" s="10">
@@ -6661,11 +6686,11 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>333</v>
       </c>
       <c r="D336" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B336, $M:$M, $N:$N), "00") &amp; TEXT(E336, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E336" s="10">
@@ -6675,11 +6700,11 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>334</v>
       </c>
       <c r="D337" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B337, $M:$M, $N:$N), "00") &amp; TEXT(E337, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E337" s="10">
@@ -6689,11 +6714,11 @@
     </row>
     <row r="338" spans="1:5">
       <c r="A338" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>335</v>
       </c>
       <c r="D338" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B338, $M:$M, $N:$N), "00") &amp; TEXT(E338, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E338" s="10">
@@ -6703,11 +6728,11 @@
     </row>
     <row r="339" spans="1:5">
       <c r="A339" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>336</v>
       </c>
       <c r="D339" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B339, $M:$M, $N:$N), "00") &amp; TEXT(E339, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E339" s="10">
@@ -6717,11 +6742,11 @@
     </row>
     <row r="340" spans="1:5">
       <c r="A340" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>337</v>
       </c>
       <c r="D340" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B340, $M:$M, $N:$N), "00") &amp; TEXT(E340, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E340" s="10">
@@ -6731,11 +6756,11 @@
     </row>
     <row r="341" spans="1:5">
       <c r="A341" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>338</v>
       </c>
       <c r="D341" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B341, $M:$M, $N:$N), "00") &amp; TEXT(E341, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E341" s="10">
@@ -6745,11 +6770,11 @@
     </row>
     <row r="342" spans="1:5">
       <c r="A342" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>339</v>
       </c>
       <c r="D342" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B342, $M:$M, $N:$N), "00") &amp; TEXT(E342, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E342" s="10">
@@ -6759,11 +6784,11 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>340</v>
       </c>
       <c r="D343" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B343, $M:$M, $N:$N), "00") &amp; TEXT(E343, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E343" s="10">
@@ -6773,11 +6798,11 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>341</v>
       </c>
       <c r="D344" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B344, $M:$M, $N:$N), "00") &amp; TEXT(E344, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E344" s="10">
@@ -6787,11 +6812,11 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>342</v>
       </c>
       <c r="D345" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B345, $M:$M, $N:$N), "00") &amp; TEXT(E345, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E345" s="10">
@@ -6801,11 +6826,11 @@
     </row>
     <row r="346" spans="1:5">
       <c r="A346" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>343</v>
       </c>
       <c r="D346" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B346, $M:$M, $N:$N), "00") &amp; TEXT(E346, "00"))</f>
+        <f t="shared" si="15"/>
         <v>#VALUE!</v>
       </c>
       <c r="E346" s="10">
@@ -6815,11 +6840,11 @@
     </row>
     <row r="347" spans="1:5">
       <c r="A347" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>344</v>
       </c>
       <c r="D347" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B347, $M:$M, $N:$N), "00") &amp; TEXT(E347, "00"))</f>
+        <f t="shared" ref="D347:D410" si="17">VALUE(TEXT(_xlfn.XLOOKUP(B347, $M:$M, $N:$N), "00") &amp; TEXT(E347, "00"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E347" s="10">
@@ -6829,11 +6854,11 @@
     </row>
     <row r="348" spans="1:5">
       <c r="A348" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>345</v>
       </c>
       <c r="D348" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B348, $M:$M, $N:$N), "00") &amp; TEXT(E348, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E348" s="10">
@@ -6843,11 +6868,11 @@
     </row>
     <row r="349" spans="1:5">
       <c r="A349" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>346</v>
       </c>
       <c r="D349" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B349, $M:$M, $N:$N), "00") &amp; TEXT(E349, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E349" s="10">
@@ -6857,11 +6882,11 @@
     </row>
     <row r="350" spans="1:5">
       <c r="A350" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>347</v>
       </c>
       <c r="D350" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B350, $M:$M, $N:$N), "00") &amp; TEXT(E350, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E350" s="10">
@@ -6871,11 +6896,11 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>348</v>
       </c>
       <c r="D351" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B351, $M:$M, $N:$N), "00") &amp; TEXT(E351, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E351" s="10">
@@ -6885,11 +6910,11 @@
     </row>
     <row r="352" spans="1:5">
       <c r="A352" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>349</v>
       </c>
       <c r="D352" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B352, $M:$M, $N:$N), "00") &amp; TEXT(E352, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E352" s="10">
@@ -6899,11 +6924,11 @@
     </row>
     <row r="353" spans="1:5">
       <c r="A353" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>350</v>
       </c>
       <c r="D353" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B353, $M:$M, $N:$N), "00") &amp; TEXT(E353, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E353" s="10">
@@ -6913,11 +6938,11 @@
     </row>
     <row r="354" spans="1:5">
       <c r="A354" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>351</v>
       </c>
       <c r="D354" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B354, $M:$M, $N:$N), "00") &amp; TEXT(E354, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E354" s="10">
@@ -6927,11 +6952,11 @@
     </row>
     <row r="355" spans="1:5">
       <c r="A355" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>352</v>
       </c>
       <c r="D355" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B355, $M:$M, $N:$N), "00") &amp; TEXT(E355, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E355" s="10">
@@ -6941,11 +6966,11 @@
     </row>
     <row r="356" spans="1:5">
       <c r="A356" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>353</v>
       </c>
       <c r="D356" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B356, $M:$M, $N:$N), "00") &amp; TEXT(E356, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E356" s="10">
@@ -6955,11 +6980,11 @@
     </row>
     <row r="357" spans="1:5">
       <c r="A357" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>354</v>
       </c>
       <c r="D357" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B357, $M:$M, $N:$N), "00") &amp; TEXT(E357, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E357" s="10">
@@ -6969,11 +6994,11 @@
     </row>
     <row r="358" spans="1:5">
       <c r="A358" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>355</v>
       </c>
       <c r="D358" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B358, $M:$M, $N:$N), "00") &amp; TEXT(E358, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E358" s="10">
@@ -6983,11 +7008,11 @@
     </row>
     <row r="359" spans="1:5">
       <c r="A359" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>356</v>
       </c>
       <c r="D359" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B359, $M:$M, $N:$N), "00") &amp; TEXT(E359, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E359" s="10">
@@ -6997,11 +7022,11 @@
     </row>
     <row r="360" spans="1:5">
       <c r="A360" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>357</v>
       </c>
       <c r="D360" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B360, $M:$M, $N:$N), "00") &amp; TEXT(E360, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E360" s="10">
@@ -7011,11 +7036,11 @@
     </row>
     <row r="361" spans="1:5">
       <c r="A361" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>358</v>
       </c>
       <c r="D361" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B361, $M:$M, $N:$N), "00") &amp; TEXT(E361, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E361" s="10">
@@ -7025,11 +7050,11 @@
     </row>
     <row r="362" spans="1:5">
       <c r="A362" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>359</v>
       </c>
       <c r="D362" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B362, $M:$M, $N:$N), "00") &amp; TEXT(E362, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E362" s="10">
@@ -7039,11 +7064,11 @@
     </row>
     <row r="363" spans="1:5">
       <c r="A363" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>360</v>
       </c>
       <c r="D363" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B363, $M:$M, $N:$N), "00") &amp; TEXT(E363, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E363" s="10">
@@ -7053,11 +7078,11 @@
     </row>
     <row r="364" spans="1:5">
       <c r="A364" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>361</v>
       </c>
       <c r="D364" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B364, $M:$M, $N:$N), "00") &amp; TEXT(E364, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E364" s="10">
@@ -7067,11 +7092,11 @@
     </row>
     <row r="365" spans="1:5">
       <c r="A365" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>362</v>
       </c>
       <c r="D365" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B365, $M:$M, $N:$N), "00") &amp; TEXT(E365, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E365" s="10">
@@ -7081,11 +7106,11 @@
     </row>
     <row r="366" spans="1:5">
       <c r="A366" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>363</v>
       </c>
       <c r="D366" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B366, $M:$M, $N:$N), "00") &amp; TEXT(E366, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E366" s="10">
@@ -7095,11 +7120,11 @@
     </row>
     <row r="367" spans="1:5">
       <c r="A367" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>364</v>
       </c>
       <c r="D367" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B367, $M:$M, $N:$N), "00") &amp; TEXT(E367, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E367" s="10">
@@ -7109,11 +7134,11 @@
     </row>
     <row r="368" spans="1:5">
       <c r="A368" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>365</v>
       </c>
       <c r="D368" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B368, $M:$M, $N:$N), "00") &amp; TEXT(E368, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E368" s="10">
@@ -7123,11 +7148,11 @@
     </row>
     <row r="369" spans="1:5">
       <c r="A369" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>366</v>
       </c>
       <c r="D369" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B369, $M:$M, $N:$N), "00") &amp; TEXT(E369, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E369" s="10">
@@ -7137,11 +7162,11 @@
     </row>
     <row r="370" spans="1:5">
       <c r="A370" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>367</v>
       </c>
       <c r="D370" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B370, $M:$M, $N:$N), "00") &amp; TEXT(E370, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E370" s="10">
@@ -7151,11 +7176,11 @@
     </row>
     <row r="371" spans="1:5">
       <c r="A371" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>368</v>
       </c>
       <c r="D371" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B371, $M:$M, $N:$N), "00") &amp; TEXT(E371, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E371" s="10">
@@ -7165,11 +7190,11 @@
     </row>
     <row r="372" spans="1:5">
       <c r="A372" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>369</v>
       </c>
       <c r="D372" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B372, $M:$M, $N:$N), "00") &amp; TEXT(E372, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E372" s="10">
@@ -7179,11 +7204,11 @@
     </row>
     <row r="373" spans="1:5">
       <c r="A373" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>370</v>
       </c>
       <c r="D373" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B373, $M:$M, $N:$N), "00") &amp; TEXT(E373, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E373" s="10">
@@ -7193,11 +7218,11 @@
     </row>
     <row r="374" spans="1:5">
       <c r="A374" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>371</v>
       </c>
       <c r="D374" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B374, $M:$M, $N:$N), "00") &amp; TEXT(E374, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E374" s="10">
@@ -7207,11 +7232,11 @@
     </row>
     <row r="375" spans="1:5">
       <c r="A375" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>372</v>
       </c>
       <c r="D375" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B375, $M:$M, $N:$N), "00") &amp; TEXT(E375, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E375" s="10">
@@ -7221,11 +7246,11 @@
     </row>
     <row r="376" spans="1:5">
       <c r="A376" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>373</v>
       </c>
       <c r="D376" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B376, $M:$M, $N:$N), "00") &amp; TEXT(E376, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E376" s="10">
@@ -7235,11 +7260,11 @@
     </row>
     <row r="377" spans="1:5">
       <c r="A377" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>374</v>
       </c>
       <c r="D377" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B377, $M:$M, $N:$N), "00") &amp; TEXT(E377, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E377" s="10">
@@ -7249,11 +7274,11 @@
     </row>
     <row r="378" spans="1:5">
       <c r="A378" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>375</v>
       </c>
       <c r="D378" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B378, $M:$M, $N:$N), "00") &amp; TEXT(E378, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E378" s="10">
@@ -7263,11 +7288,11 @@
     </row>
     <row r="379" spans="1:5">
       <c r="A379" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>376</v>
       </c>
       <c r="D379" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B379, $M:$M, $N:$N), "00") &amp; TEXT(E379, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E379" s="10">
@@ -7277,11 +7302,11 @@
     </row>
     <row r="380" spans="1:5">
       <c r="A380" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>377</v>
       </c>
       <c r="D380" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B380, $M:$M, $N:$N), "00") &amp; TEXT(E380, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E380" s="10">
@@ -7291,11 +7316,11 @@
     </row>
     <row r="381" spans="1:5">
       <c r="A381" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>378</v>
       </c>
       <c r="D381" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B381, $M:$M, $N:$N), "00") &amp; TEXT(E381, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E381" s="10">
@@ -7305,11 +7330,11 @@
     </row>
     <row r="382" spans="1:5">
       <c r="A382" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>379</v>
       </c>
       <c r="D382" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B382, $M:$M, $N:$N), "00") &amp; TEXT(E382, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E382" s="10">
@@ -7319,11 +7344,11 @@
     </row>
     <row r="383" spans="1:5">
       <c r="A383" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>380</v>
       </c>
       <c r="D383" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B383, $M:$M, $N:$N), "00") &amp; TEXT(E383, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E383" s="10">
@@ -7333,11 +7358,11 @@
     </row>
     <row r="384" spans="1:5">
       <c r="A384" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>381</v>
       </c>
       <c r="D384" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B384, $M:$M, $N:$N), "00") &amp; TEXT(E384, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E384" s="10">
@@ -7347,11 +7372,11 @@
     </row>
     <row r="385" spans="1:5">
       <c r="A385" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>382</v>
       </c>
       <c r="D385" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B385, $M:$M, $N:$N), "00") &amp; TEXT(E385, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E385" s="10">
@@ -7361,11 +7386,11 @@
     </row>
     <row r="386" spans="1:5">
       <c r="A386" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>383</v>
       </c>
       <c r="D386" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B386, $M:$M, $N:$N), "00") &amp; TEXT(E386, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E386" s="10">
@@ -7375,11 +7400,11 @@
     </row>
     <row r="387" spans="1:5">
       <c r="A387" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>384</v>
       </c>
       <c r="D387" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B387, $M:$M, $N:$N), "00") &amp; TEXT(E387, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E387" s="10">
@@ -7389,11 +7414,11 @@
     </row>
     <row r="388" spans="1:5">
       <c r="A388" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>385</v>
       </c>
       <c r="D388" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B388, $M:$M, $N:$N), "00") &amp; TEXT(E388, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E388" s="10">
@@ -7403,11 +7428,11 @@
     </row>
     <row r="389" spans="1:5">
       <c r="A389" s="1">
-        <f t="shared" ref="A389:A443" si="7">A388+1</f>
+        <f t="shared" ref="A389:A443" si="18">A388+1</f>
         <v>386</v>
       </c>
       <c r="D389" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B389, $M:$M, $N:$N), "00") &amp; TEXT(E389, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E389" s="10">
@@ -7417,11 +7442,11 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>387</v>
       </c>
       <c r="D390" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B390, $M:$M, $N:$N), "00") &amp; TEXT(E390, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E390" s="10">
@@ -7431,11 +7456,11 @@
     </row>
     <row r="391" spans="1:5">
       <c r="A391" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>388</v>
       </c>
       <c r="D391" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B391, $M:$M, $N:$N), "00") &amp; TEXT(E391, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E391" s="10">
@@ -7445,11 +7470,11 @@
     </row>
     <row r="392" spans="1:5">
       <c r="A392" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>389</v>
       </c>
       <c r="D392" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B392, $M:$M, $N:$N), "00") &amp; TEXT(E392, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E392" s="10">
@@ -7459,11 +7484,11 @@
     </row>
     <row r="393" spans="1:5">
       <c r="A393" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>390</v>
       </c>
       <c r="D393" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B393, $M:$M, $N:$N), "00") &amp; TEXT(E393, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E393" s="10">
@@ -7473,11 +7498,11 @@
     </row>
     <row r="394" spans="1:5">
       <c r="A394" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>391</v>
       </c>
       <c r="D394" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B394, $M:$M, $N:$N), "00") &amp; TEXT(E394, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E394" s="10">
@@ -7487,11 +7512,11 @@
     </row>
     <row r="395" spans="1:5">
       <c r="A395" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>392</v>
       </c>
       <c r="D395" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B395, $M:$M, $N:$N), "00") &amp; TEXT(E395, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E395" s="10">
@@ -7501,11 +7526,11 @@
     </row>
     <row r="396" spans="1:5">
       <c r="A396" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>393</v>
       </c>
       <c r="D396" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B396, $M:$M, $N:$N), "00") &amp; TEXT(E396, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E396" s="10">
@@ -7515,11 +7540,11 @@
     </row>
     <row r="397" spans="1:5">
       <c r="A397" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>394</v>
       </c>
       <c r="D397" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B397, $M:$M, $N:$N), "00") &amp; TEXT(E397, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E397" s="10">
@@ -7529,11 +7554,11 @@
     </row>
     <row r="398" spans="1:5">
       <c r="A398" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>395</v>
       </c>
       <c r="D398" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B398, $M:$M, $N:$N), "00") &amp; TEXT(E398, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E398" s="10">
@@ -7543,11 +7568,11 @@
     </row>
     <row r="399" spans="1:5">
       <c r="A399" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>396</v>
       </c>
       <c r="D399" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B399, $M:$M, $N:$N), "00") &amp; TEXT(E399, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E399" s="10">
@@ -7557,11 +7582,11 @@
     </row>
     <row r="400" spans="1:5">
       <c r="A400" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>397</v>
       </c>
       <c r="D400" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B400, $M:$M, $N:$N), "00") &amp; TEXT(E400, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E400" s="10">
@@ -7571,11 +7596,11 @@
     </row>
     <row r="401" spans="1:5">
       <c r="A401" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>398</v>
       </c>
       <c r="D401" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B401, $M:$M, $N:$N), "00") &amp; TEXT(E401, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E401" s="10">
@@ -7585,11 +7610,11 @@
     </row>
     <row r="402" spans="1:5">
       <c r="A402" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>399</v>
       </c>
       <c r="D402" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B402, $M:$M, $N:$N), "00") &amp; TEXT(E402, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E402" s="10">
@@ -7599,11 +7624,11 @@
     </row>
     <row r="403" spans="1:5">
       <c r="A403" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>400</v>
       </c>
       <c r="D403" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B403, $M:$M, $N:$N), "00") &amp; TEXT(E403, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E403" s="10">
@@ -7613,11 +7638,11 @@
     </row>
     <row r="404" spans="1:5">
       <c r="A404" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>401</v>
       </c>
       <c r="D404" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B404, $M:$M, $N:$N), "00") &amp; TEXT(E404, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E404" s="10">
@@ -7627,11 +7652,11 @@
     </row>
     <row r="405" spans="1:5">
       <c r="A405" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>402</v>
       </c>
       <c r="D405" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B405, $M:$M, $N:$N), "00") &amp; TEXT(E405, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E405" s="10">
@@ -7641,11 +7666,11 @@
     </row>
     <row r="406" spans="1:5">
       <c r="A406" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>403</v>
       </c>
       <c r="D406" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B406, $M:$M, $N:$N), "00") &amp; TEXT(E406, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E406" s="10">
@@ -7655,11 +7680,11 @@
     </row>
     <row r="407" spans="1:5">
       <c r="A407" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>404</v>
       </c>
       <c r="D407" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B407, $M:$M, $N:$N), "00") &amp; TEXT(E407, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E407" s="10">
@@ -7669,11 +7694,11 @@
     </row>
     <row r="408" spans="1:5">
       <c r="A408" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>405</v>
       </c>
       <c r="D408" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B408, $M:$M, $N:$N), "00") &amp; TEXT(E408, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E408" s="10">
@@ -7683,11 +7708,11 @@
     </row>
     <row r="409" spans="1:5">
       <c r="A409" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>406</v>
       </c>
       <c r="D409" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B409, $M:$M, $N:$N), "00") &amp; TEXT(E409, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E409" s="10">
@@ -7697,11 +7722,11 @@
     </row>
     <row r="410" spans="1:5">
       <c r="A410" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>407</v>
       </c>
       <c r="D410" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B410, $M:$M, $N:$N), "00") &amp; TEXT(E410, "00"))</f>
+        <f t="shared" si="17"/>
         <v>#VALUE!</v>
       </c>
       <c r="E410" s="10">
@@ -7711,11 +7736,11 @@
     </row>
     <row r="411" spans="1:5">
       <c r="A411" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>408</v>
       </c>
       <c r="D411" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B411, $M:$M, $N:$N), "00") &amp; TEXT(E411, "00"))</f>
+        <f t="shared" ref="D411:D474" si="19">VALUE(TEXT(_xlfn.XLOOKUP(B411, $M:$M, $N:$N), "00") &amp; TEXT(E411, "00"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="E411" s="10">
@@ -7725,11 +7750,11 @@
     </row>
     <row r="412" spans="1:5">
       <c r="A412" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>409</v>
       </c>
       <c r="D412" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B412, $M:$M, $N:$N), "00") &amp; TEXT(E412, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E412" s="10">
@@ -7739,11 +7764,11 @@
     </row>
     <row r="413" spans="1:5">
       <c r="A413" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>410</v>
       </c>
       <c r="D413" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B413, $M:$M, $N:$N), "00") &amp; TEXT(E413, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E413" s="10">
@@ -7753,11 +7778,11 @@
     </row>
     <row r="414" spans="1:5">
       <c r="A414" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>411</v>
       </c>
       <c r="D414" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B414, $M:$M, $N:$N), "00") &amp; TEXT(E414, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E414" s="10">
@@ -7767,11 +7792,11 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>412</v>
       </c>
       <c r="D415" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B415, $M:$M, $N:$N), "00") &amp; TEXT(E415, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E415" s="10">
@@ -7781,11 +7806,11 @@
     </row>
     <row r="416" spans="1:5">
       <c r="A416" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>413</v>
       </c>
       <c r="D416" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B416, $M:$M, $N:$N), "00") &amp; TEXT(E416, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E416" s="10">
@@ -7795,11 +7820,11 @@
     </row>
     <row r="417" spans="1:5">
       <c r="A417" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>414</v>
       </c>
       <c r="D417" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B417, $M:$M, $N:$N), "00") &amp; TEXT(E417, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E417" s="10">
@@ -7809,11 +7834,11 @@
     </row>
     <row r="418" spans="1:5">
       <c r="A418" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>415</v>
       </c>
       <c r="D418" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B418, $M:$M, $N:$N), "00") &amp; TEXT(E418, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E418" s="10">
@@ -7823,11 +7848,11 @@
     </row>
     <row r="419" spans="1:5">
       <c r="A419" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>416</v>
       </c>
       <c r="D419" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B419, $M:$M, $N:$N), "00") &amp; TEXT(E419, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E419" s="10">
@@ -7837,11 +7862,11 @@
     </row>
     <row r="420" spans="1:5">
       <c r="A420" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>417</v>
       </c>
       <c r="D420" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B420, $M:$M, $N:$N), "00") &amp; TEXT(E420, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E420" s="10">
@@ -7851,11 +7876,11 @@
     </row>
     <row r="421" spans="1:5">
       <c r="A421" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>418</v>
       </c>
       <c r="D421" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B421, $M:$M, $N:$N), "00") &amp; TEXT(E421, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E421" s="10">
@@ -7865,11 +7890,11 @@
     </row>
     <row r="422" spans="1:5">
       <c r="A422" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>419</v>
       </c>
       <c r="D422" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B422, $M:$M, $N:$N), "00") &amp; TEXT(E422, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E422" s="10">
@@ -7879,11 +7904,11 @@
     </row>
     <row r="423" spans="1:5">
       <c r="A423" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>420</v>
       </c>
       <c r="D423" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B423, $M:$M, $N:$N), "00") &amp; TEXT(E423, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E423" s="10">
@@ -7893,11 +7918,11 @@
     </row>
     <row r="424" spans="1:5">
       <c r="A424" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>421</v>
       </c>
       <c r="D424" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B424, $M:$M, $N:$N), "00") &amp; TEXT(E424, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E424" s="10">
@@ -7907,11 +7932,11 @@
     </row>
     <row r="425" spans="1:5">
       <c r="A425" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>422</v>
       </c>
       <c r="D425" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B425, $M:$M, $N:$N), "00") &amp; TEXT(E425, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E425" s="10">
@@ -7921,11 +7946,11 @@
     </row>
     <row r="426" spans="1:5">
       <c r="A426" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>423</v>
       </c>
       <c r="D426" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B426, $M:$M, $N:$N), "00") &amp; TEXT(E426, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E426" s="10">
@@ -7935,11 +7960,11 @@
     </row>
     <row r="427" spans="1:5">
       <c r="A427" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>424</v>
       </c>
       <c r="D427" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B427, $M:$M, $N:$N), "00") &amp; TEXT(E427, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E427" s="10">
@@ -7949,11 +7974,11 @@
     </row>
     <row r="428" spans="1:5">
       <c r="A428" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>425</v>
       </c>
       <c r="D428" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B428, $M:$M, $N:$N), "00") &amp; TEXT(E428, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E428" s="10">
@@ -7963,11 +7988,11 @@
     </row>
     <row r="429" spans="1:5">
       <c r="A429" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>426</v>
       </c>
       <c r="D429" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B429, $M:$M, $N:$N), "00") &amp; TEXT(E429, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E429" s="10">
@@ -7977,11 +8002,11 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>427</v>
       </c>
       <c r="D430" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B430, $M:$M, $N:$N), "00") &amp; TEXT(E430, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E430" s="10">
@@ -7991,11 +8016,11 @@
     </row>
     <row r="431" spans="1:5">
       <c r="A431" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>428</v>
       </c>
       <c r="D431" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B431, $M:$M, $N:$N), "00") &amp; TEXT(E431, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E431" s="10">
@@ -8005,11 +8030,11 @@
     </row>
     <row r="432" spans="1:5">
       <c r="A432" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>429</v>
       </c>
       <c r="D432" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B432, $M:$M, $N:$N), "00") &amp; TEXT(E432, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E432" s="10">
@@ -8019,11 +8044,11 @@
     </row>
     <row r="433" spans="1:5">
       <c r="A433" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>430</v>
       </c>
       <c r="D433" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B433, $M:$M, $N:$N), "00") &amp; TEXT(E433, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E433" s="10">
@@ -8033,11 +8058,11 @@
     </row>
     <row r="434" spans="1:5">
       <c r="A434" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>431</v>
       </c>
       <c r="D434" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B434, $M:$M, $N:$N), "00") &amp; TEXT(E434, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E434" s="10">
@@ -8047,11 +8072,11 @@
     </row>
     <row r="435" spans="1:5">
       <c r="A435" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>432</v>
       </c>
       <c r="D435" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B435, $M:$M, $N:$N), "00") &amp; TEXT(E435, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E435" s="10">
@@ -8061,11 +8086,11 @@
     </row>
     <row r="436" spans="1:5">
       <c r="A436" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>433</v>
       </c>
       <c r="D436" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B436, $M:$M, $N:$N), "00") &amp; TEXT(E436, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E436" s="10">
@@ -8075,11 +8100,11 @@
     </row>
     <row r="437" spans="1:5">
       <c r="A437" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>434</v>
       </c>
       <c r="D437" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B437, $M:$M, $N:$N), "00") &amp; TEXT(E437, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E437" s="10">
@@ -8089,11 +8114,11 @@
     </row>
     <row r="438" spans="1:5">
       <c r="A438" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>435</v>
       </c>
       <c r="D438" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B438, $M:$M, $N:$N), "00") &amp; TEXT(E438, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E438" s="10">
@@ -8103,11 +8128,11 @@
     </row>
     <row r="439" spans="1:5">
       <c r="A439" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>436</v>
       </c>
       <c r="D439" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B439, $M:$M, $N:$N), "00") &amp; TEXT(E439, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E439" s="10">
@@ -8117,11 +8142,11 @@
     </row>
     <row r="440" spans="1:5">
       <c r="A440" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>437</v>
       </c>
       <c r="D440" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B440, $M:$M, $N:$N), "00") &amp; TEXT(E440, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E440" s="10">
@@ -8131,11 +8156,11 @@
     </row>
     <row r="441" spans="1:5">
       <c r="A441" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>438</v>
       </c>
       <c r="D441" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B441, $M:$M, $N:$N), "00") &amp; TEXT(E441, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E441" s="10">
@@ -8145,11 +8170,11 @@
     </row>
     <row r="442" spans="1:5">
       <c r="A442" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>439</v>
       </c>
       <c r="D442" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B442, $M:$M, $N:$N), "00") &amp; TEXT(E442, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E442" s="10">
@@ -8159,11 +8184,11 @@
     </row>
     <row r="443" spans="1:5">
       <c r="A443" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="18"/>
         <v>440</v>
       </c>
       <c r="D443" s="2" t="e">
-        <f>VALUE(TEXT(_xlfn.XLOOKUP(B443, $M:$M, $N:$N), "00") &amp; TEXT(E443, "00"))</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E443" s="10">
@@ -8173,13 +8198,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D155:D1001 D2:D153">
+  <conditionalFormatting sqref="D2:D153 D155:D1001">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>COUNTIF($D:$D, D2) &gt; 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C153 C155:C443" xr:uid="{A0C9F4D0-9B68-44D9-B8DD-944F863FFED9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C155:C443 C2:C153" xr:uid="{A0C9F4D0-9B68-44D9-B8DD-944F863FFED9}">
       <formula1>$L$2:$L$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B153 B155:B443" xr:uid="{70750F9B-83E2-4167-B52A-B7919A8F4E08}">

--- a/Assets/AddressableResource/Data/Excels/CardData.xlsx
+++ b/Assets/AddressableResource/Data/Excels/CardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\AddressableResource\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881C999A-048D-416A-BA01-8B075E8F0526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A556B4-66C9-47A4-803A-5EE6951903E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="57">
   <si>
     <t>Normal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,6 +219,16 @@
     <t>적당히 넣을것</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>마지막 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
 </sst>
 </file>
 
@@ -283,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,6 +314,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -342,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -400,6 +416,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -721,7 +746,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q443"/>
+  <dimension ref="A1:Q258"/>
   <sheetFormatPr defaultColWidth="17.625" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="3" width="18.25" style="2" customWidth="1"/>
@@ -773,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <f t="shared" ref="D2:D33" si="0">VALUE(TEXT(_xlfn.XLOOKUP(B2, $M:$M, $N:$N), "00") &amp; TEXT(E2, "00"))</f>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B2, $M:$M, $N:$N), "00") &amp; TEXT(E2, "00"))</f>
         <v>100</v>
       </c>
       <c r="E2" s="10">
@@ -783,8 +808,8 @@
       <c r="F2" s="1"/>
       <c r="G2" s="4"/>
       <c r="K2" s="2">
-        <f t="shared" ref="K2:K7" si="1">COUNTIF(C:C,L2)</f>
-        <v>75</v>
+        <f>COUNTIF(C:C,L2)</f>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>31</v>
@@ -796,8 +821,8 @@
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <f t="shared" ref="O2:O28" si="2">COUNTIF(B:B,M2)</f>
-        <v>2</v>
+        <f>COUNTIF(B:B,M2)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -812,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B3, $M:$M, $N:$N), "00") &amp; TEXT(E3, "00"))</f>
         <v>200</v>
       </c>
       <c r="E3" s="10">
@@ -822,8 +847,8 @@
       <c r="F3" s="3"/>
       <c r="G3" s="4"/>
       <c r="K3" s="2">
-        <f t="shared" si="1"/>
-        <v>24</v>
+        <f>COUNTIF(C:C,L3)</f>
+        <v>45</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>32</v>
@@ -835,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>COUNTIF(B:B,M3)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
-        <f t="shared" ref="A4:A67" si="3">A3+1</f>
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -851,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B4, $M:$M, $N:$N), "00") &amp; TEXT(E4, "00"))</f>
         <v>300</v>
       </c>
       <c r="E4" s="10">
@@ -860,8 +885,8 @@
       </c>
       <c r="F4" s="1"/>
       <c r="K4" s="2">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <f>COUNTIF(C:C,L4)</f>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>33</v>
@@ -873,13 +898,13 @@
         <v>2</v>
       </c>
       <c r="O4" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M4)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -889,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B5, $M:$M, $N:$N), "00") &amp; TEXT(E5, "00"))</f>
         <v>400</v>
       </c>
       <c r="E5" s="10">
@@ -898,8 +923,8 @@
       </c>
       <c r="F5" s="1"/>
       <c r="K5" s="2">
-        <f t="shared" si="1"/>
-        <v>31</v>
+        <f>COUNTIF(C:C,L5)</f>
+        <v>51</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>34</v>
@@ -911,13 +936,13 @@
         <v>3</v>
       </c>
       <c r="O5" s="5">
-        <f t="shared" si="2"/>
-        <v>8</v>
+        <f>COUNTIF(B:B,M5)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -927,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B6, $M:$M, $N:$N), "00") &amp; TEXT(E6, "00"))</f>
         <v>500</v>
       </c>
       <c r="E6" s="10">
@@ -936,8 +961,8 @@
       </c>
       <c r="F6" s="1"/>
       <c r="K6" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <f>COUNTIF(C:C,L6)</f>
+        <v>38</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>35</v>
@@ -949,13 +974,13 @@
         <v>4</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M6)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -965,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B7, $M:$M, $N:$N), "00") &amp; TEXT(E7, "00"))</f>
         <v>600</v>
       </c>
       <c r="E7" s="10">
@@ -974,8 +999,8 @@
       </c>
       <c r="F7" s="1"/>
       <c r="K7" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f>COUNTIF(C:C,L7)</f>
+        <v>11</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>36</v>
@@ -987,13 +1012,13 @@
         <v>5</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M7)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1003,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B8, $M:$M, $N:$N), "00") &amp; TEXT(E8, "00"))</f>
         <v>700</v>
       </c>
       <c r="E8" s="10">
@@ -1017,13 +1042,13 @@
         <v>6</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M8)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1033,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B9, $M:$M, $N:$N), "00") &amp; TEXT(E9, "00"))</f>
         <v>800</v>
       </c>
       <c r="E9" s="10">
@@ -1047,13 +1072,13 @@
         <v>7</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M9)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1063,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B10, $M:$M, $N:$N), "00") &amp; TEXT(E10, "00"))</f>
         <v>900</v>
       </c>
       <c r="E10" s="10">
@@ -1077,13 +1102,13 @@
         <v>8</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f>COUNTIF(B:B,M10)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1093,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B11, $M:$M, $N:$N), "00") &amp; TEXT(E11, "00"))</f>
         <v>1000</v>
       </c>
       <c r="E11" s="10">
@@ -1107,13 +1132,13 @@
         <v>9</v>
       </c>
       <c r="O11" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M11)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1123,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B12, $M:$M, $N:$N), "00") &amp; TEXT(E12, "00"))</f>
         <v>1100</v>
       </c>
       <c r="E12" s="10">
@@ -1137,13 +1162,13 @@
         <v>10</v>
       </c>
       <c r="O12" s="5">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f>COUNTIF(B:B,M12)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1153,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B13, $M:$M, $N:$N), "00") &amp; TEXT(E13, "00"))</f>
         <v>1200</v>
       </c>
       <c r="E13" s="10">
@@ -1167,13 +1192,13 @@
         <v>11</v>
       </c>
       <c r="O13" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M13)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1183,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B14, $M:$M, $N:$N), "00") &amp; TEXT(E14, "00"))</f>
         <v>1300</v>
       </c>
       <c r="E14" s="10">
@@ -1197,13 +1222,13 @@
         <v>12</v>
       </c>
       <c r="O14" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M14)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1213,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B15, $M:$M, $N:$N), "00") &amp; TEXT(E15, "00"))</f>
         <v>1400</v>
       </c>
       <c r="E15" s="10">
@@ -1227,13 +1252,13 @@
         <v>13</v>
       </c>
       <c r="O15" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f>COUNTIF(B:B,M15)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1243,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B16, $M:$M, $N:$N), "00") &amp; TEXT(E16, "00"))</f>
         <v>1500</v>
       </c>
       <c r="E16" s="10">
@@ -1257,13 +1282,13 @@
         <v>14</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M16)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1273,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B17, $M:$M, $N:$N), "00") &amp; TEXT(E17, "00"))</f>
         <v>1600</v>
       </c>
       <c r="E17" s="10">
@@ -1287,13 +1312,13 @@
         <v>15</v>
       </c>
       <c r="O17" s="5">
-        <f t="shared" si="2"/>
-        <v>8</v>
+        <f>COUNTIF(B:B,M17)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1303,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B18, $M:$M, $N:$N), "00") &amp; TEXT(E18, "00"))</f>
         <v>1700</v>
       </c>
       <c r="E18" s="10">
@@ -1317,13 +1342,13 @@
         <v>16</v>
       </c>
       <c r="O18" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f>COUNTIF(B:B,M18)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1333,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B19, $M:$M, $N:$N), "00") &amp; TEXT(E19, "00"))</f>
         <v>1800</v>
       </c>
       <c r="E19" s="10">
@@ -1347,13 +1372,13 @@
         <v>17</v>
       </c>
       <c r="O19" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M19)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1363,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B20, $M:$M, $N:$N), "00") &amp; TEXT(E20, "00"))</f>
         <v>1900</v>
       </c>
       <c r="E20" s="10">
@@ -1377,13 +1402,13 @@
         <v>18</v>
       </c>
       <c r="O20" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M20)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1393,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B21, $M:$M, $N:$N), "00") &amp; TEXT(E21, "00"))</f>
         <v>2000</v>
       </c>
       <c r="E21" s="10">
@@ -1407,13 +1432,13 @@
         <v>19</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f>COUNTIF(B:B,M21)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1423,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B22, $M:$M, $N:$N), "00") &amp; TEXT(E22, "00"))</f>
         <v>2100</v>
       </c>
       <c r="E22" s="10">
@@ -1437,13 +1462,13 @@
         <v>20</v>
       </c>
       <c r="O22" s="5">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f>COUNTIF(B:B,M22)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1453,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B23, $M:$M, $N:$N), "00") &amp; TEXT(E23, "00"))</f>
         <v>2200</v>
       </c>
       <c r="E23" s="10">
@@ -1467,13 +1492,13 @@
         <v>21</v>
       </c>
       <c r="O23" s="5">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <f>COUNTIF(B:B,M23)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1483,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B24, $M:$M, $N:$N), "00") &amp; TEXT(E24, "00"))</f>
         <v>2300</v>
       </c>
       <c r="E24" s="10">
@@ -1497,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="O24" s="5">
-        <f t="shared" si="2"/>
-        <v>8</v>
+        <f>COUNTIF(B:B,M24)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1513,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B25, $M:$M, $N:$N), "00") &amp; TEXT(E25, "00"))</f>
         <v>2400</v>
       </c>
       <c r="E25" s="10">
@@ -1527,13 +1552,13 @@
         <v>23</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f>COUNTIF(B:B,M25)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -1543,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B26, $M:$M, $N:$N), "00") &amp; TEXT(E26, "00"))</f>
         <v>2500</v>
       </c>
       <c r="E26" s="10">
@@ -1557,13 +1582,13 @@
         <v>24</v>
       </c>
       <c r="O26" s="5">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f>COUNTIF(B:B,M26)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1573,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B27, $M:$M, $N:$N), "00") &amp; TEXT(E27, "00"))</f>
         <v>2600</v>
       </c>
       <c r="E27" s="10">
@@ -1587,13 +1612,13 @@
         <v>25</v>
       </c>
       <c r="O27" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M27)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1603,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B28, $M:$M, $N:$N), "00") &amp; TEXT(E28, "00"))</f>
         <v>0</v>
       </c>
       <c r="E28" s="10">
@@ -1617,13 +1642,13 @@
         <v>26</v>
       </c>
       <c r="O28" s="5">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <f>COUNTIF(B:B,M28)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -1633,7 +1658,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B29, $M:$M, $N:$N), "00") &amp; TEXT(E29, "00"))</f>
         <v>101</v>
       </c>
       <c r="E29" s="10">
@@ -1643,7 +1668,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -1653,7 +1678,7 @@
         <v>32</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B30, $M:$M, $N:$N), "00") &amp; TEXT(E30, "00"))</f>
         <v>102</v>
       </c>
       <c r="E30" s="10">
@@ -1663,7 +1688,7 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -1673,7 +1698,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B31, $M:$M, $N:$N), "00") &amp; TEXT(E31, "00"))</f>
         <v>103</v>
       </c>
       <c r="E31" s="10">
@@ -1683,7 +1708,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -1693,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B32, $M:$M, $N:$N), "00") &amp; TEXT(E32, "00"))</f>
         <v>104</v>
       </c>
       <c r="E32" s="10">
@@ -1703,7 +1728,7 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -1713,7 +1738,7 @@
         <v>33</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="0"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B33, $M:$M, $N:$N), "00") &amp; TEXT(E33, "00"))</f>
         <v>105</v>
       </c>
       <c r="E33" s="10">
@@ -1723,7 +1748,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1733,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" ref="D34:D65" si="4">VALUE(TEXT(_xlfn.XLOOKUP(B34, $M:$M, $N:$N), "00") &amp; TEXT(E34, "00"))</f>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B34, $M:$M, $N:$N), "00") &amp; TEXT(E34, "00"))</f>
         <v>106</v>
       </c>
       <c r="E34" s="10">
@@ -1743,7 +1768,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -1753,7 +1778,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B35, $M:$M, $N:$N), "00") &amp; TEXT(E35, "00"))</f>
         <v>107</v>
       </c>
       <c r="E35" s="10">
@@ -1763,7 +1788,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -1773,7 +1798,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B36, $M:$M, $N:$N), "00") &amp; TEXT(E36, "00"))</f>
         <v>108</v>
       </c>
       <c r="E36" s="10">
@@ -1783,7 +1808,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -1793,7 +1818,7 @@
         <v>35</v>
       </c>
       <c r="D37" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B37, $M:$M, $N:$N), "00") &amp; TEXT(E37, "00"))</f>
         <v>109</v>
       </c>
       <c r="E37" s="10">
@@ -1803,7 +1828,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -1813,7 +1838,7 @@
         <v>35</v>
       </c>
       <c r="D38" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B38, $M:$M, $N:$N), "00") &amp; TEXT(E38, "00"))</f>
         <v>110</v>
       </c>
       <c r="E38" s="10">
@@ -1824,7 +1849,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -1834,7 +1859,7 @@
         <v>36</v>
       </c>
       <c r="D39" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B39, $M:$M, $N:$N), "00") &amp; TEXT(E39, "00"))</f>
         <v>111</v>
       </c>
       <c r="E39" s="10">
@@ -1845,7 +1870,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -1855,7 +1880,7 @@
         <v>36</v>
       </c>
       <c r="D40" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B40, $M:$M, $N:$N), "00") &amp; TEXT(E40, "00"))</f>
         <v>112</v>
       </c>
       <c r="E40" s="10">
@@ -1866,7 +1891,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -1876,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B41, $M:$M, $N:$N), "00") &amp; TEXT(E41, "00"))</f>
         <v>301</v>
       </c>
       <c r="E41" s="10">
@@ -1886,7 +1911,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -1896,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="D42" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B42, $M:$M, $N:$N), "00") &amp; TEXT(E42, "00"))</f>
         <v>302</v>
       </c>
       <c r="E42" s="10">
@@ -1906,7 +1931,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -1916,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B43, $M:$M, $N:$N), "00") &amp; TEXT(E43, "00"))</f>
         <v>303</v>
       </c>
       <c r="E43" s="10">
@@ -1926,7 +1951,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -1936,7 +1961,7 @@
         <v>2</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B44, $M:$M, $N:$N), "00") &amp; TEXT(E44, "00"))</f>
         <v>401</v>
       </c>
       <c r="E44" s="10">
@@ -1946,7 +1971,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -1956,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="D45" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B45, $M:$M, $N:$N), "00") &amp; TEXT(E45, "00"))</f>
         <v>801</v>
       </c>
       <c r="E45" s="10">
@@ -1966,7 +1991,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -1976,7 +2001,7 @@
         <v>36</v>
       </c>
       <c r="D46" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B46, $M:$M, $N:$N), "00") &amp; TEXT(E46, "00"))</f>
         <v>1001</v>
       </c>
       <c r="E46" s="10">
@@ -1986,7 +2011,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1996,7 +2021,7 @@
         <v>34</v>
       </c>
       <c r="D47" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B47, $M:$M, $N:$N), "00") &amp; TEXT(E47, "00"))</f>
         <v>1301</v>
       </c>
       <c r="E47" s="10">
@@ -2006,7 +2031,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -2016,7 +2041,7 @@
         <v>35</v>
       </c>
       <c r="D48" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B48, $M:$M, $N:$N), "00") &amp; TEXT(E48, "00"))</f>
         <v>1302</v>
       </c>
       <c r="E48" s="10">
@@ -2027,7 +2052,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -2037,7 +2062,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B49, $M:$M, $N:$N), "00") &amp; TEXT(E49, "00"))</f>
         <v>1601</v>
       </c>
       <c r="E49" s="10">
@@ -2047,7 +2072,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -2057,7 +2082,7 @@
         <v>36</v>
       </c>
       <c r="D50" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B50, $M:$M, $N:$N), "00") &amp; TEXT(E50, "00"))</f>
         <v>1602</v>
       </c>
       <c r="E50" s="10">
@@ -2067,7 +2092,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -2077,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B51, $M:$M, $N:$N), "00") &amp; TEXT(E51, "00"))</f>
         <v>1901</v>
       </c>
       <c r="E51" s="10">
@@ -2087,7 +2112,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -2097,7 +2122,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B52, $M:$M, $N:$N), "00") &amp; TEXT(E52, "00"))</f>
         <v>2201</v>
       </c>
       <c r="E52" s="10">
@@ -2107,7 +2132,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -2117,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B53, $M:$M, $N:$N), "00") &amp; TEXT(E53, "00"))</f>
         <v>1</v>
       </c>
       <c r="E53" s="10">
@@ -2128,7 +2153,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -2138,7 +2163,7 @@
         <v>34</v>
       </c>
       <c r="D54" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B54, $M:$M, $N:$N), "00") &amp; TEXT(E54, "00"))</f>
         <v>2202</v>
       </c>
       <c r="E54" s="10">
@@ -2148,7 +2173,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -2158,7 +2183,7 @@
         <v>2</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B55, $M:$M, $N:$N), "00") &amp; TEXT(E55, "00"))</f>
         <v>2301</v>
       </c>
       <c r="E55" s="10">
@@ -2168,7 +2193,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -2178,7 +2203,7 @@
         <v>34</v>
       </c>
       <c r="D56" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B56, $M:$M, $N:$N), "00") &amp; TEXT(E56, "00"))</f>
         <v>2302</v>
       </c>
       <c r="E56" s="10">
@@ -2188,7 +2213,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -2198,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B57, $M:$M, $N:$N), "00") &amp; TEXT(E57, "00"))</f>
         <v>2401</v>
       </c>
       <c r="E57" s="10">
@@ -2208,7 +2233,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -2218,7 +2243,7 @@
         <v>35</v>
       </c>
       <c r="D58" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B58, $M:$M, $N:$N), "00") &amp; TEXT(E58, "00"))</f>
         <v>2402</v>
       </c>
       <c r="E58" s="10">
@@ -2228,7 +2253,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -2238,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B59, $M:$M, $N:$N), "00") &amp; TEXT(E59, "00"))</f>
         <v>304</v>
       </c>
       <c r="E59" s="10">
@@ -2248,7 +2273,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -2258,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="D60" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B60, $M:$M, $N:$N), "00") &amp; TEXT(E60, "00"))</f>
         <v>402</v>
       </c>
       <c r="E60" s="10">
@@ -2268,7 +2293,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -2278,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B61, $M:$M, $N:$N), "00") &amp; TEXT(E61, "00"))</f>
         <v>501</v>
       </c>
       <c r="E61" s="10">
@@ -2288,7 +2313,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -2298,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B62, $M:$M, $N:$N), "00") &amp; TEXT(E62, "00"))</f>
         <v>601</v>
       </c>
       <c r="E62" s="10">
@@ -2308,7 +2333,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -2318,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="D63" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B63, $M:$M, $N:$N), "00") &amp; TEXT(E63, "00"))</f>
         <v>701</v>
       </c>
       <c r="E63" s="10">
@@ -2328,7 +2353,7 @@
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -2338,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B64, $M:$M, $N:$N), "00") &amp; TEXT(E64, "00"))</f>
         <v>802</v>
       </c>
       <c r="E64" s="10">
@@ -2348,7 +2373,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -2358,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="2">
-        <f t="shared" si="4"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B65, $M:$M, $N:$N), "00") &amp; TEXT(E65, "00"))</f>
         <v>901</v>
       </c>
       <c r="E65" s="10">
@@ -2368,7 +2393,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -2378,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="2">
-        <f t="shared" ref="D66:D97" si="5">VALUE(TEXT(_xlfn.XLOOKUP(B66, $M:$M, $N:$N), "00") &amp; TEXT(E66, "00"))</f>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B66, $M:$M, $N:$N), "00") &amp; TEXT(E66, "00"))</f>
         <v>1002</v>
       </c>
       <c r="E66" s="10">
@@ -2388,7 +2413,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -2398,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B67, $M:$M, $N:$N), "00") &amp; TEXT(E67, "00"))</f>
         <v>1101</v>
       </c>
       <c r="E67" s="10">
@@ -2408,7 +2433,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1">
-        <f t="shared" ref="A68:A132" si="6">A67+1</f>
+        <f t="shared" ref="A68:A132" si="1">A67+1</f>
         <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -2418,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B68, $M:$M, $N:$N), "00") &amp; TEXT(E68, "00"))</f>
         <v>1201</v>
       </c>
       <c r="E68" s="10">
@@ -2428,7 +2453,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -2438,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B69, $M:$M, $N:$N), "00") &amp; TEXT(E69, "00"))</f>
         <v>1303</v>
       </c>
       <c r="E69" s="10">
@@ -2448,7 +2473,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -2458,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B70, $M:$M, $N:$N), "00") &amp; TEXT(E70, "00"))</f>
         <v>1401</v>
       </c>
       <c r="E70" s="10">
@@ -2468,7 +2493,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -2478,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B71, $M:$M, $N:$N), "00") &amp; TEXT(E71, "00"))</f>
         <v>1501</v>
       </c>
       <c r="E71" s="10">
@@ -2488,7 +2513,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -2498,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B72, $M:$M, $N:$N), "00") &amp; TEXT(E72, "00"))</f>
         <v>1603</v>
       </c>
       <c r="E72" s="10">
@@ -2508,7 +2533,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -2518,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B73, $M:$M, $N:$N), "00") &amp; TEXT(E73, "00"))</f>
         <v>1701</v>
       </c>
       <c r="E73" s="10">
@@ -2528,7 +2553,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -2538,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B74, $M:$M, $N:$N), "00") &amp; TEXT(E74, "00"))</f>
         <v>1801</v>
       </c>
       <c r="E74" s="10">
@@ -2548,7 +2573,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -2558,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B75, $M:$M, $N:$N), "00") &amp; TEXT(E75, "00"))</f>
         <v>1902</v>
       </c>
       <c r="E75" s="10">
@@ -2568,7 +2593,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -2578,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B76, $M:$M, $N:$N), "00") &amp; TEXT(E76, "00"))</f>
         <v>2101</v>
       </c>
       <c r="E76" s="10">
@@ -2588,7 +2613,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -2598,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B77, $M:$M, $N:$N), "00") &amp; TEXT(E77, "00"))</f>
         <v>2203</v>
       </c>
       <c r="E77" s="10">
@@ -2608,7 +2633,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -2618,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B78, $M:$M, $N:$N), "00") &amp; TEXT(E78, "00"))</f>
         <v>2303</v>
       </c>
       <c r="E78" s="10">
@@ -2628,7 +2653,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -2638,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B79, $M:$M, $N:$N), "00") &amp; TEXT(E79, "00"))</f>
         <v>2403</v>
       </c>
       <c r="E79" s="10">
@@ -2648,7 +2673,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -2658,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B80, $M:$M, $N:$N), "00") &amp; TEXT(E80, "00"))</f>
         <v>2601</v>
       </c>
       <c r="E80" s="10">
@@ -2668,7 +2693,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -2678,7 +2703,7 @@
         <v>32</v>
       </c>
       <c r="D81" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B81, $M:$M, $N:$N), "00") &amp; TEXT(E81, "00"))</f>
         <v>201</v>
       </c>
       <c r="E81" s="10">
@@ -2688,7 +2713,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -2698,7 +2723,7 @@
         <v>32</v>
       </c>
       <c r="D82" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B82, $M:$M, $N:$N), "00") &amp; TEXT(E82, "00"))</f>
         <v>502</v>
       </c>
       <c r="E82" s="10">
@@ -2708,7 +2733,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -2718,7 +2743,7 @@
         <v>32</v>
       </c>
       <c r="D83" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B83, $M:$M, $N:$N), "00") &amp; TEXT(E83, "00"))</f>
         <v>803</v>
       </c>
       <c r="E83" s="10">
@@ -2728,7 +2753,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -2738,7 +2763,7 @@
         <v>32</v>
       </c>
       <c r="D84" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B84, $M:$M, $N:$N), "00") &amp; TEXT(E84, "00"))</f>
         <v>1003</v>
       </c>
       <c r="E84" s="10">
@@ -2748,7 +2773,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -2758,7 +2783,7 @@
         <v>32</v>
       </c>
       <c r="D85" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B85, $M:$M, $N:$N), "00") &amp; TEXT(E85, "00"))</f>
         <v>1202</v>
       </c>
       <c r="E85" s="10">
@@ -2768,7 +2793,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -2778,7 +2803,7 @@
         <v>32</v>
       </c>
       <c r="D86" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B86, $M:$M, $N:$N), "00") &amp; TEXT(E86, "00"))</f>
         <v>1304</v>
       </c>
       <c r="E86" s="10">
@@ -2788,7 +2813,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -2798,7 +2823,7 @@
         <v>32</v>
       </c>
       <c r="D87" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B87, $M:$M, $N:$N), "00") &amp; TEXT(E87, "00"))</f>
         <v>1402</v>
       </c>
       <c r="E87" s="10">
@@ -2808,7 +2833,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -2818,7 +2843,7 @@
         <v>32</v>
       </c>
       <c r="D88" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B88, $M:$M, $N:$N), "00") &amp; TEXT(E88, "00"))</f>
         <v>1502</v>
       </c>
       <c r="E88" s="10">
@@ -2828,7 +2853,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -2838,7 +2863,7 @@
         <v>32</v>
       </c>
       <c r="D89" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B89, $M:$M, $N:$N), "00") &amp; TEXT(E89, "00"))</f>
         <v>1503</v>
       </c>
       <c r="E89" s="10">
@@ -2848,7 +2873,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -2858,7 +2883,7 @@
         <v>32</v>
       </c>
       <c r="D90" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B90, $M:$M, $N:$N), "00") &amp; TEXT(E90, "00"))</f>
         <v>1504</v>
       </c>
       <c r="E90" s="10">
@@ -2868,7 +2893,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -2878,7 +2903,7 @@
         <v>32</v>
       </c>
       <c r="D91" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B91, $M:$M, $N:$N), "00") &amp; TEXT(E91, "00"))</f>
         <v>1604</v>
       </c>
       <c r="E91" s="10">
@@ -2888,7 +2913,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -2898,7 +2923,7 @@
         <v>32</v>
       </c>
       <c r="D92" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B92, $M:$M, $N:$N), "00") &amp; TEXT(E92, "00"))</f>
         <v>2102</v>
       </c>
       <c r="E92" s="10">
@@ -2908,7 +2933,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -2918,7 +2943,7 @@
         <v>32</v>
       </c>
       <c r="D93" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B93, $M:$M, $N:$N), "00") &amp; TEXT(E93, "00"))</f>
         <v>2204</v>
       </c>
       <c r="E93" s="10">
@@ -2928,7 +2953,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -2938,7 +2963,7 @@
         <v>32</v>
       </c>
       <c r="D94" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B94, $M:$M, $N:$N), "00") &amp; TEXT(E94, "00"))</f>
         <v>2404</v>
       </c>
       <c r="E94" s="10">
@@ -2948,7 +2973,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -2958,7 +2983,7 @@
         <v>33</v>
       </c>
       <c r="D95" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B95, $M:$M, $N:$N), "00") &amp; TEXT(E95, "00"))</f>
         <v>305</v>
       </c>
       <c r="E95" s="10">
@@ -2968,7 +2993,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -2978,7 +3003,7 @@
         <v>33</v>
       </c>
       <c r="D96" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B96, $M:$M, $N:$N), "00") &amp; TEXT(E96, "00"))</f>
         <v>1505</v>
       </c>
       <c r="E96" s="10">
@@ -2988,7 +3013,7 @@
     </row>
     <row r="97" spans="1:17">
       <c r="A97" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -2998,7 +3023,7 @@
         <v>33</v>
       </c>
       <c r="D97" s="2">
-        <f t="shared" si="5"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B97, $M:$M, $N:$N), "00") &amp; TEXT(E97, "00"))</f>
         <v>1702</v>
       </c>
       <c r="E97" s="10">
@@ -3008,7 +3033,7 @@
     </row>
     <row r="98" spans="1:17">
       <c r="A98" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -3018,7 +3043,7 @@
         <v>33</v>
       </c>
       <c r="D98" s="2">
-        <f t="shared" ref="D98:D129" si="7">VALUE(TEXT(_xlfn.XLOOKUP(B98, $M:$M, $N:$N), "00") &amp; TEXT(E98, "00"))</f>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B98, $M:$M, $N:$N), "00") &amp; TEXT(E98, "00"))</f>
         <v>2103</v>
       </c>
       <c r="E98" s="10">
@@ -3028,7 +3053,7 @@
     </row>
     <row r="99" spans="1:17">
       <c r="A99" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -3038,7 +3063,7 @@
         <v>33</v>
       </c>
       <c r="D99" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B99, $M:$M, $N:$N), "00") &amp; TEXT(E99, "00"))</f>
         <v>2205</v>
       </c>
       <c r="E99" s="10">
@@ -3048,7 +3073,7 @@
     </row>
     <row r="100" spans="1:17">
       <c r="A100" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -3058,7 +3083,7 @@
         <v>33</v>
       </c>
       <c r="D100" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B100, $M:$M, $N:$N), "00") &amp; TEXT(E100, "00"))</f>
         <v>2304</v>
       </c>
       <c r="E100" s="10">
@@ -3068,7 +3093,7 @@
     </row>
     <row r="101" spans="1:17">
       <c r="A101" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -3078,7 +3103,7 @@
         <v>33</v>
       </c>
       <c r="D101" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B101, $M:$M, $N:$N), "00") &amp; TEXT(E101, "00"))</f>
         <v>2501</v>
       </c>
       <c r="E101" s="10">
@@ -3088,7 +3113,7 @@
     </row>
     <row r="102" spans="1:17" s="17" customFormat="1">
       <c r="A102" s="16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B102" s="17" t="s">
@@ -3098,7 +3123,7 @@
         <v>31</v>
       </c>
       <c r="D102" s="17">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B102, $M:$M, $N:$N), "00") &amp; TEXT(E102, "00"))</f>
         <v>804</v>
       </c>
       <c r="E102" s="18">
@@ -3114,7 +3139,7 @@
     </row>
     <row r="103" spans="1:17">
       <c r="A103" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -3124,7 +3149,7 @@
         <v>31</v>
       </c>
       <c r="D103" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B103, $M:$M, $N:$N), "00") &amp; TEXT(E103, "00"))</f>
         <v>1802</v>
       </c>
       <c r="E103" s="10">
@@ -3134,7 +3159,7 @@
     </row>
     <row r="104" spans="1:17">
       <c r="A104" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -3144,7 +3169,7 @@
         <v>31</v>
       </c>
       <c r="D104" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B104, $M:$M, $N:$N), "00") &amp; TEXT(E104, "00"))</f>
         <v>1102</v>
       </c>
       <c r="E104" s="10">
@@ -3154,7 +3179,7 @@
     </row>
     <row r="105" spans="1:17">
       <c r="A105" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -3164,7 +3189,7 @@
         <v>31</v>
       </c>
       <c r="D105" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B105, $M:$M, $N:$N), "00") &amp; TEXT(E105, "00"))</f>
         <v>2206</v>
       </c>
       <c r="E105" s="10">
@@ -3174,7 +3199,7 @@
     </row>
     <row r="106" spans="1:17">
       <c r="A106" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -3184,7 +3209,7 @@
         <v>31</v>
       </c>
       <c r="D106" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B106, $M:$M, $N:$N), "00") &amp; TEXT(E106, "00"))</f>
         <v>1203</v>
       </c>
       <c r="E106" s="10">
@@ -3194,7 +3219,7 @@
     </row>
     <row r="107" spans="1:17">
       <c r="A107" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -3204,7 +3229,7 @@
         <v>31</v>
       </c>
       <c r="D107" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B107, $M:$M, $N:$N), "00") &amp; TEXT(E107, "00"))</f>
         <v>113</v>
       </c>
       <c r="E107" s="10">
@@ -3214,7 +3239,7 @@
     </row>
     <row r="108" spans="1:17">
       <c r="A108" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -3224,7 +3249,7 @@
         <v>31</v>
       </c>
       <c r="D108" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B108, $M:$M, $N:$N), "00") &amp; TEXT(E108, "00"))</f>
         <v>702</v>
       </c>
       <c r="E108" s="10">
@@ -3234,7 +3259,7 @@
     </row>
     <row r="109" spans="1:17">
       <c r="A109" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -3244,7 +3269,7 @@
         <v>31</v>
       </c>
       <c r="D109" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B109, $M:$M, $N:$N), "00") &amp; TEXT(E109, "00"))</f>
         <v>503</v>
       </c>
       <c r="E109" s="10">
@@ -3254,7 +3279,7 @@
     </row>
     <row r="110" spans="1:17">
       <c r="A110" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -3264,7 +3289,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B110, $M:$M, $N:$N), "00") &amp; TEXT(E110, "00"))</f>
         <v>2602</v>
       </c>
       <c r="E110" s="10">
@@ -3274,7 +3299,7 @@
     </row>
     <row r="111" spans="1:17">
       <c r="A111" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -3284,7 +3309,7 @@
         <v>31</v>
       </c>
       <c r="D111" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B111, $M:$M, $N:$N), "00") &amp; TEXT(E111, "00"))</f>
         <v>306</v>
       </c>
       <c r="E111" s="10">
@@ -3294,7 +3319,7 @@
     </row>
     <row r="112" spans="1:17">
       <c r="A112" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -3304,7 +3329,7 @@
         <v>31</v>
       </c>
       <c r="D112" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B112, $M:$M, $N:$N), "00") &amp; TEXT(E112, "00"))</f>
         <v>2405</v>
       </c>
       <c r="E112" s="10">
@@ -3314,7 +3339,7 @@
     </row>
     <row r="113" spans="1:17">
       <c r="A113" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -3324,7 +3349,7 @@
         <v>31</v>
       </c>
       <c r="D113" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B113, $M:$M, $N:$N), "00") &amp; TEXT(E113, "00"))</f>
         <v>902</v>
       </c>
       <c r="E113" s="10">
@@ -3334,7 +3359,7 @@
     </row>
     <row r="114" spans="1:17">
       <c r="A114" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -3344,7 +3369,7 @@
         <v>31</v>
       </c>
       <c r="D114" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B114, $M:$M, $N:$N), "00") &amp; TEXT(E114, "00"))</f>
         <v>1605</v>
       </c>
       <c r="E114" s="10">
@@ -3354,7 +3379,7 @@
     </row>
     <row r="115" spans="1:17">
       <c r="A115" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -3364,7 +3389,7 @@
         <v>31</v>
       </c>
       <c r="D115" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B115, $M:$M, $N:$N), "00") &amp; TEXT(E115, "00"))</f>
         <v>2502</v>
       </c>
       <c r="E115" s="10">
@@ -3374,7 +3399,7 @@
     </row>
     <row r="116" spans="1:17">
       <c r="A116" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -3384,7 +3409,7 @@
         <v>31</v>
       </c>
       <c r="D116" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B116, $M:$M, $N:$N), "00") &amp; TEXT(E116, "00"))</f>
         <v>2104</v>
       </c>
       <c r="E116" s="10">
@@ -3394,7 +3419,7 @@
     </row>
     <row r="117" spans="1:17">
       <c r="A117" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -3404,7 +3429,7 @@
         <v>31</v>
       </c>
       <c r="D117" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B117, $M:$M, $N:$N), "00") &amp; TEXT(E117, "00"))</f>
         <v>2305</v>
       </c>
       <c r="E117" s="10">
@@ -3414,7 +3439,7 @@
     </row>
     <row r="118" spans="1:17">
       <c r="A118" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -3424,7 +3449,7 @@
         <v>31</v>
       </c>
       <c r="D118" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B118, $M:$M, $N:$N), "00") &amp; TEXT(E118, "00"))</f>
         <v>1004</v>
       </c>
       <c r="E118" s="10">
@@ -3434,7 +3459,7 @@
     </row>
     <row r="119" spans="1:17">
       <c r="A119" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -3444,7 +3469,7 @@
         <v>31</v>
       </c>
       <c r="D119" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B119, $M:$M, $N:$N), "00") &amp; TEXT(E119, "00"))</f>
         <v>1703</v>
       </c>
       <c r="E119" s="10">
@@ -3454,7 +3479,7 @@
     </row>
     <row r="120" spans="1:17">
       <c r="A120" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -3464,7 +3489,7 @@
         <v>31</v>
       </c>
       <c r="D120" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B120, $M:$M, $N:$N), "00") &amp; TEXT(E120, "00"))</f>
         <v>202</v>
       </c>
       <c r="E120" s="10">
@@ -3474,7 +3499,7 @@
     </row>
     <row r="121" spans="1:17">
       <c r="A121" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -3484,7 +3509,7 @@
         <v>31</v>
       </c>
       <c r="D121" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B121, $M:$M, $N:$N), "00") &amp; TEXT(E121, "00"))</f>
         <v>1506</v>
       </c>
       <c r="E121" s="10">
@@ -3494,7 +3519,7 @@
     </row>
     <row r="122" spans="1:17">
       <c r="A122" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -3504,7 +3529,7 @@
         <v>31</v>
       </c>
       <c r="D122" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B122, $M:$M, $N:$N), "00") &amp; TEXT(E122, "00"))</f>
         <v>2001</v>
       </c>
       <c r="E122" s="10">
@@ -3514,7 +3539,7 @@
     </row>
     <row r="123" spans="1:17">
       <c r="A123" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -3524,7 +3549,7 @@
         <v>31</v>
       </c>
       <c r="D123" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B123, $M:$M, $N:$N), "00") &amp; TEXT(E123, "00"))</f>
         <v>1403</v>
       </c>
       <c r="E123" s="10">
@@ -3534,7 +3559,7 @@
     </row>
     <row r="124" spans="1:17">
       <c r="A124" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -3544,7 +3569,7 @@
         <v>31</v>
       </c>
       <c r="D124" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B124, $M:$M, $N:$N), "00") &amp; TEXT(E124, "00"))</f>
         <v>403</v>
       </c>
       <c r="E124" s="10">
@@ -3554,7 +3579,7 @@
     </row>
     <row r="125" spans="1:17">
       <c r="A125" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B125" s="2" t="s">
@@ -3564,7 +3589,7 @@
         <v>31</v>
       </c>
       <c r="D125" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B125, $M:$M, $N:$N), "00") &amp; TEXT(E125, "00"))</f>
         <v>602</v>
       </c>
       <c r="E125" s="10">
@@ -3574,7 +3599,7 @@
     </row>
     <row r="126" spans="1:17">
       <c r="A126" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -3584,7 +3609,7 @@
         <v>31</v>
       </c>
       <c r="D126" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B126, $M:$M, $N:$N), "00") &amp; TEXT(E126, "00"))</f>
         <v>1305</v>
       </c>
       <c r="E126" s="10">
@@ -3594,7 +3619,7 @@
     </row>
     <row r="127" spans="1:17">
       <c r="A127" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B127" s="2" t="s">
@@ -3604,7 +3629,7 @@
         <v>31</v>
       </c>
       <c r="D127" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B127, $M:$M, $N:$N), "00") &amp; TEXT(E127, "00"))</f>
         <v>1903</v>
       </c>
       <c r="E127" s="10">
@@ -3614,7 +3639,7 @@
     </row>
     <row r="128" spans="1:17" s="12" customFormat="1">
       <c r="A128" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B128" s="12" t="s">
@@ -3624,7 +3649,7 @@
         <v>47</v>
       </c>
       <c r="D128" s="12">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B128, $M:$M, $N:$N), "00") &amp; TEXT(E128, "00"))</f>
         <v>805</v>
       </c>
       <c r="E128" s="13">
@@ -3640,7 +3665,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B129" s="2" t="s">
@@ -3650,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="D129" s="2">
-        <f t="shared" si="7"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B129, $M:$M, $N:$N), "00") &amp; TEXT(E129, "00"))</f>
         <v>1803</v>
       </c>
       <c r="E129" s="10">
@@ -3660,7 +3685,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -3670,7 +3695,7 @@
         <v>47</v>
       </c>
       <c r="D130" s="2">
-        <f t="shared" ref="D130:D161" si="8">VALUE(TEXT(_xlfn.XLOOKUP(B130, $M:$M, $N:$N), "00") &amp; TEXT(E130, "00"))</f>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B130, $M:$M, $N:$N), "00") &amp; TEXT(E130, "00"))</f>
         <v>1103</v>
       </c>
       <c r="E130" s="10">
@@ -3680,7 +3705,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -3690,7 +3715,7 @@
         <v>47</v>
       </c>
       <c r="D131" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B131, $M:$M, $N:$N), "00") &amp; TEXT(E131, "00"))</f>
         <v>2207</v>
       </c>
       <c r="E131" s="10">
@@ -3700,7 +3725,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -3710,7 +3735,7 @@
         <v>47</v>
       </c>
       <c r="D132" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B132, $M:$M, $N:$N), "00") &amp; TEXT(E132, "00"))</f>
         <v>1204</v>
       </c>
       <c r="E132" s="10">
@@ -3720,7 +3745,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1">
-        <f t="shared" ref="A133:A153" si="9">A132+1</f>
+        <f t="shared" ref="A133:A153" si="2">A132+1</f>
         <v>131</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -3730,7 +3755,7 @@
         <v>47</v>
       </c>
       <c r="D133" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B133, $M:$M, $N:$N), "00") &amp; TEXT(E133, "00"))</f>
         <v>114</v>
       </c>
       <c r="E133" s="10">
@@ -3740,7 +3765,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -3750,7 +3775,7 @@
         <v>47</v>
       </c>
       <c r="D134" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B134, $M:$M, $N:$N), "00") &amp; TEXT(E134, "00"))</f>
         <v>703</v>
       </c>
       <c r="E134" s="10">
@@ -3760,7 +3785,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -3770,7 +3795,7 @@
         <v>47</v>
       </c>
       <c r="D135" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B135, $M:$M, $N:$N), "00") &amp; TEXT(E135, "00"))</f>
         <v>504</v>
       </c>
       <c r="E135" s="10">
@@ -3780,7 +3805,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -3790,7 +3815,7 @@
         <v>47</v>
       </c>
       <c r="D136" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B136, $M:$M, $N:$N), "00") &amp; TEXT(E136, "00"))</f>
         <v>2603</v>
       </c>
       <c r="E136" s="10">
@@ -3800,7 +3825,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B137" s="2" t="s">
@@ -3810,7 +3835,7 @@
         <v>47</v>
       </c>
       <c r="D137" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B137, $M:$M, $N:$N), "00") &amp; TEXT(E137, "00"))</f>
         <v>307</v>
       </c>
       <c r="E137" s="10">
@@ -3820,7 +3845,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -3830,7 +3855,7 @@
         <v>47</v>
       </c>
       <c r="D138" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B138, $M:$M, $N:$N), "00") &amp; TEXT(E138, "00"))</f>
         <v>2406</v>
       </c>
       <c r="E138" s="10">
@@ -3840,7 +3865,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B139" s="2" t="s">
@@ -3850,7 +3875,7 @@
         <v>47</v>
       </c>
       <c r="D139" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B139, $M:$M, $N:$N), "00") &amp; TEXT(E139, "00"))</f>
         <v>903</v>
       </c>
       <c r="E139" s="10">
@@ -3860,7 +3885,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -3870,7 +3895,7 @@
         <v>47</v>
       </c>
       <c r="D140" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B140, $M:$M, $N:$N), "00") &amp; TEXT(E140, "00"))</f>
         <v>1606</v>
       </c>
       <c r="E140" s="10">
@@ -3880,7 +3905,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -3890,7 +3915,7 @@
         <v>47</v>
       </c>
       <c r="D141" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B141, $M:$M, $N:$N), "00") &amp; TEXT(E141, "00"))</f>
         <v>2503</v>
       </c>
       <c r="E141" s="10">
@@ -3900,7 +3925,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -3910,7 +3935,7 @@
         <v>47</v>
       </c>
       <c r="D142" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B142, $M:$M, $N:$N), "00") &amp; TEXT(E142, "00"))</f>
         <v>2105</v>
       </c>
       <c r="E142" s="10">
@@ -3920,7 +3945,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -3930,7 +3955,7 @@
         <v>47</v>
       </c>
       <c r="D143" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B143, $M:$M, $N:$N), "00") &amp; TEXT(E143, "00"))</f>
         <v>2306</v>
       </c>
       <c r="E143" s="10">
@@ -3940,7 +3965,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -3950,7 +3975,7 @@
         <v>47</v>
       </c>
       <c r="D144" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B144, $M:$M, $N:$N), "00") &amp; TEXT(E144, "00"))</f>
         <v>1005</v>
       </c>
       <c r="E144" s="10">
@@ -3958,9 +3983,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -3970,7 +3995,7 @@
         <v>47</v>
       </c>
       <c r="D145" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B145, $M:$M, $N:$N), "00") &amp; TEXT(E145, "00"))</f>
         <v>1704</v>
       </c>
       <c r="E145" s="10">
@@ -3978,9 +4003,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -3990,7 +4015,7 @@
         <v>47</v>
       </c>
       <c r="D146" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B146, $M:$M, $N:$N), "00") &amp; TEXT(E146, "00"))</f>
         <v>203</v>
       </c>
       <c r="E146" s="10">
@@ -3998,9 +4023,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -4010,7 +4035,7 @@
         <v>47</v>
       </c>
       <c r="D147" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B147, $M:$M, $N:$N), "00") &amp; TEXT(E147, "00"))</f>
         <v>1507</v>
       </c>
       <c r="E147" s="10">
@@ -4018,9 +4043,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -4030,7 +4055,7 @@
         <v>47</v>
       </c>
       <c r="D148" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B148, $M:$M, $N:$N), "00") &amp; TEXT(E148, "00"))</f>
         <v>2002</v>
       </c>
       <c r="E148" s="10">
@@ -4038,9 +4063,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -4050,7 +4075,7 @@
         <v>47</v>
       </c>
       <c r="D149" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B149, $M:$M, $N:$N), "00") &amp; TEXT(E149, "00"))</f>
         <v>1404</v>
       </c>
       <c r="E149" s="10">
@@ -4058,9 +4083,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -4070,7 +4095,7 @@
         <v>47</v>
       </c>
       <c r="D150" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B150, $M:$M, $N:$N), "00") &amp; TEXT(E150, "00"))</f>
         <v>404</v>
       </c>
       <c r="E150" s="10">
@@ -4078,9 +4103,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -4090,7 +4115,7 @@
         <v>47</v>
       </c>
       <c r="D151" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B151, $M:$M, $N:$N), "00") &amp; TEXT(E151, "00"))</f>
         <v>603</v>
       </c>
       <c r="E151" s="10">
@@ -4098,9 +4123,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -4110,7 +4135,7 @@
         <v>47</v>
       </c>
       <c r="D152" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B152, $M:$M, $N:$N), "00") &amp; TEXT(E152, "00"))</f>
         <v>1306</v>
       </c>
       <c r="E152" s="10">
@@ -4118,9 +4143,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -4130,7 +4155,7 @@
         <v>47</v>
       </c>
       <c r="D153" s="2">
-        <f t="shared" si="8"/>
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B153, $M:$M, $N:$N), "00") &amp; TEXT(E153, "00"))</f>
         <v>1904</v>
       </c>
       <c r="E153" s="10">
@@ -4138,4076 +4163,2136 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
-      <c r="A155" s="1">
+    <row r="154" spans="1:9">
+      <c r="A154" s="21">
         <f>A153+1</f>
         <v>152</v>
       </c>
-      <c r="D155" s="2" t="e">
-        <f t="shared" ref="D155:D218" si="10">VALUE(TEXT(_xlfn.XLOOKUP(B155, $M:$M, $N:$N), "00") &amp; TEXT(E155, "00"))</f>
-        <v>#VALUE!</v>
+      <c r="B154" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D154" s="22">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B154, $M:$M, $N:$N), "00") &amp; TEXT(E154, "00"))</f>
+        <v>806</v>
+      </c>
+      <c r="E154" s="23">
+        <f>COUNTIF($B$2:B154, B154) - 1</f>
+        <v>6</v>
+      </c>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H154" s="22"/>
+      <c r="I154" s="22"/>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="1">
+        <f t="shared" ref="A155:A195" si="3">A154+1</f>
+        <v>153</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D155" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B155, $M:$M, $N:$N), "00") &amp; TEXT(E155, "00"))</f>
+        <v>1804</v>
       </c>
       <c r="E155" s="10">
         <f>COUNTIF($B$2:B155, B155) - 1</f>
-        <v>-1</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
-        <f t="shared" ref="A156:A196" si="11">A155+1</f>
-        <v>153</v>
-      </c>
-      <c r="D156" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>154</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D156" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B156, $M:$M, $N:$N), "00") &amp; TEXT(E156, "00"))</f>
+        <v>1104</v>
       </c>
       <c r="E156" s="10">
         <f>COUNTIF($B$2:B156, B156) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
-        <f t="shared" si="11"/>
-        <v>154</v>
-      </c>
-      <c r="D157" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>155</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D157" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B157, $M:$M, $N:$N), "00") &amp; TEXT(E157, "00"))</f>
+        <v>2208</v>
       </c>
       <c r="E157" s="10">
         <f>COUNTIF($B$2:B157, B157) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
-        <f t="shared" si="11"/>
-        <v>155</v>
-      </c>
-      <c r="D158" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>156</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D158" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B158, $M:$M, $N:$N), "00") &amp; TEXT(E158, "00"))</f>
+        <v>1205</v>
       </c>
       <c r="E158" s="10">
         <f>COUNTIF($B$2:B158, B158) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
-        <f t="shared" si="11"/>
-        <v>156</v>
-      </c>
-      <c r="D159" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>157</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D159" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B159, $M:$M, $N:$N), "00") &amp; TEXT(E159, "00"))</f>
+        <v>115</v>
       </c>
       <c r="E159" s="10">
         <f>COUNTIF($B$2:B159, B159) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
-        <f t="shared" si="11"/>
-        <v>157</v>
-      </c>
-      <c r="D160" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>158</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D160" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B160, $M:$M, $N:$N), "00") &amp; TEXT(E160, "00"))</f>
+        <v>704</v>
       </c>
       <c r="E160" s="10">
         <f>COUNTIF($B$2:B160, B160) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="1">
-        <f t="shared" si="11"/>
-        <v>158</v>
-      </c>
-      <c r="D161" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>159</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D161" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B161, $M:$M, $N:$N), "00") &amp; TEXT(E161, "00"))</f>
+        <v>505</v>
       </c>
       <c r="E161" s="10">
         <f>COUNTIF($B$2:B161, B161) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="1">
-        <f t="shared" si="11"/>
-        <v>159</v>
-      </c>
-      <c r="D162" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D162" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B162, $M:$M, $N:$N), "00") &amp; TEXT(E162, "00"))</f>
+        <v>2604</v>
       </c>
       <c r="E162" s="10">
         <f>COUNTIF($B$2:B162, B162) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="1">
-        <f t="shared" si="11"/>
-        <v>160</v>
-      </c>
-      <c r="D163" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>161</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D163" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B163, $M:$M, $N:$N), "00") &amp; TEXT(E163, "00"))</f>
+        <v>308</v>
       </c>
       <c r="E163" s="10">
         <f>COUNTIF($B$2:B163, B163) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="1">
-        <f t="shared" si="11"/>
-        <v>161</v>
-      </c>
-      <c r="D164" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>162</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D164" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B164, $M:$M, $N:$N), "00") &amp; TEXT(E164, "00"))</f>
+        <v>2407</v>
       </c>
       <c r="E164" s="10">
         <f>COUNTIF($B$2:B164, B164) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="1">
-        <f t="shared" si="11"/>
-        <v>162</v>
-      </c>
-      <c r="D165" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>163</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D165" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B165, $M:$M, $N:$N), "00") &amp; TEXT(E165, "00"))</f>
+        <v>904</v>
       </c>
       <c r="E165" s="10">
         <f>COUNTIF($B$2:B165, B165) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="1">
-        <f t="shared" si="11"/>
-        <v>163</v>
-      </c>
-      <c r="D166" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D166" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B166, $M:$M, $N:$N), "00") &amp; TEXT(E166, "00"))</f>
+        <v>1607</v>
       </c>
       <c r="E166" s="10">
         <f>COUNTIF($B$2:B166, B166) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="1">
-        <f t="shared" si="11"/>
-        <v>164</v>
-      </c>
-      <c r="D167" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>165</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D167" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B167, $M:$M, $N:$N), "00") &amp; TEXT(E167, "00"))</f>
+        <v>2504</v>
       </c>
       <c r="E167" s="10">
         <f>COUNTIF($B$2:B167, B167) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="1">
-        <f t="shared" si="11"/>
-        <v>165</v>
-      </c>
-      <c r="D168" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>166</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D168" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B168, $M:$M, $N:$N), "00") &amp; TEXT(E168, "00"))</f>
+        <v>2106</v>
       </c>
       <c r="E168" s="10">
         <f>COUNTIF($B$2:B168, B168) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="1">
-        <f t="shared" si="11"/>
-        <v>166</v>
-      </c>
-      <c r="D169" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>167</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D169" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B169, $M:$M, $N:$N), "00") &amp; TEXT(E169, "00"))</f>
+        <v>2307</v>
       </c>
       <c r="E169" s="10">
         <f>COUNTIF($B$2:B169, B169) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="1">
-        <f t="shared" si="11"/>
-        <v>167</v>
-      </c>
-      <c r="D170" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>168</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D170" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B170, $M:$M, $N:$N), "00") &amp; TEXT(E170, "00"))</f>
+        <v>1006</v>
       </c>
       <c r="E170" s="10">
         <f>COUNTIF($B$2:B170, B170) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="1">
-        <f t="shared" si="11"/>
-        <v>168</v>
-      </c>
-      <c r="D171" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D171" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B171, $M:$M, $N:$N), "00") &amp; TEXT(E171, "00"))</f>
+        <v>1705</v>
       </c>
       <c r="E171" s="10">
         <f>COUNTIF($B$2:B171, B171) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="1">
-        <f t="shared" si="11"/>
-        <v>169</v>
-      </c>
-      <c r="D172" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>170</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D172" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B172, $M:$M, $N:$N), "00") &amp; TEXT(E172, "00"))</f>
+        <v>204</v>
       </c>
       <c r="E172" s="10">
         <f>COUNTIF($B$2:B172, B172) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="1">
-        <f t="shared" si="11"/>
-        <v>170</v>
-      </c>
-      <c r="D173" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>171</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D173" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B173, $M:$M, $N:$N), "00") &amp; TEXT(E173, "00"))</f>
+        <v>1508</v>
       </c>
       <c r="E173" s="10">
         <f>COUNTIF($B$2:B173, B173) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="1">
-        <f t="shared" si="11"/>
-        <v>171</v>
-      </c>
-      <c r="D174" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>172</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D174" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B174, $M:$M, $N:$N), "00") &amp; TEXT(E174, "00"))</f>
+        <v>2003</v>
       </c>
       <c r="E174" s="10">
         <f>COUNTIF($B$2:B174, B174) - 1</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="1">
-        <f t="shared" si="11"/>
-        <v>172</v>
-      </c>
-      <c r="D175" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>173</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D175" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B175, $M:$M, $N:$N), "00") &amp; TEXT(E175, "00"))</f>
+        <v>1405</v>
       </c>
       <c r="E175" s="10">
         <f>COUNTIF($B$2:B175, B175) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="1">
-        <f t="shared" si="11"/>
-        <v>173</v>
-      </c>
-      <c r="D176" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>174</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D176" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B176, $M:$M, $N:$N), "00") &amp; TEXT(E176, "00"))</f>
+        <v>405</v>
       </c>
       <c r="E176" s="10">
         <f>COUNTIF($B$2:B176, B176) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="1">
-        <f t="shared" si="11"/>
-        <v>174</v>
-      </c>
-      <c r="D177" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D177" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B177, $M:$M, $N:$N), "00") &amp; TEXT(E177, "00"))</f>
+        <v>604</v>
       </c>
       <c r="E177" s="10">
         <f>COUNTIF($B$2:B177, B177) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="1">
-        <f t="shared" si="11"/>
-        <v>175</v>
-      </c>
-      <c r="D178" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>176</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D178" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B178, $M:$M, $N:$N), "00") &amp; TEXT(E178, "00"))</f>
+        <v>1307</v>
       </c>
       <c r="E178" s="10">
         <f>COUNTIF($B$2:B178, B178) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="1">
-        <f t="shared" si="11"/>
-        <v>176</v>
-      </c>
-      <c r="D179" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>177</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D179" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B179, $M:$M, $N:$N), "00") &amp; TEXT(E179, "00"))</f>
+        <v>1905</v>
       </c>
       <c r="E179" s="10">
         <f>COUNTIF($B$2:B179, B179) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="1">
-        <f t="shared" si="11"/>
-        <v>177</v>
-      </c>
-      <c r="D180" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>178</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D180" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B180, $M:$M, $N:$N), "00") &amp; TEXT(E180, "00"))</f>
+        <v>2</v>
       </c>
       <c r="E180" s="10">
         <f>COUNTIF($B$2:B180, B180) - 1</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="1">
-        <f t="shared" si="11"/>
-        <v>178</v>
-      </c>
-      <c r="D181" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>179</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D181" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B181, $M:$M, $N:$N), "00") &amp; TEXT(E181, "00"))</f>
+        <v>3</v>
       </c>
       <c r="E181" s="10">
         <f>COUNTIF($B$2:B181, B181) - 1</f>
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="1">
-        <f t="shared" si="11"/>
-        <v>179</v>
-      </c>
-      <c r="D182" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D182" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B182, $M:$M, $N:$N), "00") &amp; TEXT(E182, "00"))</f>
+        <v>4</v>
       </c>
       <c r="E182" s="10">
         <f>COUNTIF($B$2:B182, B182) - 1</f>
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="1">
-        <f t="shared" si="11"/>
-        <v>180</v>
-      </c>
-      <c r="D183" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>181</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D183" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B183, $M:$M, $N:$N), "00") &amp; TEXT(E183, "00"))</f>
+        <v>5</v>
       </c>
       <c r="E183" s="10">
         <f>COUNTIF($B$2:B183, B183) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="1">
-        <f t="shared" si="11"/>
-        <v>181</v>
-      </c>
-      <c r="D184" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>182</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D184" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B184, $M:$M, $N:$N), "00") &amp; TEXT(E184, "00"))</f>
+        <v>6</v>
       </c>
       <c r="E184" s="10">
         <f>COUNTIF($B$2:B184, B184) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="1">
-        <f t="shared" si="11"/>
-        <v>182</v>
-      </c>
-      <c r="D185" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D185" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B185, $M:$M, $N:$N), "00") &amp; TEXT(E185, "00"))</f>
+        <v>7</v>
       </c>
       <c r="E185" s="10">
         <f>COUNTIF($B$2:B185, B185) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="1">
-        <f t="shared" si="11"/>
-        <v>183</v>
-      </c>
-      <c r="D186" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>184</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D186" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B186, $M:$M, $N:$N), "00") &amp; TEXT(E186, "00"))</f>
+        <v>8</v>
       </c>
       <c r="E186" s="10">
         <f>COUNTIF($B$2:B186, B186) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="1">
-        <f t="shared" si="11"/>
-        <v>184</v>
-      </c>
-      <c r="D187" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D187" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B187, $M:$M, $N:$N), "00") &amp; TEXT(E187, "00"))</f>
+        <v>9</v>
       </c>
       <c r="E187" s="10">
         <f>COUNTIF($B$2:B187, B187) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="1">
-        <f t="shared" si="11"/>
-        <v>185</v>
-      </c>
-      <c r="D188" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>186</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D188" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B188, $M:$M, $N:$N), "00") &amp; TEXT(E188, "00"))</f>
+        <v>10</v>
       </c>
       <c r="E188" s="10">
         <f>COUNTIF($B$2:B188, B188) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="1">
-        <f t="shared" si="11"/>
-        <v>186</v>
-      </c>
-      <c r="D189" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>187</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D189" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B189, $M:$M, $N:$N), "00") &amp; TEXT(E189, "00"))</f>
+        <v>11</v>
       </c>
       <c r="E189" s="10">
         <f>COUNTIF($B$2:B189, B189) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="1">
-        <f t="shared" si="11"/>
-        <v>187</v>
-      </c>
-      <c r="D190" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>188</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D190" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B190, $M:$M, $N:$N), "00") &amp; TEXT(E190, "00"))</f>
+        <v>12</v>
       </c>
       <c r="E190" s="10">
         <f>COUNTIF($B$2:B190, B190) - 1</f>
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="1">
-        <f t="shared" si="11"/>
-        <v>188</v>
-      </c>
-      <c r="D191" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>189</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D191" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B191, $M:$M, $N:$N), "00") &amp; TEXT(E191, "00"))</f>
+        <v>13</v>
       </c>
       <c r="E191" s="10">
         <f>COUNTIF($B$2:B191, B191) - 1</f>
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="1">
-        <f t="shared" si="11"/>
-        <v>189</v>
-      </c>
-      <c r="D192" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D192" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B192, $M:$M, $N:$N), "00") &amp; TEXT(E192, "00"))</f>
+        <v>14</v>
       </c>
       <c r="E192" s="10">
         <f>COUNTIF($B$2:B192, B192) - 1</f>
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="1">
-        <f t="shared" si="11"/>
-        <v>190</v>
-      </c>
-      <c r="D193" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>191</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D193" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B193, $M:$M, $N:$N), "00") &amp; TEXT(E193, "00"))</f>
+        <v>15</v>
       </c>
       <c r="E193" s="10">
         <f>COUNTIF($B$2:B193, B193) - 1</f>
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="1">
-        <f t="shared" si="11"/>
-        <v>191</v>
-      </c>
-      <c r="D194" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>192</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D194" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B194, $M:$M, $N:$N), "00") &amp; TEXT(E194, "00"))</f>
+        <v>16</v>
       </c>
       <c r="E194" s="10">
         <f>COUNTIF($B$2:B194, B194) - 1</f>
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="1">
-        <f t="shared" si="11"/>
-        <v>192</v>
-      </c>
-      <c r="D195" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="3"/>
+        <v>193</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D195" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B195, $M:$M, $N:$N), "00") &amp; TEXT(E195, "00"))</f>
+        <v>17</v>
       </c>
       <c r="E195" s="10">
         <f>COUNTIF($B$2:B195, B195) - 1</f>
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="1">
-        <f t="shared" si="11"/>
-        <v>193</v>
-      </c>
-      <c r="D196" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" ref="A196:A258" si="4">A195+1</f>
+        <v>194</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D196" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B196, $M:$M, $N:$N), "00") &amp; TEXT(E196, "00"))</f>
+        <v>18</v>
       </c>
       <c r="E196" s="10">
         <f>COUNTIF($B$2:B196, B196) - 1</f>
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="1">
-        <f t="shared" ref="A197:A260" si="12">A196+1</f>
-        <v>194</v>
-      </c>
-      <c r="D197" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>195</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D197" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B197, $M:$M, $N:$N), "00") &amp; TEXT(E197, "00"))</f>
+        <v>19</v>
       </c>
       <c r="E197" s="10">
         <f>COUNTIF($B$2:B197, B197) - 1</f>
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="1">
-        <f t="shared" si="12"/>
-        <v>195</v>
-      </c>
-      <c r="D198" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>196</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D198" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B198, $M:$M, $N:$N), "00") &amp; TEXT(E198, "00"))</f>
+        <v>309</v>
       </c>
       <c r="E198" s="10">
         <f>COUNTIF($B$2:B198, B198) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="1">
-        <f t="shared" si="12"/>
-        <v>196</v>
-      </c>
-      <c r="D199" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>197</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D199" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B199, $M:$M, $N:$N), "00") &amp; TEXT(E199, "00"))</f>
+        <v>310</v>
       </c>
       <c r="E199" s="10">
         <f>COUNTIF($B$2:B199, B199) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="1">
-        <f t="shared" si="12"/>
-        <v>197</v>
-      </c>
-      <c r="D200" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>198</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D200" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B200, $M:$M, $N:$N), "00") &amp; TEXT(E200, "00"))</f>
+        <v>311</v>
       </c>
       <c r="E200" s="10">
         <f>COUNTIF($B$2:B200, B200) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="1">
-        <f t="shared" si="12"/>
-        <v>198</v>
-      </c>
-      <c r="D201" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>199</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D201" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B201, $M:$M, $N:$N), "00") &amp; TEXT(E201, "00"))</f>
+        <v>506</v>
       </c>
       <c r="E201" s="10">
         <f>COUNTIF($B$2:B201, B201) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="1">
-        <f t="shared" si="12"/>
-        <v>199</v>
-      </c>
-      <c r="D202" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D202" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B202, $M:$M, $N:$N), "00") &amp; TEXT(E202, "00"))</f>
+        <v>507</v>
       </c>
       <c r="E202" s="10">
         <f>COUNTIF($B$2:B202, B202) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="1">
-        <f t="shared" si="12"/>
-        <v>200</v>
-      </c>
-      <c r="D203" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>201</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D203" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B203, $M:$M, $N:$N), "00") &amp; TEXT(E203, "00"))</f>
+        <v>508</v>
       </c>
       <c r="E203" s="10">
         <f>COUNTIF($B$2:B203, B203) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="1">
-        <f t="shared" si="12"/>
-        <v>201</v>
-      </c>
-      <c r="D204" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>202</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D204" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B204, $M:$M, $N:$N), "00") &amp; TEXT(E204, "00"))</f>
+        <v>509</v>
       </c>
       <c r="E204" s="10">
         <f>COUNTIF($B$2:B204, B204) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="1">
-        <f t="shared" si="12"/>
-        <v>202</v>
-      </c>
-      <c r="D205" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>203</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D205" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B205, $M:$M, $N:$N), "00") &amp; TEXT(E205, "00"))</f>
+        <v>510</v>
       </c>
       <c r="E205" s="10">
         <f>COUNTIF($B$2:B205, B205) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="1">
-        <f t="shared" si="12"/>
-        <v>203</v>
-      </c>
-      <c r="D206" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>204</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D206" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B206, $M:$M, $N:$N), "00") &amp; TEXT(E206, "00"))</f>
+        <v>511</v>
       </c>
       <c r="E206" s="10">
         <f>COUNTIF($B$2:B206, B206) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="1">
-        <f t="shared" si="12"/>
-        <v>204</v>
-      </c>
-      <c r="D207" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>205</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D207" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B207, $M:$M, $N:$N), "00") &amp; TEXT(E207, "00"))</f>
+        <v>512</v>
       </c>
       <c r="E207" s="10">
         <f>COUNTIF($B$2:B207, B207) - 1</f>
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="1">
-        <f t="shared" si="12"/>
-        <v>205</v>
-      </c>
-      <c r="D208" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>206</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D208" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B208, $M:$M, $N:$N), "00") &amp; TEXT(E208, "00"))</f>
+        <v>605</v>
       </c>
       <c r="E208" s="10">
         <f>COUNTIF($B$2:B208, B208) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="1">
-        <f t="shared" si="12"/>
-        <v>206</v>
-      </c>
-      <c r="D209" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>207</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D209" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B209, $M:$M, $N:$N), "00") &amp; TEXT(E209, "00"))</f>
+        <v>606</v>
       </c>
       <c r="E209" s="10">
         <f>COUNTIF($B$2:B209, B209) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="1">
-        <f t="shared" si="12"/>
-        <v>207</v>
-      </c>
-      <c r="D210" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>208</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D210" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B210, $M:$M, $N:$N), "00") &amp; TEXT(E210, "00"))</f>
+        <v>607</v>
       </c>
       <c r="E210" s="10">
         <f>COUNTIF($B$2:B210, B210) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="1">
-        <f t="shared" si="12"/>
-        <v>208</v>
-      </c>
-      <c r="D211" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>209</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D211" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B211, $M:$M, $N:$N), "00") &amp; TEXT(E211, "00"))</f>
+        <v>705</v>
       </c>
       <c r="E211" s="10">
         <f>COUNTIF($B$2:B211, B211) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="1">
-        <f t="shared" si="12"/>
-        <v>209</v>
-      </c>
-      <c r="D212" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B212, $M:$M, $N:$N), "00") &amp; TEXT(E212, "00"))</f>
+        <v>706</v>
       </c>
       <c r="E212" s="10">
         <f>COUNTIF($B$2:B212, B212) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="1">
-        <f t="shared" si="12"/>
-        <v>210</v>
-      </c>
-      <c r="D213" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>211</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D213" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B213, $M:$M, $N:$N), "00") &amp; TEXT(E213, "00"))</f>
+        <v>707</v>
       </c>
       <c r="E213" s="10">
         <f>COUNTIF($B$2:B213, B213) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="1">
-        <f t="shared" si="12"/>
-        <v>211</v>
-      </c>
-      <c r="D214" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>212</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D214" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B214, $M:$M, $N:$N), "00") &amp; TEXT(E214, "00"))</f>
+        <v>708</v>
       </c>
       <c r="E214" s="10">
         <f>COUNTIF($B$2:B214, B214) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="1">
-        <f t="shared" si="12"/>
-        <v>212</v>
-      </c>
-      <c r="D215" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>213</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D215" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B215, $M:$M, $N:$N), "00") &amp; TEXT(E215, "00"))</f>
+        <v>807</v>
       </c>
       <c r="E215" s="10">
         <f>COUNTIF($B$2:B215, B215) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="1">
-        <f t="shared" si="12"/>
-        <v>213</v>
-      </c>
-      <c r="D216" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>214</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D216" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B216, $M:$M, $N:$N), "00") &amp; TEXT(E216, "00"))</f>
+        <v>905</v>
       </c>
       <c r="E216" s="10">
         <f>COUNTIF($B$2:B216, B216) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="1">
-        <f t="shared" si="12"/>
-        <v>214</v>
-      </c>
-      <c r="D217" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>215</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D217" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B217, $M:$M, $N:$N), "00") &amp; TEXT(E217, "00"))</f>
+        <v>906</v>
       </c>
       <c r="E217" s="10">
         <f>COUNTIF($B$2:B217, B217) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="1">
-        <f t="shared" si="12"/>
-        <v>215</v>
-      </c>
-      <c r="D218" s="2" t="e">
-        <f t="shared" si="10"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>216</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D218" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B218, $M:$M, $N:$N), "00") &amp; TEXT(E218, "00"))</f>
+        <v>907</v>
       </c>
       <c r="E218" s="10">
         <f>COUNTIF($B$2:B218, B218) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="1">
-        <f t="shared" si="12"/>
-        <v>216</v>
-      </c>
-      <c r="D219" s="2" t="e">
-        <f t="shared" ref="D219:D282" si="13">VALUE(TEXT(_xlfn.XLOOKUP(B219, $M:$M, $N:$N), "00") &amp; TEXT(E219, "00"))</f>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>217</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D219" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B219, $M:$M, $N:$N), "00") &amp; TEXT(E219, "00"))</f>
+        <v>1007</v>
       </c>
       <c r="E219" s="10">
         <f>COUNTIF($B$2:B219, B219) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="1">
-        <f t="shared" si="12"/>
-        <v>217</v>
-      </c>
-      <c r="D220" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>218</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D220" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B220, $M:$M, $N:$N), "00") &amp; TEXT(E220, "00"))</f>
+        <v>1008</v>
       </c>
       <c r="E220" s="10">
         <f>COUNTIF($B$2:B220, B220) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="1">
-        <f t="shared" si="12"/>
-        <v>218</v>
-      </c>
-      <c r="D221" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>219</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D221" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B221, $M:$M, $N:$N), "00") &amp; TEXT(E221, "00"))</f>
+        <v>1009</v>
       </c>
       <c r="E221" s="10">
         <f>COUNTIF($B$2:B221, B221) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="1">
-        <f t="shared" si="12"/>
-        <v>219</v>
-      </c>
-      <c r="D222" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D222" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B222, $M:$M, $N:$N), "00") &amp; TEXT(E222, "00"))</f>
+        <v>1105</v>
       </c>
       <c r="E222" s="10">
         <f>COUNTIF($B$2:B222, B222) - 1</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="1">
-        <f t="shared" si="12"/>
-        <v>220</v>
-      </c>
-      <c r="D223" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>221</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D223" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B223, $M:$M, $N:$N), "00") &amp; TEXT(E223, "00"))</f>
+        <v>1106</v>
       </c>
       <c r="E223" s="10">
         <f>COUNTIF($B$2:B223, B223) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="1">
-        <f t="shared" si="12"/>
-        <v>221</v>
-      </c>
-      <c r="D224" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>222</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D224" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B224, $M:$M, $N:$N), "00") &amp; TEXT(E224, "00"))</f>
+        <v>1107</v>
       </c>
       <c r="E224" s="10">
         <f>COUNTIF($B$2:B224, B224) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="1">
-        <f t="shared" si="12"/>
-        <v>222</v>
-      </c>
-      <c r="D225" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>223</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D225" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B225, $M:$M, $N:$N), "00") &amp; TEXT(E225, "00"))</f>
+        <v>1108</v>
       </c>
       <c r="E225" s="10">
         <f>COUNTIF($B$2:B225, B225) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="1">
-        <f t="shared" si="12"/>
-        <v>223</v>
-      </c>
-      <c r="D226" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>224</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D226" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B226, $M:$M, $N:$N), "00") &amp; TEXT(E226, "00"))</f>
+        <v>1308</v>
       </c>
       <c r="E226" s="10">
         <f>COUNTIF($B$2:B226, B226) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="1">
-        <f t="shared" si="12"/>
-        <v>224</v>
-      </c>
-      <c r="D227" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>225</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D227" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B227, $M:$M, $N:$N), "00") &amp; TEXT(E227, "00"))</f>
+        <v>1309</v>
       </c>
       <c r="E227" s="10">
         <f>COUNTIF($B$2:B227, B227) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="1">
-        <f t="shared" si="12"/>
-        <v>225</v>
-      </c>
-      <c r="D228" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>226</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D228" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B228, $M:$M, $N:$N), "00") &amp; TEXT(E228, "00"))</f>
+        <v>1310</v>
       </c>
       <c r="E228" s="10">
         <f>COUNTIF($B$2:B228, B228) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="1">
-        <f t="shared" si="12"/>
-        <v>226</v>
-      </c>
-      <c r="D229" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>227</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D229" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B229, $M:$M, $N:$N), "00") &amp; TEXT(E229, "00"))</f>
+        <v>1311</v>
       </c>
       <c r="E229" s="10">
         <f>COUNTIF($B$2:B229, B229) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="1">
-        <f t="shared" si="12"/>
-        <v>227</v>
-      </c>
-      <c r="D230" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>228</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D230" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B230, $M:$M, $N:$N), "00") &amp; TEXT(E230, "00"))</f>
+        <v>1312</v>
       </c>
       <c r="E230" s="10">
         <f>COUNTIF($B$2:B230, B230) - 1</f>
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="1">
-        <f t="shared" si="12"/>
-        <v>228</v>
-      </c>
-      <c r="D231" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>229</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D231" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B231, $M:$M, $N:$N), "00") &amp; TEXT(E231, "00"))</f>
+        <v>1406</v>
       </c>
       <c r="E231" s="10">
         <f>COUNTIF($B$2:B231, B231) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="1">
-        <f t="shared" si="12"/>
-        <v>229</v>
-      </c>
-      <c r="D232" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D232" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B232, $M:$M, $N:$N), "00") &amp; TEXT(E232, "00"))</f>
+        <v>1407</v>
       </c>
       <c r="E232" s="10">
         <f>COUNTIF($B$2:B232, B232) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="1">
-        <f t="shared" si="12"/>
-        <v>230</v>
-      </c>
-      <c r="D233" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>231</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D233" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B233, $M:$M, $N:$N), "00") &amp; TEXT(E233, "00"))</f>
+        <v>1408</v>
       </c>
       <c r="E233" s="10">
         <f>COUNTIF($B$2:B233, B233) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="1">
-        <f t="shared" si="12"/>
-        <v>231</v>
-      </c>
-      <c r="D234" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>232</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D234" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B234, $M:$M, $N:$N), "00") &amp; TEXT(E234, "00"))</f>
+        <v>1509</v>
       </c>
       <c r="E234" s="10">
         <f>COUNTIF($B$2:B234, B234) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="1">
-        <f t="shared" si="12"/>
-        <v>232</v>
-      </c>
-      <c r="D235" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>233</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D235" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B235, $M:$M, $N:$N), "00") &amp; TEXT(E235, "00"))</f>
+        <v>1608</v>
       </c>
       <c r="E235" s="10">
         <f>COUNTIF($B$2:B235, B235) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="1">
-        <f t="shared" si="12"/>
-        <v>233</v>
-      </c>
-      <c r="D236" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>234</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D236" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B236, $M:$M, $N:$N), "00") &amp; TEXT(E236, "00"))</f>
+        <v>1609</v>
       </c>
       <c r="E236" s="10">
         <f>COUNTIF($B$2:B236, B236) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="1">
-        <f t="shared" si="12"/>
-        <v>234</v>
-      </c>
-      <c r="D237" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>235</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D237" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B237, $M:$M, $N:$N), "00") &amp; TEXT(E237, "00"))</f>
+        <v>1610</v>
       </c>
       <c r="E237" s="10">
         <f>COUNTIF($B$2:B237, B237) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="1">
-        <f t="shared" si="12"/>
-        <v>235</v>
-      </c>
-      <c r="D238" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>236</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D238" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B238, $M:$M, $N:$N), "00") &amp; TEXT(E238, "00"))</f>
+        <v>1611</v>
       </c>
       <c r="E238" s="10">
         <f>COUNTIF($B$2:B238, B238) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="1">
-        <f t="shared" si="12"/>
-        <v>236</v>
-      </c>
-      <c r="D239" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>237</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D239" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B239, $M:$M, $N:$N), "00") &amp; TEXT(E239, "00"))</f>
+        <v>1612</v>
       </c>
       <c r="E239" s="10">
         <f>COUNTIF($B$2:B239, B239) - 1</f>
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="1">
-        <f t="shared" si="12"/>
-        <v>237</v>
-      </c>
-      <c r="D240" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>238</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D240" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B240, $M:$M, $N:$N), "00") &amp; TEXT(E240, "00"))</f>
+        <v>1613</v>
       </c>
       <c r="E240" s="10">
         <f>COUNTIF($B$2:B240, B240) - 1</f>
-        <v>-1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="1">
-        <f t="shared" si="12"/>
-        <v>238</v>
-      </c>
-      <c r="D241" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D241" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B241, $M:$M, $N:$N), "00") &amp; TEXT(E241, "00"))</f>
+        <v>1614</v>
       </c>
       <c r="E241" s="10">
         <f>COUNTIF($B$2:B241, B241) - 1</f>
-        <v>-1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="1">
-        <f t="shared" si="12"/>
-        <v>239</v>
-      </c>
-      <c r="D242" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D242" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B242, $M:$M, $N:$N), "00") &amp; TEXT(E242, "00"))</f>
+        <v>1615</v>
       </c>
       <c r="E242" s="10">
         <f>COUNTIF($B$2:B242, B242) - 1</f>
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="1">
-        <f t="shared" si="12"/>
-        <v>240</v>
-      </c>
-      <c r="D243" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>241</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D243" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B243, $M:$M, $N:$N), "00") &amp; TEXT(E243, "00"))</f>
+        <v>1616</v>
       </c>
       <c r="E243" s="10">
         <f>COUNTIF($B$2:B243, B243) - 1</f>
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="1">
-        <f t="shared" si="12"/>
-        <v>241</v>
-      </c>
-      <c r="D244" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>242</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D244" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B244, $M:$M, $N:$N), "00") &amp; TEXT(E244, "00"))</f>
+        <v>1617</v>
       </c>
       <c r="E244" s="10">
         <f>COUNTIF($B$2:B244, B244) - 1</f>
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="1">
-        <f t="shared" si="12"/>
-        <v>242</v>
-      </c>
-      <c r="D245" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>243</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D245" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B245, $M:$M, $N:$N), "00") &amp; TEXT(E245, "00"))</f>
+        <v>1618</v>
       </c>
       <c r="E245" s="10">
         <f>COUNTIF($B$2:B245, B245) - 1</f>
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="1">
-        <f t="shared" si="12"/>
-        <v>243</v>
-      </c>
-      <c r="D246" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>244</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D246" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B246, $M:$M, $N:$N), "00") &amp; TEXT(E246, "00"))</f>
+        <v>1706</v>
       </c>
       <c r="E246" s="10">
         <f>COUNTIF($B$2:B246, B246) - 1</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="1">
-        <f t="shared" si="12"/>
-        <v>244</v>
-      </c>
-      <c r="D247" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>245</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D247" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B247, $M:$M, $N:$N), "00") &amp; TEXT(E247, "00"))</f>
+        <v>1707</v>
       </c>
       <c r="E247" s="10">
         <f>COUNTIF($B$2:B247, B247) - 1</f>
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="1">
-        <f t="shared" si="12"/>
-        <v>245</v>
-      </c>
-      <c r="D248" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>246</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D248" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B248, $M:$M, $N:$N), "00") &amp; TEXT(E248, "00"))</f>
+        <v>2209</v>
       </c>
       <c r="E248" s="10">
         <f>COUNTIF($B$2:B248, B248) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="1">
-        <f t="shared" si="12"/>
-        <v>246</v>
-      </c>
-      <c r="D249" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>247</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D249" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B249, $M:$M, $N:$N), "00") &amp; TEXT(E249, "00"))</f>
+        <v>2308</v>
       </c>
       <c r="E249" s="10">
         <f>COUNTIF($B$2:B249, B249) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="1">
-        <f t="shared" si="12"/>
-        <v>247</v>
-      </c>
-      <c r="D250" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>248</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D250" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B250, $M:$M, $N:$N), "00") &amp; TEXT(E250, "00"))</f>
+        <v>2408</v>
       </c>
       <c r="E250" s="10">
         <f>COUNTIF($B$2:B250, B250) - 1</f>
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="1">
-        <f t="shared" si="12"/>
-        <v>248</v>
-      </c>
-      <c r="D251" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>249</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D251" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B251, $M:$M, $N:$N), "00") &amp; TEXT(E251, "00"))</f>
+        <v>2409</v>
       </c>
       <c r="E251" s="10">
         <f>COUNTIF($B$2:B251, B251) - 1</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="1">
-        <f t="shared" si="12"/>
-        <v>249</v>
-      </c>
-      <c r="D252" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D252" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B252, $M:$M, $N:$N), "00") &amp; TEXT(E252, "00"))</f>
+        <v>2410</v>
       </c>
       <c r="E252" s="10">
         <f>COUNTIF($B$2:B252, B252) - 1</f>
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="1">
-        <f t="shared" si="12"/>
-        <v>250</v>
-      </c>
-      <c r="D253" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>251</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D253" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B253, $M:$M, $N:$N), "00") &amp; TEXT(E253, "00"))</f>
+        <v>2411</v>
       </c>
       <c r="E253" s="10">
         <f>COUNTIF($B$2:B253, B253) - 1</f>
-        <v>-1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="1">
-        <f t="shared" si="12"/>
-        <v>251</v>
-      </c>
-      <c r="D254" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>252</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D254" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B254, $M:$M, $N:$N), "00") &amp; TEXT(E254, "00"))</f>
+        <v>2412</v>
       </c>
       <c r="E254" s="10">
         <f>COUNTIF($B$2:B254, B254) - 1</f>
-        <v>-1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="1">
-        <f t="shared" si="12"/>
-        <v>252</v>
-      </c>
-      <c r="D255" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>253</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D255" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B255, $M:$M, $N:$N), "00") &amp; TEXT(E255, "00"))</f>
+        <v>116</v>
       </c>
       <c r="E255" s="10">
         <f>COUNTIF($B$2:B255, B255) - 1</f>
-        <v>-1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="1">
-        <f t="shared" si="12"/>
-        <v>253</v>
-      </c>
-      <c r="D256" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>254</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D256" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B256, $M:$M, $N:$N), "00") &amp; TEXT(E256, "00"))</f>
+        <v>117</v>
       </c>
       <c r="E256" s="10">
         <f>COUNTIF($B$2:B256, B256) - 1</f>
-        <v>-1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="1">
-        <f t="shared" si="12"/>
-        <v>254</v>
-      </c>
-      <c r="D257" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>255</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D257" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B257, $M:$M, $N:$N), "00") &amp; TEXT(E257, "00"))</f>
+        <v>118</v>
       </c>
       <c r="E257" s="10">
         <f>COUNTIF($B$2:B257, B257) - 1</f>
-        <v>-1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="1">
-        <f t="shared" si="12"/>
-        <v>255</v>
-      </c>
-      <c r="D258" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
+        <f t="shared" si="4"/>
+        <v>256</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D258" s="2">
+        <f>VALUE(TEXT(_xlfn.XLOOKUP(B258, $M:$M, $N:$N), "00") &amp; TEXT(E258, "00"))</f>
+        <v>119</v>
       </c>
       <c r="E258" s="10">
         <f>COUNTIF($B$2:B258, B258) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5">
-      <c r="A259" s="1">
-        <f t="shared" si="12"/>
-        <v>256</v>
-      </c>
-      <c r="D259" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E259" s="10">
-        <f>COUNTIF($B$2:B259, B259) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5">
-      <c r="A260" s="1">
-        <f t="shared" si="12"/>
-        <v>257</v>
-      </c>
-      <c r="D260" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E260" s="10">
-        <f>COUNTIF($B$2:B260, B260) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5">
-      <c r="A261" s="1">
-        <f t="shared" ref="A261:A324" si="14">A260+1</f>
-        <v>258</v>
-      </c>
-      <c r="D261" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E261" s="10">
-        <f>COUNTIF($B$2:B261, B261) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5">
-      <c r="A262" s="1">
-        <f t="shared" si="14"/>
-        <v>259</v>
-      </c>
-      <c r="D262" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E262" s="10">
-        <f>COUNTIF($B$2:B262, B262) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5">
-      <c r="A263" s="1">
-        <f t="shared" si="14"/>
-        <v>260</v>
-      </c>
-      <c r="D263" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E263" s="10">
-        <f>COUNTIF($B$2:B263, B263) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5">
-      <c r="A264" s="1">
-        <f t="shared" si="14"/>
-        <v>261</v>
-      </c>
-      <c r="D264" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E264" s="10">
-        <f>COUNTIF($B$2:B264, B264) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5">
-      <c r="A265" s="1">
-        <f t="shared" si="14"/>
-        <v>262</v>
-      </c>
-      <c r="D265" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E265" s="10">
-        <f>COUNTIF($B$2:B265, B265) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5">
-      <c r="A266" s="1">
-        <f t="shared" si="14"/>
-        <v>263</v>
-      </c>
-      <c r="D266" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E266" s="10">
-        <f>COUNTIF($B$2:B266, B266) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5">
-      <c r="A267" s="1">
-        <f t="shared" si="14"/>
-        <v>264</v>
-      </c>
-      <c r="D267" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E267" s="10">
-        <f>COUNTIF($B$2:B267, B267) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
-      <c r="A268" s="1">
-        <f t="shared" si="14"/>
-        <v>265</v>
-      </c>
-      <c r="D268" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E268" s="10">
-        <f>COUNTIF($B$2:B268, B268) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
-      <c r="A269" s="1">
-        <f t="shared" si="14"/>
-        <v>266</v>
-      </c>
-      <c r="D269" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E269" s="10">
-        <f>COUNTIF($B$2:B269, B269) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5">
-      <c r="A270" s="1">
-        <f t="shared" si="14"/>
-        <v>267</v>
-      </c>
-      <c r="D270" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E270" s="10">
-        <f>COUNTIF($B$2:B270, B270) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5">
-      <c r="A271" s="1">
-        <f t="shared" si="14"/>
-        <v>268</v>
-      </c>
-      <c r="D271" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E271" s="10">
-        <f>COUNTIF($B$2:B271, B271) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5">
-      <c r="A272" s="1">
-        <f t="shared" si="14"/>
-        <v>269</v>
-      </c>
-      <c r="D272" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E272" s="10">
-        <f>COUNTIF($B$2:B272, B272) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5">
-      <c r="A273" s="1">
-        <f t="shared" si="14"/>
-        <v>270</v>
-      </c>
-      <c r="D273" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E273" s="10">
-        <f>COUNTIF($B$2:B273, B273) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
-      <c r="A274" s="1">
-        <f t="shared" si="14"/>
-        <v>271</v>
-      </c>
-      <c r="D274" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E274" s="10">
-        <f>COUNTIF($B$2:B274, B274) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5">
-      <c r="A275" s="1">
-        <f t="shared" si="14"/>
-        <v>272</v>
-      </c>
-      <c r="D275" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E275" s="10">
-        <f>COUNTIF($B$2:B275, B275) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5">
-      <c r="A276" s="1">
-        <f t="shared" si="14"/>
-        <v>273</v>
-      </c>
-      <c r="D276" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E276" s="10">
-        <f>COUNTIF($B$2:B276, B276) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5">
-      <c r="A277" s="1">
-        <f t="shared" si="14"/>
-        <v>274</v>
-      </c>
-      <c r="D277" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E277" s="10">
-        <f>COUNTIF($B$2:B277, B277) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
-      <c r="A278" s="1">
-        <f t="shared" si="14"/>
-        <v>275</v>
-      </c>
-      <c r="D278" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E278" s="10">
-        <f>COUNTIF($B$2:B278, B278) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5">
-      <c r="A279" s="1">
-        <f t="shared" si="14"/>
-        <v>276</v>
-      </c>
-      <c r="D279" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E279" s="10">
-        <f>COUNTIF($B$2:B279, B279) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5">
-      <c r="A280" s="1">
-        <f t="shared" si="14"/>
-        <v>277</v>
-      </c>
-      <c r="D280" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E280" s="10">
-        <f>COUNTIF($B$2:B280, B280) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="281" spans="1:5">
-      <c r="A281" s="1">
-        <f t="shared" si="14"/>
-        <v>278</v>
-      </c>
-      <c r="D281" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E281" s="10">
-        <f>COUNTIF($B$2:B281, B281) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5">
-      <c r="A282" s="1">
-        <f t="shared" si="14"/>
-        <v>279</v>
-      </c>
-      <c r="D282" s="2" t="e">
-        <f t="shared" si="13"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E282" s="10">
-        <f>COUNTIF($B$2:B282, B282) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5">
-      <c r="A283" s="1">
-        <f t="shared" si="14"/>
-        <v>280</v>
-      </c>
-      <c r="D283" s="2" t="e">
-        <f t="shared" ref="D283:D346" si="15">VALUE(TEXT(_xlfn.XLOOKUP(B283, $M:$M, $N:$N), "00") &amp; TEXT(E283, "00"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E283" s="10">
-        <f>COUNTIF($B$2:B283, B283) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5">
-      <c r="A284" s="1">
-        <f t="shared" si="14"/>
-        <v>281</v>
-      </c>
-      <c r="D284" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E284" s="10">
-        <f>COUNTIF($B$2:B284, B284) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5">
-      <c r="A285" s="1">
-        <f t="shared" si="14"/>
-        <v>282</v>
-      </c>
-      <c r="D285" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E285" s="10">
-        <f>COUNTIF($B$2:B285, B285) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5">
-      <c r="A286" s="1">
-        <f t="shared" si="14"/>
-        <v>283</v>
-      </c>
-      <c r="D286" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E286" s="10">
-        <f>COUNTIF($B$2:B286, B286) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5">
-      <c r="A287" s="1">
-        <f t="shared" si="14"/>
-        <v>284</v>
-      </c>
-      <c r="D287" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E287" s="10">
-        <f>COUNTIF($B$2:B287, B287) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5">
-      <c r="A288" s="1">
-        <f t="shared" si="14"/>
-        <v>285</v>
-      </c>
-      <c r="D288" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E288" s="10">
-        <f>COUNTIF($B$2:B288, B288) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5">
-      <c r="A289" s="1">
-        <f t="shared" si="14"/>
-        <v>286</v>
-      </c>
-      <c r="D289" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E289" s="10">
-        <f>COUNTIF($B$2:B289, B289) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5">
-      <c r="A290" s="1">
-        <f t="shared" si="14"/>
-        <v>287</v>
-      </c>
-      <c r="D290" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E290" s="10">
-        <f>COUNTIF($B$2:B290, B290) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5">
-      <c r="A291" s="1">
-        <f t="shared" si="14"/>
-        <v>288</v>
-      </c>
-      <c r="D291" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E291" s="10">
-        <f>COUNTIF($B$2:B291, B291) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
-      <c r="A292" s="1">
-        <f t="shared" si="14"/>
-        <v>289</v>
-      </c>
-      <c r="D292" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E292" s="10">
-        <f>COUNTIF($B$2:B292, B292) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5">
-      <c r="A293" s="1">
-        <f t="shared" si="14"/>
-        <v>290</v>
-      </c>
-      <c r="D293" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E293" s="10">
-        <f>COUNTIF($B$2:B293, B293) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5">
-      <c r="A294" s="1">
-        <f t="shared" si="14"/>
-        <v>291</v>
-      </c>
-      <c r="D294" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E294" s="10">
-        <f>COUNTIF($B$2:B294, B294) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5">
-      <c r="A295" s="1">
-        <f t="shared" si="14"/>
-        <v>292</v>
-      </c>
-      <c r="D295" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E295" s="10">
-        <f>COUNTIF($B$2:B295, B295) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5">
-      <c r="A296" s="1">
-        <f t="shared" si="14"/>
-        <v>293</v>
-      </c>
-      <c r="D296" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E296" s="10">
-        <f>COUNTIF($B$2:B296, B296) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
-      <c r="A297" s="1">
-        <f t="shared" si="14"/>
-        <v>294</v>
-      </c>
-      <c r="D297" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E297" s="10">
-        <f>COUNTIF($B$2:B297, B297) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5">
-      <c r="A298" s="1">
-        <f t="shared" si="14"/>
-        <v>295</v>
-      </c>
-      <c r="D298" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E298" s="10">
-        <f>COUNTIF($B$2:B298, B298) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
-      <c r="A299" s="1">
-        <f t="shared" si="14"/>
-        <v>296</v>
-      </c>
-      <c r="D299" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E299" s="10">
-        <f>COUNTIF($B$2:B299, B299) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
-      <c r="A300" s="1">
-        <f t="shared" si="14"/>
-        <v>297</v>
-      </c>
-      <c r="D300" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E300" s="10">
-        <f>COUNTIF($B$2:B300, B300) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5">
-      <c r="A301" s="1">
-        <f t="shared" si="14"/>
-        <v>298</v>
-      </c>
-      <c r="D301" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E301" s="10">
-        <f>COUNTIF($B$2:B301, B301) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
-      <c r="A302" s="1">
-        <f t="shared" si="14"/>
-        <v>299</v>
-      </c>
-      <c r="D302" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E302" s="10">
-        <f>COUNTIF($B$2:B302, B302) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
-      <c r="A303" s="1">
-        <f t="shared" si="14"/>
-        <v>300</v>
-      </c>
-      <c r="D303" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E303" s="10">
-        <f>COUNTIF($B$2:B303, B303) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
-      <c r="A304" s="1">
-        <f t="shared" si="14"/>
-        <v>301</v>
-      </c>
-      <c r="D304" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E304" s="10">
-        <f>COUNTIF($B$2:B304, B304) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5">
-      <c r="A305" s="1">
-        <f t="shared" si="14"/>
-        <v>302</v>
-      </c>
-      <c r="D305" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E305" s="10">
-        <f>COUNTIF($B$2:B305, B305) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" s="1">
-        <f t="shared" si="14"/>
-        <v>303</v>
-      </c>
-      <c r="D306" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E306" s="10">
-        <f>COUNTIF($B$2:B306, B306) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5">
-      <c r="A307" s="1">
-        <f t="shared" si="14"/>
-        <v>304</v>
-      </c>
-      <c r="D307" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E307" s="10">
-        <f>COUNTIF($B$2:B307, B307) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
-      <c r="A308" s="1">
-        <f t="shared" si="14"/>
-        <v>305</v>
-      </c>
-      <c r="D308" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E308" s="10">
-        <f>COUNTIF($B$2:B308, B308) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
-      <c r="A309" s="1">
-        <f t="shared" si="14"/>
-        <v>306</v>
-      </c>
-      <c r="D309" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E309" s="10">
-        <f>COUNTIF($B$2:B309, B309) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
-      <c r="A310" s="1">
-        <f t="shared" si="14"/>
-        <v>307</v>
-      </c>
-      <c r="D310" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E310" s="10">
-        <f>COUNTIF($B$2:B310, B310) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
-      <c r="A311" s="1">
-        <f t="shared" si="14"/>
-        <v>308</v>
-      </c>
-      <c r="D311" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E311" s="10">
-        <f>COUNTIF($B$2:B311, B311) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
-      <c r="A312" s="1">
-        <f t="shared" si="14"/>
-        <v>309</v>
-      </c>
-      <c r="D312" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E312" s="10">
-        <f>COUNTIF($B$2:B312, B312) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5">
-      <c r="A313" s="1">
-        <f t="shared" si="14"/>
-        <v>310</v>
-      </c>
-      <c r="D313" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E313" s="10">
-        <f>COUNTIF($B$2:B313, B313) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
-      <c r="A314" s="1">
-        <f t="shared" si="14"/>
-        <v>311</v>
-      </c>
-      <c r="D314" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E314" s="10">
-        <f>COUNTIF($B$2:B314, B314) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" s="1">
-        <f t="shared" si="14"/>
-        <v>312</v>
-      </c>
-      <c r="D315" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E315" s="10">
-        <f>COUNTIF($B$2:B315, B315) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" s="1">
-        <f t="shared" si="14"/>
-        <v>313</v>
-      </c>
-      <c r="D316" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E316" s="10">
-        <f>COUNTIF($B$2:B316, B316) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
-      <c r="A317" s="1">
-        <f t="shared" si="14"/>
-        <v>314</v>
-      </c>
-      <c r="D317" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E317" s="10">
-        <f>COUNTIF($B$2:B317, B317) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
-      <c r="A318" s="1">
-        <f t="shared" si="14"/>
-        <v>315</v>
-      </c>
-      <c r="D318" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E318" s="10">
-        <f>COUNTIF($B$2:B318, B318) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5">
-      <c r="A319" s="1">
-        <f t="shared" si="14"/>
-        <v>316</v>
-      </c>
-      <c r="D319" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E319" s="10">
-        <f>COUNTIF($B$2:B319, B319) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
-      <c r="A320" s="1">
-        <f t="shared" si="14"/>
-        <v>317</v>
-      </c>
-      <c r="D320" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E320" s="10">
-        <f>COUNTIF($B$2:B320, B320) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
-      <c r="A321" s="1">
-        <f t="shared" si="14"/>
-        <v>318</v>
-      </c>
-      <c r="D321" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E321" s="10">
-        <f>COUNTIF($B$2:B321, B321) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
-      <c r="A322" s="1">
-        <f t="shared" si="14"/>
-        <v>319</v>
-      </c>
-      <c r="D322" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E322" s="10">
-        <f>COUNTIF($B$2:B322, B322) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" s="1">
-        <f t="shared" si="14"/>
-        <v>320</v>
-      </c>
-      <c r="D323" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E323" s="10">
-        <f>COUNTIF($B$2:B323, B323) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
-      <c r="A324" s="1">
-        <f t="shared" si="14"/>
-        <v>321</v>
-      </c>
-      <c r="D324" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E324" s="10">
-        <f>COUNTIF($B$2:B324, B324) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
-      <c r="A325" s="1">
-        <f t="shared" ref="A325:A388" si="16">A324+1</f>
-        <v>322</v>
-      </c>
-      <c r="D325" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E325" s="10">
-        <f>COUNTIF($B$2:B325, B325) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
-      <c r="A326" s="1">
-        <f t="shared" si="16"/>
-        <v>323</v>
-      </c>
-      <c r="D326" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E326" s="10">
-        <f>COUNTIF($B$2:B326, B326) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
-      <c r="A327" s="1">
-        <f t="shared" si="16"/>
-        <v>324</v>
-      </c>
-      <c r="D327" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E327" s="10">
-        <f>COUNTIF($B$2:B327, B327) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
-      <c r="A328" s="1">
-        <f t="shared" si="16"/>
-        <v>325</v>
-      </c>
-      <c r="D328" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E328" s="10">
-        <f>COUNTIF($B$2:B328, B328) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
-      <c r="A329" s="1">
-        <f t="shared" si="16"/>
-        <v>326</v>
-      </c>
-      <c r="D329" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E329" s="10">
-        <f>COUNTIF($B$2:B329, B329) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
-      <c r="A330" s="1">
-        <f t="shared" si="16"/>
-        <v>327</v>
-      </c>
-      <c r="D330" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E330" s="10">
-        <f>COUNTIF($B$2:B330, B330) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
-      <c r="A331" s="1">
-        <f t="shared" si="16"/>
-        <v>328</v>
-      </c>
-      <c r="D331" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E331" s="10">
-        <f>COUNTIF($B$2:B331, B331) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
-      <c r="A332" s="1">
-        <f t="shared" si="16"/>
-        <v>329</v>
-      </c>
-      <c r="D332" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E332" s="10">
-        <f>COUNTIF($B$2:B332, B332) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
-      <c r="A333" s="1">
-        <f t="shared" si="16"/>
-        <v>330</v>
-      </c>
-      <c r="D333" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E333" s="10">
-        <f>COUNTIF($B$2:B333, B333) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
-      <c r="A334" s="1">
-        <f t="shared" si="16"/>
-        <v>331</v>
-      </c>
-      <c r="D334" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E334" s="10">
-        <f>COUNTIF($B$2:B334, B334) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
-      <c r="A335" s="1">
-        <f t="shared" si="16"/>
-        <v>332</v>
-      </c>
-      <c r="D335" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E335" s="10">
-        <f>COUNTIF($B$2:B335, B335) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
-      <c r="A336" s="1">
-        <f t="shared" si="16"/>
-        <v>333</v>
-      </c>
-      <c r="D336" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E336" s="10">
-        <f>COUNTIF($B$2:B336, B336) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
-      <c r="A337" s="1">
-        <f t="shared" si="16"/>
-        <v>334</v>
-      </c>
-      <c r="D337" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E337" s="10">
-        <f>COUNTIF($B$2:B337, B337) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
-      <c r="A338" s="1">
-        <f t="shared" si="16"/>
-        <v>335</v>
-      </c>
-      <c r="D338" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E338" s="10">
-        <f>COUNTIF($B$2:B338, B338) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
-      <c r="A339" s="1">
-        <f t="shared" si="16"/>
-        <v>336</v>
-      </c>
-      <c r="D339" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E339" s="10">
-        <f>COUNTIF($B$2:B339, B339) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
-      <c r="A340" s="1">
-        <f t="shared" si="16"/>
-        <v>337</v>
-      </c>
-      <c r="D340" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E340" s="10">
-        <f>COUNTIF($B$2:B340, B340) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
-      <c r="A341" s="1">
-        <f t="shared" si="16"/>
-        <v>338</v>
-      </c>
-      <c r="D341" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E341" s="10">
-        <f>COUNTIF($B$2:B341, B341) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
-      <c r="A342" s="1">
-        <f t="shared" si="16"/>
-        <v>339</v>
-      </c>
-      <c r="D342" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E342" s="10">
-        <f>COUNTIF($B$2:B342, B342) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
-      <c r="A343" s="1">
-        <f t="shared" si="16"/>
-        <v>340</v>
-      </c>
-      <c r="D343" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E343" s="10">
-        <f>COUNTIF($B$2:B343, B343) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
-      <c r="A344" s="1">
-        <f t="shared" si="16"/>
-        <v>341</v>
-      </c>
-      <c r="D344" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E344" s="10">
-        <f>COUNTIF($B$2:B344, B344) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
-      <c r="A345" s="1">
-        <f t="shared" si="16"/>
-        <v>342</v>
-      </c>
-      <c r="D345" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E345" s="10">
-        <f>COUNTIF($B$2:B345, B345) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
-      <c r="A346" s="1">
-        <f t="shared" si="16"/>
-        <v>343</v>
-      </c>
-      <c r="D346" s="2" t="e">
-        <f t="shared" si="15"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E346" s="10">
-        <f>COUNTIF($B$2:B346, B346) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
-      <c r="A347" s="1">
-        <f t="shared" si="16"/>
-        <v>344</v>
-      </c>
-      <c r="D347" s="2" t="e">
-        <f t="shared" ref="D347:D410" si="17">VALUE(TEXT(_xlfn.XLOOKUP(B347, $M:$M, $N:$N), "00") &amp; TEXT(E347, "00"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E347" s="10">
-        <f>COUNTIF($B$2:B347, B347) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
-      <c r="A348" s="1">
-        <f t="shared" si="16"/>
-        <v>345</v>
-      </c>
-      <c r="D348" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E348" s="10">
-        <f>COUNTIF($B$2:B348, B348) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
-      <c r="A349" s="1">
-        <f t="shared" si="16"/>
-        <v>346</v>
-      </c>
-      <c r="D349" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E349" s="10">
-        <f>COUNTIF($B$2:B349, B349) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
-      <c r="A350" s="1">
-        <f t="shared" si="16"/>
-        <v>347</v>
-      </c>
-      <c r="D350" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E350" s="10">
-        <f>COUNTIF($B$2:B350, B350) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
-      <c r="A351" s="1">
-        <f t="shared" si="16"/>
-        <v>348</v>
-      </c>
-      <c r="D351" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E351" s="10">
-        <f>COUNTIF($B$2:B351, B351) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
-      <c r="A352" s="1">
-        <f t="shared" si="16"/>
-        <v>349</v>
-      </c>
-      <c r="D352" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E352" s="10">
-        <f>COUNTIF($B$2:B352, B352) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
-      <c r="A353" s="1">
-        <f t="shared" si="16"/>
-        <v>350</v>
-      </c>
-      <c r="D353" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E353" s="10">
-        <f>COUNTIF($B$2:B353, B353) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
-      <c r="A354" s="1">
-        <f t="shared" si="16"/>
-        <v>351</v>
-      </c>
-      <c r="D354" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E354" s="10">
-        <f>COUNTIF($B$2:B354, B354) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
-      <c r="A355" s="1">
-        <f t="shared" si="16"/>
-        <v>352</v>
-      </c>
-      <c r="D355" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E355" s="10">
-        <f>COUNTIF($B$2:B355, B355) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
-      <c r="A356" s="1">
-        <f t="shared" si="16"/>
-        <v>353</v>
-      </c>
-      <c r="D356" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E356" s="10">
-        <f>COUNTIF($B$2:B356, B356) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
-      <c r="A357" s="1">
-        <f t="shared" si="16"/>
-        <v>354</v>
-      </c>
-      <c r="D357" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E357" s="10">
-        <f>COUNTIF($B$2:B357, B357) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
-      <c r="A358" s="1">
-        <f t="shared" si="16"/>
-        <v>355</v>
-      </c>
-      <c r="D358" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E358" s="10">
-        <f>COUNTIF($B$2:B358, B358) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
-      <c r="A359" s="1">
-        <f t="shared" si="16"/>
-        <v>356</v>
-      </c>
-      <c r="D359" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E359" s="10">
-        <f>COUNTIF($B$2:B359, B359) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
-      <c r="A360" s="1">
-        <f t="shared" si="16"/>
-        <v>357</v>
-      </c>
-      <c r="D360" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E360" s="10">
-        <f>COUNTIF($B$2:B360, B360) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
-      <c r="A361" s="1">
-        <f t="shared" si="16"/>
-        <v>358</v>
-      </c>
-      <c r="D361" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E361" s="10">
-        <f>COUNTIF($B$2:B361, B361) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
-      <c r="A362" s="1">
-        <f t="shared" si="16"/>
-        <v>359</v>
-      </c>
-      <c r="D362" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E362" s="10">
-        <f>COUNTIF($B$2:B362, B362) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
-      <c r="A363" s="1">
-        <f t="shared" si="16"/>
-        <v>360</v>
-      </c>
-      <c r="D363" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E363" s="10">
-        <f>COUNTIF($B$2:B363, B363) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
-      <c r="A364" s="1">
-        <f t="shared" si="16"/>
-        <v>361</v>
-      </c>
-      <c r="D364" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E364" s="10">
-        <f>COUNTIF($B$2:B364, B364) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
-      <c r="A365" s="1">
-        <f t="shared" si="16"/>
-        <v>362</v>
-      </c>
-      <c r="D365" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E365" s="10">
-        <f>COUNTIF($B$2:B365, B365) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
-      <c r="A366" s="1">
-        <f t="shared" si="16"/>
-        <v>363</v>
-      </c>
-      <c r="D366" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E366" s="10">
-        <f>COUNTIF($B$2:B366, B366) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
-      <c r="A367" s="1">
-        <f t="shared" si="16"/>
-        <v>364</v>
-      </c>
-      <c r="D367" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E367" s="10">
-        <f>COUNTIF($B$2:B367, B367) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
-      <c r="A368" s="1">
-        <f t="shared" si="16"/>
-        <v>365</v>
-      </c>
-      <c r="D368" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E368" s="10">
-        <f>COUNTIF($B$2:B368, B368) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
-      <c r="A369" s="1">
-        <f t="shared" si="16"/>
-        <v>366</v>
-      </c>
-      <c r="D369" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E369" s="10">
-        <f>COUNTIF($B$2:B369, B369) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
-      <c r="A370" s="1">
-        <f t="shared" si="16"/>
-        <v>367</v>
-      </c>
-      <c r="D370" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E370" s="10">
-        <f>COUNTIF($B$2:B370, B370) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
-      <c r="A371" s="1">
-        <f t="shared" si="16"/>
-        <v>368</v>
-      </c>
-      <c r="D371" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E371" s="10">
-        <f>COUNTIF($B$2:B371, B371) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
-      <c r="A372" s="1">
-        <f t="shared" si="16"/>
-        <v>369</v>
-      </c>
-      <c r="D372" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E372" s="10">
-        <f>COUNTIF($B$2:B372, B372) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
-      <c r="A373" s="1">
-        <f t="shared" si="16"/>
-        <v>370</v>
-      </c>
-      <c r="D373" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E373" s="10">
-        <f>COUNTIF($B$2:B373, B373) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5">
-      <c r="A374" s="1">
-        <f t="shared" si="16"/>
-        <v>371</v>
-      </c>
-      <c r="D374" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E374" s="10">
-        <f>COUNTIF($B$2:B374, B374) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5">
-      <c r="A375" s="1">
-        <f t="shared" si="16"/>
-        <v>372</v>
-      </c>
-      <c r="D375" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E375" s="10">
-        <f>COUNTIF($B$2:B375, B375) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5">
-      <c r="A376" s="1">
-        <f t="shared" si="16"/>
-        <v>373</v>
-      </c>
-      <c r="D376" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E376" s="10">
-        <f>COUNTIF($B$2:B376, B376) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5">
-      <c r="A377" s="1">
-        <f t="shared" si="16"/>
-        <v>374</v>
-      </c>
-      <c r="D377" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E377" s="10">
-        <f>COUNTIF($B$2:B377, B377) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5">
-      <c r="A378" s="1">
-        <f t="shared" si="16"/>
-        <v>375</v>
-      </c>
-      <c r="D378" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E378" s="10">
-        <f>COUNTIF($B$2:B378, B378) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
-      <c r="A379" s="1">
-        <f t="shared" si="16"/>
-        <v>376</v>
-      </c>
-      <c r="D379" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E379" s="10">
-        <f>COUNTIF($B$2:B379, B379) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5">
-      <c r="A380" s="1">
-        <f t="shared" si="16"/>
-        <v>377</v>
-      </c>
-      <c r="D380" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E380" s="10">
-        <f>COUNTIF($B$2:B380, B380) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5">
-      <c r="A381" s="1">
-        <f t="shared" si="16"/>
-        <v>378</v>
-      </c>
-      <c r="D381" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E381" s="10">
-        <f>COUNTIF($B$2:B381, B381) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5">
-      <c r="A382" s="1">
-        <f t="shared" si="16"/>
-        <v>379</v>
-      </c>
-      <c r="D382" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E382" s="10">
-        <f>COUNTIF($B$2:B382, B382) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
-      <c r="A383" s="1">
-        <f t="shared" si="16"/>
-        <v>380</v>
-      </c>
-      <c r="D383" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E383" s="10">
-        <f>COUNTIF($B$2:B383, B383) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5">
-      <c r="A384" s="1">
-        <f t="shared" si="16"/>
-        <v>381</v>
-      </c>
-      <c r="D384" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E384" s="10">
-        <f>COUNTIF($B$2:B384, B384) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5">
-      <c r="A385" s="1">
-        <f t="shared" si="16"/>
-        <v>382</v>
-      </c>
-      <c r="D385" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E385" s="10">
-        <f>COUNTIF($B$2:B385, B385) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5">
-      <c r="A386" s="1">
-        <f t="shared" si="16"/>
-        <v>383</v>
-      </c>
-      <c r="D386" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E386" s="10">
-        <f>COUNTIF($B$2:B386, B386) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5">
-      <c r="A387" s="1">
-        <f t="shared" si="16"/>
-        <v>384</v>
-      </c>
-      <c r="D387" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E387" s="10">
-        <f>COUNTIF($B$2:B387, B387) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5">
-      <c r="A388" s="1">
-        <f t="shared" si="16"/>
-        <v>385</v>
-      </c>
-      <c r="D388" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E388" s="10">
-        <f>COUNTIF($B$2:B388, B388) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5">
-      <c r="A389" s="1">
-        <f t="shared" ref="A389:A443" si="18">A388+1</f>
-        <v>386</v>
-      </c>
-      <c r="D389" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E389" s="10">
-        <f>COUNTIF($B$2:B389, B389) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5">
-      <c r="A390" s="1">
-        <f t="shared" si="18"/>
-        <v>387</v>
-      </c>
-      <c r="D390" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E390" s="10">
-        <f>COUNTIF($B$2:B390, B390) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5">
-      <c r="A391" s="1">
-        <f t="shared" si="18"/>
-        <v>388</v>
-      </c>
-      <c r="D391" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E391" s="10">
-        <f>COUNTIF($B$2:B391, B391) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5">
-      <c r="A392" s="1">
-        <f t="shared" si="18"/>
-        <v>389</v>
-      </c>
-      <c r="D392" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E392" s="10">
-        <f>COUNTIF($B$2:B392, B392) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5">
-      <c r="A393" s="1">
-        <f t="shared" si="18"/>
-        <v>390</v>
-      </c>
-      <c r="D393" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E393" s="10">
-        <f>COUNTIF($B$2:B393, B393) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5">
-      <c r="A394" s="1">
-        <f t="shared" si="18"/>
-        <v>391</v>
-      </c>
-      <c r="D394" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E394" s="10">
-        <f>COUNTIF($B$2:B394, B394) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5">
-      <c r="A395" s="1">
-        <f t="shared" si="18"/>
-        <v>392</v>
-      </c>
-      <c r="D395" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E395" s="10">
-        <f>COUNTIF($B$2:B395, B395) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5">
-      <c r="A396" s="1">
-        <f t="shared" si="18"/>
-        <v>393</v>
-      </c>
-      <c r="D396" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E396" s="10">
-        <f>COUNTIF($B$2:B396, B396) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5">
-      <c r="A397" s="1">
-        <f t="shared" si="18"/>
-        <v>394</v>
-      </c>
-      <c r="D397" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E397" s="10">
-        <f>COUNTIF($B$2:B397, B397) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5">
-      <c r="A398" s="1">
-        <f t="shared" si="18"/>
-        <v>395</v>
-      </c>
-      <c r="D398" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E398" s="10">
-        <f>COUNTIF($B$2:B398, B398) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5">
-      <c r="A399" s="1">
-        <f t="shared" si="18"/>
-        <v>396</v>
-      </c>
-      <c r="D399" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E399" s="10">
-        <f>COUNTIF($B$2:B399, B399) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5">
-      <c r="A400" s="1">
-        <f t="shared" si="18"/>
-        <v>397</v>
-      </c>
-      <c r="D400" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E400" s="10">
-        <f>COUNTIF($B$2:B400, B400) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5">
-      <c r="A401" s="1">
-        <f t="shared" si="18"/>
-        <v>398</v>
-      </c>
-      <c r="D401" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E401" s="10">
-        <f>COUNTIF($B$2:B401, B401) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5">
-      <c r="A402" s="1">
-        <f t="shared" si="18"/>
-        <v>399</v>
-      </c>
-      <c r="D402" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E402" s="10">
-        <f>COUNTIF($B$2:B402, B402) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5">
-      <c r="A403" s="1">
-        <f t="shared" si="18"/>
-        <v>400</v>
-      </c>
-      <c r="D403" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E403" s="10">
-        <f>COUNTIF($B$2:B403, B403) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5">
-      <c r="A404" s="1">
-        <f t="shared" si="18"/>
-        <v>401</v>
-      </c>
-      <c r="D404" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E404" s="10">
-        <f>COUNTIF($B$2:B404, B404) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5">
-      <c r="A405" s="1">
-        <f t="shared" si="18"/>
-        <v>402</v>
-      </c>
-      <c r="D405" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E405" s="10">
-        <f>COUNTIF($B$2:B405, B405) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5">
-      <c r="A406" s="1">
-        <f t="shared" si="18"/>
-        <v>403</v>
-      </c>
-      <c r="D406" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E406" s="10">
-        <f>COUNTIF($B$2:B406, B406) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5">
-      <c r="A407" s="1">
-        <f t="shared" si="18"/>
-        <v>404</v>
-      </c>
-      <c r="D407" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E407" s="10">
-        <f>COUNTIF($B$2:B407, B407) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5">
-      <c r="A408" s="1">
-        <f t="shared" si="18"/>
-        <v>405</v>
-      </c>
-      <c r="D408" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E408" s="10">
-        <f>COUNTIF($B$2:B408, B408) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5">
-      <c r="A409" s="1">
-        <f t="shared" si="18"/>
-        <v>406</v>
-      </c>
-      <c r="D409" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E409" s="10">
-        <f>COUNTIF($B$2:B409, B409) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5">
-      <c r="A410" s="1">
-        <f t="shared" si="18"/>
-        <v>407</v>
-      </c>
-      <c r="D410" s="2" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E410" s="10">
-        <f>COUNTIF($B$2:B410, B410) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5">
-      <c r="A411" s="1">
-        <f t="shared" si="18"/>
-        <v>408</v>
-      </c>
-      <c r="D411" s="2" t="e">
-        <f t="shared" ref="D411:D474" si="19">VALUE(TEXT(_xlfn.XLOOKUP(B411, $M:$M, $N:$N), "00") &amp; TEXT(E411, "00"))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E411" s="10">
-        <f>COUNTIF($B$2:B411, B411) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5">
-      <c r="A412" s="1">
-        <f t="shared" si="18"/>
-        <v>409</v>
-      </c>
-      <c r="D412" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E412" s="10">
-        <f>COUNTIF($B$2:B412, B412) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5">
-      <c r="A413" s="1">
-        <f t="shared" si="18"/>
-        <v>410</v>
-      </c>
-      <c r="D413" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E413" s="10">
-        <f>COUNTIF($B$2:B413, B413) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5">
-      <c r="A414" s="1">
-        <f t="shared" si="18"/>
-        <v>411</v>
-      </c>
-      <c r="D414" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E414" s="10">
-        <f>COUNTIF($B$2:B414, B414) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5">
-      <c r="A415" s="1">
-        <f t="shared" si="18"/>
-        <v>412</v>
-      </c>
-      <c r="D415" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E415" s="10">
-        <f>COUNTIF($B$2:B415, B415) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5">
-      <c r="A416" s="1">
-        <f t="shared" si="18"/>
-        <v>413</v>
-      </c>
-      <c r="D416" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E416" s="10">
-        <f>COUNTIF($B$2:B416, B416) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5">
-      <c r="A417" s="1">
-        <f t="shared" si="18"/>
-        <v>414</v>
-      </c>
-      <c r="D417" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E417" s="10">
-        <f>COUNTIF($B$2:B417, B417) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5">
-      <c r="A418" s="1">
-        <f t="shared" si="18"/>
-        <v>415</v>
-      </c>
-      <c r="D418" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E418" s="10">
-        <f>COUNTIF($B$2:B418, B418) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5">
-      <c r="A419" s="1">
-        <f t="shared" si="18"/>
-        <v>416</v>
-      </c>
-      <c r="D419" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E419" s="10">
-        <f>COUNTIF($B$2:B419, B419) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5">
-      <c r="A420" s="1">
-        <f t="shared" si="18"/>
-        <v>417</v>
-      </c>
-      <c r="D420" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E420" s="10">
-        <f>COUNTIF($B$2:B420, B420) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5">
-      <c r="A421" s="1">
-        <f t="shared" si="18"/>
-        <v>418</v>
-      </c>
-      <c r="D421" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E421" s="10">
-        <f>COUNTIF($B$2:B421, B421) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5">
-      <c r="A422" s="1">
-        <f t="shared" si="18"/>
-        <v>419</v>
-      </c>
-      <c r="D422" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E422" s="10">
-        <f>COUNTIF($B$2:B422, B422) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5">
-      <c r="A423" s="1">
-        <f t="shared" si="18"/>
-        <v>420</v>
-      </c>
-      <c r="D423" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E423" s="10">
-        <f>COUNTIF($B$2:B423, B423) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5">
-      <c r="A424" s="1">
-        <f t="shared" si="18"/>
-        <v>421</v>
-      </c>
-      <c r="D424" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E424" s="10">
-        <f>COUNTIF($B$2:B424, B424) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5">
-      <c r="A425" s="1">
-        <f t="shared" si="18"/>
-        <v>422</v>
-      </c>
-      <c r="D425" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E425" s="10">
-        <f>COUNTIF($B$2:B425, B425) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5">
-      <c r="A426" s="1">
-        <f t="shared" si="18"/>
-        <v>423</v>
-      </c>
-      <c r="D426" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E426" s="10">
-        <f>COUNTIF($B$2:B426, B426) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5">
-      <c r="A427" s="1">
-        <f t="shared" si="18"/>
-        <v>424</v>
-      </c>
-      <c r="D427" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E427" s="10">
-        <f>COUNTIF($B$2:B427, B427) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="428" spans="1:5">
-      <c r="A428" s="1">
-        <f t="shared" si="18"/>
-        <v>425</v>
-      </c>
-      <c r="D428" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E428" s="10">
-        <f>COUNTIF($B$2:B428, B428) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5">
-      <c r="A429" s="1">
-        <f t="shared" si="18"/>
-        <v>426</v>
-      </c>
-      <c r="D429" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E429" s="10">
-        <f>COUNTIF($B$2:B429, B429) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5">
-      <c r="A430" s="1">
-        <f t="shared" si="18"/>
-        <v>427</v>
-      </c>
-      <c r="D430" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E430" s="10">
-        <f>COUNTIF($B$2:B430, B430) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5">
-      <c r="A431" s="1">
-        <f t="shared" si="18"/>
-        <v>428</v>
-      </c>
-      <c r="D431" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E431" s="10">
-        <f>COUNTIF($B$2:B431, B431) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5">
-      <c r="A432" s="1">
-        <f t="shared" si="18"/>
-        <v>429</v>
-      </c>
-      <c r="D432" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E432" s="10">
-        <f>COUNTIF($B$2:B432, B432) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="433" spans="1:5">
-      <c r="A433" s="1">
-        <f t="shared" si="18"/>
-        <v>430</v>
-      </c>
-      <c r="D433" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E433" s="10">
-        <f>COUNTIF($B$2:B433, B433) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5">
-      <c r="A434" s="1">
-        <f t="shared" si="18"/>
-        <v>431</v>
-      </c>
-      <c r="D434" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E434" s="10">
-        <f>COUNTIF($B$2:B434, B434) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5">
-      <c r="A435" s="1">
-        <f t="shared" si="18"/>
-        <v>432</v>
-      </c>
-      <c r="D435" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E435" s="10">
-        <f>COUNTIF($B$2:B435, B435) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5">
-      <c r="A436" s="1">
-        <f t="shared" si="18"/>
-        <v>433</v>
-      </c>
-      <c r="D436" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E436" s="10">
-        <f>COUNTIF($B$2:B436, B436) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5">
-      <c r="A437" s="1">
-        <f t="shared" si="18"/>
-        <v>434</v>
-      </c>
-      <c r="D437" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E437" s="10">
-        <f>COUNTIF($B$2:B437, B437) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5">
-      <c r="A438" s="1">
-        <f t="shared" si="18"/>
-        <v>435</v>
-      </c>
-      <c r="D438" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E438" s="10">
-        <f>COUNTIF($B$2:B438, B438) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5">
-      <c r="A439" s="1">
-        <f t="shared" si="18"/>
-        <v>436</v>
-      </c>
-      <c r="D439" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E439" s="10">
-        <f>COUNTIF($B$2:B439, B439) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5">
-      <c r="A440" s="1">
-        <f t="shared" si="18"/>
-        <v>437</v>
-      </c>
-      <c r="D440" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E440" s="10">
-        <f>COUNTIF($B$2:B440, B440) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5">
-      <c r="A441" s="1">
-        <f t="shared" si="18"/>
-        <v>438</v>
-      </c>
-      <c r="D441" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E441" s="10">
-        <f>COUNTIF($B$2:B441, B441) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5">
-      <c r="A442" s="1">
-        <f t="shared" si="18"/>
-        <v>439</v>
-      </c>
-      <c r="D442" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E442" s="10">
-        <f>COUNTIF($B$2:B442, B442) - 1</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5">
-      <c r="A443" s="1">
-        <f t="shared" si="18"/>
-        <v>440</v>
-      </c>
-      <c r="D443" s="2" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E443" s="10">
-        <f>COUNTIF($B$2:B443, B443) - 1</f>
-        <v>-1</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D2:D153 D155:D1001">
+  <conditionalFormatting sqref="D2:D719">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>COUNTIF($D:$D, D2) &gt; 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C155:C443 C2:C153" xr:uid="{A0C9F4D0-9B68-44D9-B8DD-944F863FFED9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C258" xr:uid="{A0C9F4D0-9B68-44D9-B8DD-944F863FFED9}">
       <formula1>$L$2:$L$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B153 B155:B443" xr:uid="{70750F9B-83E2-4167-B52A-B7919A8F4E08}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B258" xr:uid="{70750F9B-83E2-4167-B52A-B7919A8F4E08}">
       <formula1>$M$2:$M$28</formula1>
     </dataValidation>
   </dataValidations>
